--- a/SplitBelt Studies.xlsx
+++ b/SplitBelt Studies.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27126"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/33ab2cc4ec646a75/Documents/GitHub/Treadmill/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="8_{88D53368-C933-4C8C-9CC6-82E29FF24AFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6C6DADBC-3D24-468D-A49D-FB98C42FD3C8}"/>
+  <xr:revisionPtr revIDLastSave="44" documentId="8_{9B8E492B-0E78-4C94-A44A-5323969E6F8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3C8DB6C4-18E7-481C-A2A5-A63C8B02414B}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14400" windowHeight="15600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="292">
   <si>
     <t>SPLIT BELT PAPERS</t>
   </si>
@@ -609,17 +609,380 @@
   </si>
   <si>
     <t>no rails; 10 min adaptation; 6 min washout; no relevance of savings</t>
+  </si>
+  <si>
+    <t>Potential contributions of training intensity on locomotor performance in individuals with chronic stroke</t>
+  </si>
+  <si>
+    <t>Holleran, Rodriguez, Echauz, Leech,Hornby</t>
+  </si>
+  <si>
+    <t>French, Morton, Chralambous,Reisman</t>
+  </si>
+  <si>
+    <t>A locomotor learning paradigm using distorted visual feedback elicits strategic learning</t>
+  </si>
+  <si>
+    <t>Misiaszek</t>
+  </si>
+  <si>
+    <t>Lewek, Feasel, Wentzm Brooks, Whitton</t>
+  </si>
+  <si>
+    <t>Use of visual and proprioceptive feedback to improve gait speed and spatiotemporal symmetry follwing chronic stroke: a case series</t>
+  </si>
+  <si>
+    <t>vasudevan, Hamzey, Kirk</t>
+  </si>
+  <si>
+    <t>Using a split-belt treadmill to evaluate generalization of human locomotor adaptation</t>
+  </si>
+  <si>
+    <t>Reisman, Bastian, Morton</t>
+  </si>
+  <si>
+    <t>Neurophysiologic and Rehabilitation insights from split-belt and other locomotor adaptation programs</t>
+  </si>
+  <si>
+    <t>Rossi, Roemmich, Bastian</t>
+  </si>
+  <si>
+    <t>Understanding mechanisms of generalization folowing locomotor adaptation</t>
+  </si>
+  <si>
+    <t>Wood, Morton, Kim</t>
+  </si>
+  <si>
+    <t>the consistency of prior movements shapes locomotor use-dependent learning</t>
+  </si>
+  <si>
+    <t>Price</t>
+  </si>
+  <si>
+    <t>Minimum effort simulations of split-belt treadmill walking exploit asymmetry to reduce metabolic energy expenditure</t>
+  </si>
+  <si>
+    <t>Thompson,Bhat, French, Morton, Pohlig, Reisman</t>
+  </si>
+  <si>
+    <t>Effects of an acute high intensity exercise bout on retention of explicit, strategic locomotor learning in individuals with chronic stroke</t>
+  </si>
+  <si>
+    <t>Kim, Howsden, Bartels, Lee</t>
+  </si>
+  <si>
+    <t>Concurrent locomotor adaptation and retention to vusual and split-belt perturbations</t>
+  </si>
+  <si>
+    <t>Fettrow, Hupfeld,Reimann, Choi, Hass, Seidler</t>
+  </si>
+  <si>
+    <t>Age differences in adaptation of medial-lateral gait parameters during split-belt treadmill walking</t>
+  </si>
+  <si>
+    <t>Scarano, Tesio, Rota, Cerina, Catino, Maloggi</t>
+  </si>
+  <si>
+    <t>Dynamic Asymmetries do not match spatiotemporal step asymetries during split-belt walking</t>
+  </si>
+  <si>
+    <t>Song, Stenum, Leech, Keller, Roemmich</t>
+  </si>
+  <si>
+    <t>unilateral step training can drive faster learning of novel gait patterns</t>
+  </si>
+  <si>
+    <t>Mariscal, Iturralde, Torres-Oviedo</t>
+  </si>
+  <si>
+    <t>Altering attention to split-belt walking increases the generalization of motor memories across walking contexts</t>
+  </si>
+  <si>
+    <t>stroke patients (n = 12); walked on tied belts at increasing speed until 30 - 40% of heart rate reserve - this was set speed for two 4 week blocks of training (high intensity or low intensity) high intensity was a 70 - 80% of heart rate reserve - intensity was increased by adding (in order until HR was achieved: 10 lb weight vest, 5lb ankle weight on paretic leg, posterior directed resisitive forces on the trunk</t>
+  </si>
+  <si>
+    <t>up to 12 training sessions over 4 weeks, followed by a 4 week washout and a repeated 4 week training session in the opposite intensity session</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>6 minute walk test improved during high intensity training block than during low intensity. With the largest changes associated with participants that completed the high intensity session first.</t>
+  </si>
+  <si>
+    <t>Kim, Ogilvie, Shinabukuro, Stewart, Shin</t>
+  </si>
+  <si>
+    <t>Effects of visual feedback distortion on gait adaptation: comparison of implicit visual distortion versus concious modulation on retention of motor learning</t>
+  </si>
+  <si>
+    <t>from  French et al. 2018: "individuals who were naïve to the DVF continued to produce the asymmetric walking pattern when the VF was removed while the group informed about the DVF returned to a more symmetric walking pattern. Although the authors of that study did not conclude that there is an explicit component of the DVF paradigm, their result suggests that there may be both implicit and explicit learning processes occurring with this paradigm"</t>
+  </si>
+  <si>
+    <t>tied belts at 1.2 m/s; baseline, orientation, learning(gradual), 30s catch, learning(stable),post learning. Exp2 had 3 retention blocks with (what you learned, normal walking, returned to learned)</t>
+  </si>
+  <si>
+    <t>1.2 m/s, always tied belts - split is induced with visual feedback</t>
+  </si>
+  <si>
+    <t>handrails at the front of the treadmill</t>
+  </si>
+  <si>
+    <t>No instruction and Instruction group; Instructions:  “You will now see the same bars ...You will also see a horizontal line on the screen. I would like you to keep the bars at that line..., you will need to gradually increase or decrease your step length because the feedback may not be accurate all the time.”</t>
+  </si>
+  <si>
+    <t xml:space="preserve">front rail; gradual adaotation ove 9 +6 min; </t>
+  </si>
+  <si>
+    <t>exp1 n = 33; exp2 n = 6; used a visuomotor rotation framework to design a walking task with distorted visual feedback; treadmill walking with realtime visual feedback of steplength. One session, 4 phases: baseline, orientation, learning, postlearning. Visual feedback was a bargraph - positive feedback (text on screen) given when bars were within 1.5 % of same length. distortion was introduced gradually over 9 minutes until one steplength was shown ans 9% longer and the other as 9% shorter. groups instructions and no instruction. overground trials were down a 10 m hall. Walked for 15 minutes during learning, 5 of which were at full distortion, separated from gradual adaptation with a 30 s catch trial.1.2 m/s.. exp2 included 5 minute retention blocks 1) continue walking with same pattern you learned; 2) normal walking; 3) return to the learned walking phaase</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>exp1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">: used step symmetry index (left - right) where right leg was manipulated to be + 9% and left was -9%; adaptation in stp sym index was greater (~7%) in the instruction group than in the no instruction group (~ 4.5 %); no difference during the catch trial, but retuned to similar differences withh return of visual feedback (indicates a small similar sized aftereffect); </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Exp2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: learning, some deccy during the (continue walking as you had been), return to near symmetry during normal walking retenction, recovered most of learning during the walk as you did during learning block. verbal instructions and distorted visual feedback impact learning and aftereffects in split-belt walking. Distorted visual feedback results largely in explicit learning with some implicit</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> apparent in the catch trial, but large explicit component noticeable in the "return to walking how you did in learning"</t>
+    </r>
+  </si>
+  <si>
+    <t>Neural control of walking balance: IF falling THEN react ELSE continue (REVIEW)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Possibly a citation for walking stability, otherwise not super relevant: context dependent nature of balance responses - not consistent with simple local reflexes, but very fast, so suggesting some higher level influence or biasing on the reflexes;  </t>
+  </si>
+  <si>
+    <t>n = 2, so not comfortable drawing findings except for preliminary</t>
+  </si>
+  <si>
+    <t>Enhanced gait-related improvements after therapist- versus robotic-assisted locomotor training in subjects with chronic stroke: a randomized controlled study.</t>
+  </si>
+  <si>
+    <t>Hornby, Campbell, Kahn…</t>
+  </si>
+  <si>
+    <t>suggest that forcing symmetrical gait does not improve symmetry (from Lewek et al. 2012)</t>
+  </si>
+  <si>
+    <t>intervention: visual feedback for asymmetry (step length or stance time) was provided by rotating the VR scene (projected in front of participant) with a radius of curvature proportionalto asym. Proprioceptive feedback was provided by running the treadmill at different speeds so that the speed difference was proportional to asymmetry. treadmill speed was dynamically controlled based on an algorithm incorporating steplength and cadence.</t>
+  </si>
+  <si>
+    <t>improve gait speed and spaciotemporal symmetry after stroke - use combined proprioceptive and visual feedback to try to improve gait. n = 2 participants compleded a 6 wk treadmill + overground practice. Visual feedback from immersive virtual reality. Proprioceptive feedback from dual-belt treadmill. both patients improved. 18 sessions over 6 weeks 20 minutes on treadmill with feedback + 10 - 15 minute of overground practice.  encouraged to walk quickly, but maintained HR under 75% of max</t>
+  </si>
+  <si>
+    <t>yes harness and handriail</t>
+  </si>
+  <si>
+    <t>paper described split-belt protocol that incorportates quantification of locomotor learning and generalization to other contexts.</t>
+  </si>
+  <si>
+    <t>Dietz, Zijlstra, Duysens</t>
+  </si>
+  <si>
+    <t>first split-belt paper on human adults</t>
+  </si>
+  <si>
+    <t>Human neuronal interlimb coordination during split-belt locomotion</t>
+  </si>
+  <si>
+    <t>first paper with 10 min (somewhat extended adaptation)</t>
+  </si>
+  <si>
+    <t>first split-belt study on adults</t>
+  </si>
+  <si>
+    <t>evaluate mechanistic hypotheses of gait generalization to explain partial generalization. Findings suggest two central mondels that are separately adapted during split-velt walking, and of which only one generalizes to overground walking. Split-belt adaptation = forward model recal + stimulus response mapping (implicit)</t>
+  </si>
+  <si>
+    <t>Rossi, Leech, Roemmich, Bastian</t>
+  </si>
+  <si>
+    <t>Automatic Learning mechanisms for flexible human locomotion</t>
+  </si>
+  <si>
+    <t>seeing the errors you feel enchances locomotor performance but not learning</t>
+  </si>
+  <si>
+    <t>taylor and Ivry</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Flexible cognitive strategies during motor learning</t>
+  </si>
+  <si>
+    <t>Huberdeau, Krakuer, Haith</t>
+  </si>
+  <si>
+    <t>dual-process decomposition in human sensorimotor adaptation</t>
+  </si>
+  <si>
+    <t>Galgiani, French, Morton</t>
+  </si>
+  <si>
+    <t>Acute pain impairs retention of locomotor learning</t>
+  </si>
+  <si>
+    <t>Hasson, Manczurowsky, Yen</t>
+  </si>
+  <si>
+    <t>A reinforcement learning approach to gait training improves retention</t>
+  </si>
+  <si>
+    <t>"suggests a hierarchical organization that prioritizes corrections to temporal asymmetry over spatial asymmetry51. Thus, temporal gait asymmetry may be controlled via processes distinct from the ‘error-based’ mechanism that governs spatial learning." from Song et al. 2020</t>
+  </si>
+  <si>
+    <t>“prediction errors based on asymmetries in spatiotemporal stepping parameters (e.g., asymmetries in step length or step time) are unlikely to constitute the errors that drive split-belt adaptation, given that only one leg stepped during the unilateral stepping tasks.” (Song et al., 2020, p. 3)</t>
+  </si>
+  <si>
+    <t>all participants compledted a 10 minute prelearning, 10s catch trial, 10 minute splite-belt and 10 minute washout. Prelearnings were 1) control, 10 minutes tied walking at slow speed; 2)alternating unilateral training, fast leg at fast speed alternating with slow leg at slow speed in one minute intervals, 3) unilateral fast leg at fast speed only, 4) unilateral fast leg at slow speed only; 5) unilateral slow leg at slow speed only; 6) observation</t>
+  </si>
+  <si>
+    <t>faster learning than control in 1) alternating, 2) unilateral fast leg at fast, 3) unilateral fast leg at slow. Learning for the 4) slow leg at slow did not accelerate indicating a senticitty for learning associated with speed difference rather than with absolute speed</t>
+  </si>
+  <si>
+    <t>Ellmers, Cocks, Kal, Young</t>
+  </si>
+  <si>
+    <t>Conciours movement processing, fall related anxiety, and the visoumotor control of locomotion in older adults</t>
+  </si>
+  <si>
+    <t>cited in Tasy et  al. 2024 elife review as evidence of explicit learning in walking</t>
+  </si>
+  <si>
+    <t>cited in Tsay et al. 2024 elife review as evidence for explicit strategies in split belt walking</t>
+  </si>
+  <si>
+    <t>Roemmich and Bastian</t>
+  </si>
+  <si>
+    <t>Sombric, Calvert, Torres-Oviedo</t>
+  </si>
+  <si>
+    <t>Large propulsion demands increase locomotor adaptation at the expense of step length symmetry</t>
+  </si>
+  <si>
+    <t>3:1 ratio with 1.5 and ).5 m/s belt speeds, 600 adaptation strides in incline (+ 8.5 degree), flat, and decline (-8.5 degree) groups</t>
+  </si>
+  <si>
+    <t>further (and visually faster) adaptation to split-belt with visual feedback of steplengths rather than neutral visuals; cited in Tsay et al. 2024 elife review as suggesting explitit strategy in split belt; cited in Jacobsen and Ferris 2024 as a distinct voluntary correction process</t>
+  </si>
+  <si>
+    <t>Jacobsen and Ferris</t>
+  </si>
+  <si>
+    <t>Exploring electrocortical signatures of gait adaptation: differential neural dynamics in slow and fast gait adapters</t>
+  </si>
+  <si>
+    <t>n = 33 naive participants that would later be partitioned into fast and slow adapters - recorded neck EMG, dual-layer EEG (128 pin-type scalp electrodes and 128 flat-type noise electrodes - the pin and noise electrodes are mechanically coupled but electrically isolated to improve SNR (signal - noise). noise electordes allow isolation of motion articiact and electrical intereference - demonstrated and instructed to avoid jaw clenching, blinking, and neck muscle tension - electrode locations digitized with a head scan -  force plate treadmill and lower body motion capture - split-belt tast with 40 minutes: 15 minutes baseline (slow fast and medium), 15 minutes adaptationn (1.2 / 0.6 faster to dominant right foot), 10 min post (medium) -  fast / slow partition: “steady-state step length asymmetry similar to Fettrow et al. (2021) and Finley et al. (2015). Steady state was the average value calculated over the final 30 steps of adaptation. The threshold for achieving the steady state was determined when step length asymmetry remained within two SDs of the steady state for a minimum of 10 consecutive steps. Participants were sorted into two groups using a median split of the number of strides it took them to adapt, resulting in slow and fast adaptation groups.”</t>
+  </si>
+  <si>
+    <t>distinct patterns of alpha oscillations within the posterior parietal cortex, theta oscillations in the bilateral sensorimotor cortex, and alpha/beta oscillations within the right primary visual cortex, which differed between slow and fast adapters. Notably, the group effect on posterior parietal spectral power suggests that reduced alpha power during early adaptation may play a pivotal role in facilitating faster locomotor adaptation. These findings align with the role of the posterior parietal cortex in sensorimotor adaptation and its importance in spatial attention, sensory integration, and movement planning.”  - differences in electrocortical activity could indicate differences in perception of perturbation, balance loss, differences in visuospatial processing, different strategies requiring different visual cortex engagement</t>
+  </si>
+  <si>
+    <t>not changed while moving, not warned during stops</t>
+  </si>
+  <si>
+    <t>15 base (5/5/5 at slow, fast medium), 15 adapt (1.2 /0.6) , 10 post (medium)</t>
+  </si>
+  <si>
+    <t>no</t>
+  </si>
+  <si>
+    <t>Torres-Oviedo, Bastian</t>
+  </si>
+  <si>
+    <t>Seeeing is believing: effects of visual contextual cues on learning and transfer of locomotor adaptation</t>
+  </si>
+  <si>
+    <t>occulded vision during a gradually introduced perturbation and catch trials before testing transfer to overground walking - no vision group showed greater learning (aftereffects in the catch trial) and better transfer. Attributed to 1) greater variability during learning (more uncertainty -&gt; more sensitivity to / learning from error and 2) to sensory reweighting where the lack of visual cues augments proprioceptive gain</t>
+  </si>
+  <si>
+    <t>Sado, Nielsen, Glaister, Takahashi, Malcom, Mukherjee</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A passive exoskeleton can assist split-belt adaptation </t>
+  </si>
+  <si>
+    <t>n = 18 naive, healthy subjects, sort ed in to EXO and noExo groups. Kickstart exo device uses an exo tendon parallel to the lateral leg through pulleys on the hip, knee, and ankle. tendon tightened until participants felt the assist (no objective measure, but counted the tightening clicks of the device)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>faster learning through error augmentation? (as cited by Sado et al. 2022)</t>
+  </si>
+  <si>
+    <t>Cornwell, Novotny, Finley</t>
+  </si>
+  <si>
+    <t>Associations between asymmetry and reactive balance control during split-belt walking</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="13">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -650,8 +1013,44 @@
       <color rgb="FF000000"/>
       <name val="&quot;Arial&quot;"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -682,6 +1081,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -695,38 +1106,67 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -949,15 +1389,19 @@
   <dimension ref="A1:P1000"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="3.5703125" customWidth="1"/>
-    <col min="3" max="3" width="22.5703125" customWidth="1"/>
-    <col min="4" max="4" width="7.5703125" customWidth="1"/>
-    <col min="5" max="5" width="34.85546875" customWidth="1"/>
-    <col min="6" max="7" width="22.5703125" customWidth="1"/>
-    <col min="8" max="8" width="5.7109375" customWidth="1"/>
-    <col min="9" max="9" width="20" customWidth="1"/>
-    <col min="10" max="10" width="18.42578125" customWidth="1"/>
-    <col min="11" max="11" width="28.5703125" customWidth="1"/>
+    <col min="1" max="1" width="3.5703125" style="9" customWidth="1"/>
+    <col min="2" max="2" width="12.5703125" style="9"/>
+    <col min="3" max="3" width="31.85546875" style="9" customWidth="1"/>
+    <col min="4" max="4" width="7.5703125" style="9" customWidth="1"/>
+    <col min="5" max="5" width="71" style="9" customWidth="1"/>
+    <col min="6" max="7" width="22.5703125" style="9" customWidth="1"/>
+    <col min="8" max="8" width="5.7109375" style="9" customWidth="1"/>
+    <col min="9" max="9" width="20" style="9" customWidth="1"/>
+    <col min="10" max="10" width="18.42578125" style="9" customWidth="1"/>
+    <col min="11" max="11" width="66.42578125" style="9" customWidth="1"/>
+    <col min="12" max="14" width="12.5703125" style="9"/>
+    <col min="15" max="15" width="36.85546875" style="9" customWidth="1"/>
+    <col min="16" max="16384" width="12.5703125" style="9"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="25.5">
@@ -980,41 +1424,41 @@
       <c r="O1" s="1"/>
       <c r="P1" s="1"/>
     </row>
-    <row r="2" spans="1:16" ht="42.75">
+    <row r="2" spans="1:16" ht="51.75">
       <c r="A2" s="1"/>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="H2" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="I2" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1" t="s">
+      <c r="J2" s="13"/>
+      <c r="K2" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="L2" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="M2" s="1"/>
-      <c r="N2" s="1" t="s">
+      <c r="M2" s="13"/>
+      <c r="N2" s="13" t="s">
         <v>11</v>
       </c>
       <c r="O2" s="2" t="s">
@@ -1064,8 +1508,8 @@
       <c r="O3" s="1"/>
       <c r="P3" s="1"/>
     </row>
-    <row r="4" spans="1:16" ht="114.75">
-      <c r="A4" s="1">
+    <row r="4" spans="1:16" ht="89.25">
+      <c r="A4" s="18">
         <v>2</v>
       </c>
       <c r="B4" s="5" t="s">
@@ -1074,7 +1518,9 @@
       <c r="C4" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="D4" s="1"/>
+      <c r="D4" s="1">
+        <v>2019</v>
+      </c>
       <c r="E4" s="1" t="s">
         <v>25</v>
       </c>
@@ -1105,11 +1551,13 @@
       <c r="N4" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="O4" s="1"/>
+      <c r="O4" s="1" t="s">
+        <v>262</v>
+      </c>
       <c r="P4" s="1"/>
     </row>
-    <row r="5" spans="1:16" ht="242.25">
-      <c r="A5" s="1">
+    <row r="5" spans="1:16" ht="102">
+      <c r="A5" s="18">
         <v>3</v>
       </c>
       <c r="B5" s="1" t="s">
@@ -1144,7 +1592,7 @@
       <c r="M5" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="N5" s="11" t="s">
+      <c r="N5" s="10" t="s">
         <v>42</v>
       </c>
       <c r="O5" s="1"/>
@@ -1192,7 +1640,7 @@
       <c r="O6" s="1"/>
       <c r="P6" s="1"/>
     </row>
-    <row r="7" spans="1:16" ht="153">
+    <row r="7" spans="1:16" ht="89.25">
       <c r="A7" s="1">
         <v>5</v>
       </c>
@@ -1235,10 +1683,12 @@
       <c r="N7" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="O7" s="1"/>
+      <c r="O7" s="1" t="s">
+        <v>269</v>
+      </c>
       <c r="P7" s="1"/>
     </row>
-    <row r="8" spans="1:16" ht="280.5">
+    <row r="8" spans="1:16" ht="140.25">
       <c r="A8" s="1">
         <v>6</v>
       </c>
@@ -1278,13 +1728,13 @@
       <c r="M8" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="N8" s="11" t="s">
+      <c r="N8" s="10" t="s">
         <v>71</v>
       </c>
       <c r="O8" s="1"/>
       <c r="P8" s="1"/>
     </row>
-    <row r="9" spans="1:16" ht="178.5">
+    <row r="9" spans="1:16" ht="114.75">
       <c r="A9" s="1">
         <v>7</v>
       </c>
@@ -1330,7 +1780,7 @@
       <c r="O9" s="1"/>
       <c r="P9" s="1"/>
     </row>
-    <row r="10" spans="1:16" ht="57">
+    <row r="10" spans="1:16" ht="42.75">
       <c r="A10" s="1">
         <v>8</v>
       </c>
@@ -1358,7 +1808,7 @@
       <c r="O10" s="1"/>
       <c r="P10" s="1"/>
     </row>
-    <row r="11" spans="1:16" ht="153">
+    <row r="11" spans="1:16" ht="76.5">
       <c r="A11" s="1">
         <v>9</v>
       </c>
@@ -1399,10 +1849,12 @@
       <c r="N11" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="O11" s="1"/>
+      <c r="O11" s="15" t="s">
+        <v>248</v>
+      </c>
       <c r="P11" s="1"/>
     </row>
-    <row r="12" spans="1:16" ht="280.5">
+    <row r="12" spans="1:16" ht="293.25">
       <c r="A12" s="7">
         <v>10</v>
       </c>
@@ -1538,7 +1990,7 @@
       <c r="O14" s="1"/>
       <c r="P14" s="1"/>
     </row>
-    <row r="15" spans="1:16" ht="255">
+    <row r="15" spans="1:16" ht="165.75">
       <c r="A15" s="1">
         <v>13</v>
       </c>
@@ -1650,13 +2102,13 @@
       <c r="M17" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="N17" s="11" t="s">
+      <c r="N17" s="10" t="s">
         <v>153</v>
       </c>
       <c r="O17" s="1"/>
       <c r="P17" s="1"/>
     </row>
-    <row r="18" spans="1:16" ht="71.25">
+    <row r="18" spans="1:16" ht="63.75">
       <c r="A18" s="1">
         <v>16</v>
       </c>
@@ -1684,7 +2136,7 @@
       <c r="O18" s="1"/>
       <c r="P18" s="1"/>
     </row>
-    <row r="19" spans="1:16" ht="229.5">
+    <row r="19" spans="1:16" ht="127.5">
       <c r="A19" s="1">
         <v>17</v>
       </c>
@@ -1724,13 +2176,13 @@
       <c r="M19" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="N19" s="11" t="s">
+      <c r="N19" s="10" t="s">
         <v>167</v>
       </c>
       <c r="O19" s="1"/>
       <c r="P19" s="1"/>
     </row>
-    <row r="20" spans="1:16" ht="71.25">
+    <row r="20" spans="1:16" ht="42.75">
       <c r="A20" s="1">
         <v>18</v>
       </c>
@@ -1756,7 +2208,7 @@
       <c r="O20" s="1"/>
       <c r="P20" s="1"/>
     </row>
-    <row r="21" spans="1:16" ht="42.75">
+    <row r="21" spans="1:16" ht="38.25">
       <c r="A21" s="1">
         <v>19</v>
       </c>
@@ -1775,13 +2227,13 @@
       <c r="H21" s="1"/>
       <c r="I21" s="1"/>
       <c r="J21" s="1"/>
-      <c r="K21" s="1"/>
+      <c r="K21" s="15" t="s">
+        <v>289</v>
+      </c>
       <c r="L21" s="1"/>
       <c r="M21" s="1"/>
-      <c r="N21" s="10"/>
-      <c r="O21" s="10"/>
-    </row>
-    <row r="22" spans="1:16" ht="99.75">
+    </row>
+    <row r="22" spans="1:16" ht="89.25">
       <c r="A22" s="1">
         <v>20</v>
       </c>
@@ -1822,7 +2274,6 @@
       <c r="N22" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="O22" s="10"/>
     </row>
     <row r="23" spans="1:16" ht="63.75">
       <c r="A23" s="1">
@@ -1846,8 +2297,6 @@
       <c r="K23" s="1"/>
       <c r="L23" s="1"/>
       <c r="M23" s="1"/>
-      <c r="N23" s="10"/>
-      <c r="O23" s="10"/>
     </row>
     <row r="24" spans="1:16" ht="102">
       <c r="A24" s="1"/>
@@ -1881,3008 +2330,3307 @@
       <c r="K24" s="1"/>
       <c r="L24" s="1"/>
       <c r="M24" s="1"/>
-      <c r="N24" s="10" t="s">
+      <c r="N24" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="O24" s="10"/>
-    </row>
-    <row r="25" spans="1:16" ht="14.25">
+    </row>
+    <row r="25" spans="1:16" ht="89.25">
       <c r="A25" s="1"/>
-      <c r="B25" s="1"/>
-      <c r="C25" s="2"/>
-      <c r="D25" s="1"/>
-      <c r="E25" s="1"/>
-      <c r="F25" s="1"/>
-      <c r="G25" s="1"/>
-      <c r="H25" s="1"/>
-      <c r="I25" s="1"/>
+      <c r="B25" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="D25" s="1">
+        <v>2015</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="G25" s="15" t="s">
+        <v>223</v>
+      </c>
+      <c r="H25" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="I25" s="15" t="s">
+        <v>223</v>
+      </c>
       <c r="J25" s="1"/>
-      <c r="K25" s="1"/>
+      <c r="K25" s="15" t="s">
+        <v>224</v>
+      </c>
       <c r="L25" s="1"/>
       <c r="M25" s="1"/>
-      <c r="N25" s="10"/>
-      <c r="O25" s="10"/>
-    </row>
-    <row r="26" spans="1:16" ht="14.25">
+    </row>
+    <row r="26" spans="1:16" ht="191.25">
       <c r="A26" s="1"/>
-      <c r="B26" s="1"/>
-      <c r="C26" s="2"/>
-      <c r="D26" s="1"/>
-      <c r="E26" s="1"/>
-      <c r="F26" s="1"/>
-      <c r="G26" s="1"/>
-      <c r="H26" s="1"/>
-      <c r="I26" s="1"/>
-      <c r="J26" s="1"/>
-      <c r="K26" s="1"/>
+      <c r="B26" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="D26" s="1">
+        <v>2018</v>
+      </c>
+      <c r="E26" s="15" t="s">
+        <v>233</v>
+      </c>
+      <c r="F26" s="15" t="s">
+        <v>228</v>
+      </c>
+      <c r="G26" s="15" t="s">
+        <v>229</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="J26" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="K26" s="15" t="s">
+        <v>234</v>
+      </c>
       <c r="L26" s="1"/>
       <c r="M26" s="1"/>
-      <c r="N26" s="10"/>
-      <c r="O26" s="10"/>
-    </row>
-    <row r="27" spans="1:16" ht="14.25">
-      <c r="A27" s="10"/>
-      <c r="B27" s="10"/>
-      <c r="C27" s="2"/>
-      <c r="D27" s="10"/>
-      <c r="E27" s="10"/>
-      <c r="F27" s="10"/>
-      <c r="G27" s="10"/>
-      <c r="H27" s="10"/>
-      <c r="I27" s="10"/>
-      <c r="J27" s="10"/>
-      <c r="K27" s="10"/>
-      <c r="L27" s="10"/>
-      <c r="M27" s="10"/>
-      <c r="N27" s="10"/>
-      <c r="O27" s="10"/>
-    </row>
-    <row r="28" spans="1:16" ht="14.25">
-      <c r="A28" s="10"/>
-      <c r="B28" s="10"/>
-      <c r="C28" s="2"/>
-      <c r="D28" s="10"/>
-      <c r="E28" s="10"/>
-      <c r="F28" s="10"/>
-      <c r="G28" s="10"/>
-      <c r="H28" s="10"/>
-      <c r="I28" s="10"/>
-      <c r="J28" s="10"/>
-      <c r="K28" s="10"/>
-      <c r="L28" s="10"/>
-      <c r="M28" s="10"/>
-      <c r="N28" s="10"/>
-      <c r="O28" s="10"/>
-    </row>
-    <row r="29" spans="1:16" ht="14.25">
-      <c r="A29" s="10"/>
-      <c r="B29" s="10"/>
-      <c r="C29" s="2"/>
-      <c r="D29" s="10"/>
-      <c r="E29" s="10"/>
-      <c r="F29" s="10"/>
-      <c r="G29" s="10"/>
-      <c r="H29" s="10"/>
-      <c r="I29" s="10"/>
-      <c r="J29" s="10"/>
-      <c r="K29" s="10"/>
-      <c r="L29" s="10"/>
-      <c r="M29" s="10"/>
-      <c r="N29" s="10"/>
-      <c r="O29" s="10"/>
-    </row>
-    <row r="30" spans="1:16" ht="14.25">
-      <c r="C30" s="9"/>
-    </row>
-    <row r="31" spans="1:16" ht="14.25">
-      <c r="C31" s="9"/>
-    </row>
-    <row r="32" spans="1:16" ht="14.25">
-      <c r="C32" s="9"/>
-    </row>
-    <row r="33" spans="3:3" ht="14.25">
-      <c r="C33" s="9"/>
-    </row>
-    <row r="34" spans="3:3" ht="14.25">
-      <c r="C34" s="9"/>
-    </row>
-    <row r="35" spans="3:3" ht="14.25">
-      <c r="C35" s="9"/>
-    </row>
-    <row r="36" spans="3:3" ht="14.25">
-      <c r="C36" s="9"/>
-    </row>
-    <row r="37" spans="3:3" ht="14.25">
-      <c r="C37" s="9"/>
-    </row>
-    <row r="38" spans="3:3" ht="14.25">
-      <c r="C38" s="9"/>
-    </row>
-    <row r="39" spans="3:3" ht="14.25">
-      <c r="C39" s="9"/>
-    </row>
-    <row r="40" spans="3:3" ht="14.25">
-      <c r="C40" s="9"/>
-    </row>
-    <row r="41" spans="3:3" ht="14.25">
-      <c r="C41" s="9"/>
-    </row>
-    <row r="42" spans="3:3" ht="14.25">
-      <c r="C42" s="9"/>
-    </row>
-    <row r="43" spans="3:3" ht="14.25">
-      <c r="C43" s="9"/>
-    </row>
-    <row r="44" spans="3:3" ht="14.25">
-      <c r="C44" s="9"/>
-    </row>
-    <row r="45" spans="3:3" ht="14.25">
-      <c r="C45" s="9"/>
-    </row>
-    <row r="46" spans="3:3" ht="14.25">
-      <c r="C46" s="9"/>
-    </row>
-    <row r="47" spans="3:3" ht="14.25">
-      <c r="C47" s="9"/>
-    </row>
-    <row r="48" spans="3:3" ht="14.25">
-      <c r="C48" s="9"/>
-    </row>
-    <row r="49" spans="3:3" ht="14.25">
-      <c r="C49" s="9"/>
-    </row>
-    <row r="50" spans="3:3" ht="14.25">
-      <c r="C50" s="9"/>
-    </row>
-    <row r="51" spans="3:3" ht="14.25">
-      <c r="C51" s="9"/>
-    </row>
-    <row r="52" spans="3:3" ht="14.25">
-      <c r="C52" s="9"/>
-    </row>
-    <row r="53" spans="3:3" ht="14.25">
-      <c r="C53" s="9"/>
-    </row>
-    <row r="54" spans="3:3" ht="14.25">
-      <c r="C54" s="9"/>
-    </row>
-    <row r="55" spans="3:3" ht="14.25">
-      <c r="C55" s="9"/>
-    </row>
-    <row r="56" spans="3:3" ht="14.25">
-      <c r="C56" s="9"/>
-    </row>
-    <row r="57" spans="3:3" ht="14.25">
-      <c r="C57" s="9"/>
-    </row>
-    <row r="58" spans="3:3" ht="14.25">
-      <c r="C58" s="9"/>
-    </row>
-    <row r="59" spans="3:3" ht="14.25">
-      <c r="C59" s="9"/>
-    </row>
-    <row r="60" spans="3:3" ht="14.25">
-      <c r="C60" s="9"/>
-    </row>
-    <row r="61" spans="3:3" ht="14.25">
-      <c r="C61" s="9"/>
-    </row>
-    <row r="62" spans="3:3" ht="14.25">
-      <c r="C62" s="9"/>
-    </row>
-    <row r="63" spans="3:3" ht="14.25">
-      <c r="C63" s="9"/>
-    </row>
-    <row r="64" spans="3:3" ht="14.25">
-      <c r="C64" s="9"/>
+    </row>
+    <row r="27" spans="1:16" ht="42.75">
+      <c r="B27" s="9" t="s">
+        <v>196</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="D27" s="9">
+        <v>2006</v>
+      </c>
+      <c r="E27" s="9" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16" ht="242.25">
+      <c r="B28" s="9" t="s">
+        <v>197</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="D28" s="9">
+        <v>2012</v>
+      </c>
+      <c r="E28" s="9" t="s">
+        <v>242</v>
+      </c>
+      <c r="F28" s="9" t="s">
+        <v>241</v>
+      </c>
+      <c r="H28" s="9" t="s">
+        <v>243</v>
+      </c>
+      <c r="K28" s="9" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16" ht="42.75">
+      <c r="B29" s="9" t="s">
+        <v>199</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="D29" s="9">
+        <v>2017</v>
+      </c>
+      <c r="E29" s="9" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16" ht="57">
+      <c r="B30" s="9" t="s">
+        <v>201</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="D30" s="9">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16" ht="51">
+      <c r="B31" s="11" t="s">
+        <v>203</v>
+      </c>
+      <c r="C31" s="12" t="s">
+        <v>204</v>
+      </c>
+      <c r="D31" s="9">
+        <v>2024</v>
+      </c>
+      <c r="E31" s="9" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16" ht="42.75">
+      <c r="B32" s="11" t="s">
+        <v>205</v>
+      </c>
+      <c r="C32" s="12" t="s">
+        <v>206</v>
+      </c>
+      <c r="D32" s="9">
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" ht="57">
+      <c r="B33" s="11" t="s">
+        <v>207</v>
+      </c>
+      <c r="C33" s="12" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" ht="71.25">
+      <c r="B34" s="11" t="s">
+        <v>209</v>
+      </c>
+      <c r="C34" s="12" t="s">
+        <v>210</v>
+      </c>
+      <c r="D34" s="9">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" ht="57">
+      <c r="B35" s="11" t="s">
+        <v>211</v>
+      </c>
+      <c r="C35" s="12" t="s">
+        <v>212</v>
+      </c>
+      <c r="D35" s="9">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" ht="51">
+      <c r="B36" s="11" t="s">
+        <v>213</v>
+      </c>
+      <c r="C36" s="12" t="s">
+        <v>214</v>
+      </c>
+      <c r="D36" s="9">
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15" ht="63.75">
+      <c r="B37" s="11" t="s">
+        <v>215</v>
+      </c>
+      <c r="C37" s="12" t="s">
+        <v>216</v>
+      </c>
+      <c r="D37" s="9">
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15" ht="89.25">
+      <c r="A38" s="19"/>
+      <c r="B38" s="11" t="s">
+        <v>217</v>
+      </c>
+      <c r="C38" s="17" t="s">
+        <v>218</v>
+      </c>
+      <c r="D38" s="9">
+        <v>2020</v>
+      </c>
+      <c r="E38" s="9" t="s">
+        <v>264</v>
+      </c>
+      <c r="K38" s="9" t="s">
+        <v>265</v>
+      </c>
+      <c r="O38" s="9" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15" ht="71.25">
+      <c r="B39" s="11" t="s">
+        <v>219</v>
+      </c>
+      <c r="C39" s="12" t="s">
+        <v>220</v>
+      </c>
+      <c r="D39" s="9">
+        <v>2020</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15" ht="85.5">
+      <c r="B40" s="11" t="s">
+        <v>225</v>
+      </c>
+      <c r="C40" s="16" t="s">
+        <v>226</v>
+      </c>
+      <c r="D40" s="9">
+        <v>2015</v>
+      </c>
+      <c r="K40" s="11" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15" ht="85.5">
+      <c r="B41" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="D41" s="9">
+        <v>2008</v>
+      </c>
+      <c r="K41" s="9" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15" ht="38.25">
+      <c r="B42" s="11" t="s">
+        <v>245</v>
+      </c>
+      <c r="C42" s="11" t="s">
+        <v>247</v>
+      </c>
+      <c r="D42" s="9">
+        <v>1994</v>
+      </c>
+      <c r="E42" s="11" t="s">
+        <v>246</v>
+      </c>
+      <c r="O42" s="11" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15" ht="42.75">
+      <c r="B43" s="9" t="s">
+        <v>251</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="D43" s="9">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15" ht="51">
+      <c r="B44" s="9" t="s">
+        <v>270</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="D44" s="9">
+        <v>2016</v>
+      </c>
+      <c r="K44" s="9" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15" ht="28.5">
+      <c r="B45" s="9" t="s">
+        <v>254</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="D45" s="9">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15" ht="38.25">
+      <c r="B46" s="9" t="s">
+        <v>256</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="D46" s="9">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15" ht="38.25">
+      <c r="B47" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="D47" s="9">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="48" spans="1:15" ht="42.75">
+      <c r="B48" s="9" t="s">
+        <v>260</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="D48" s="9">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="49" spans="2:11" ht="57">
+      <c r="B49" s="9" t="s">
+        <v>266</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="D49" s="9">
+        <v>2020</v>
+      </c>
+      <c r="K49" s="9" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="50" spans="2:11" ht="57">
+      <c r="B50" s="9" t="s">
+        <v>271</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="D50" s="9">
+        <v>2019</v>
+      </c>
+      <c r="E50" s="9" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="51" spans="2:11" ht="204">
+      <c r="B51" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="D51" s="9">
+        <v>2024</v>
+      </c>
+      <c r="E51" s="9" t="s">
+        <v>277</v>
+      </c>
+      <c r="F51" s="11" t="s">
+        <v>280</v>
+      </c>
+      <c r="G51" s="11" t="s">
+        <v>279</v>
+      </c>
+      <c r="H51" s="11" t="s">
+        <v>281</v>
+      </c>
+      <c r="I51" s="11" t="s">
+        <v>281</v>
+      </c>
+      <c r="K51" s="11" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="52" spans="2:11" ht="63.75">
+      <c r="B52" s="9" t="s">
+        <v>282</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="D52" s="9">
+        <v>2010</v>
+      </c>
+      <c r="E52" s="9" t="s">
+        <v>284</v>
+      </c>
+      <c r="K52" s="20"/>
+    </row>
+    <row r="53" spans="2:11" ht="76.5">
+      <c r="B53" s="9" t="s">
+        <v>285</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="D53" s="9">
+        <v>2022</v>
+      </c>
+      <c r="E53" s="9" t="s">
+        <v>287</v>
+      </c>
+      <c r="F53" s="11" t="s">
+        <v>288</v>
+      </c>
+      <c r="K53" s="20"/>
+    </row>
+    <row r="54" spans="2:11" ht="42.75">
+      <c r="B54" s="9" t="s">
+        <v>290</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="D54" s="9">
+        <v>2024</v>
+      </c>
+      <c r="K54" s="20"/>
+    </row>
+    <row r="55" spans="2:11" ht="14.25">
+      <c r="C55" s="2"/>
+      <c r="K55" s="20"/>
+    </row>
+    <row r="56" spans="2:11" ht="14.25">
+      <c r="C56" s="2"/>
+      <c r="K56" s="20"/>
+    </row>
+    <row r="57" spans="2:11" ht="14.25">
+      <c r="C57" s="2"/>
+      <c r="K57" s="20"/>
+    </row>
+    <row r="58" spans="2:11" ht="14.25">
+      <c r="C58" s="2"/>
+      <c r="K58" s="20"/>
+    </row>
+    <row r="59" spans="2:11" ht="14.25">
+      <c r="C59" s="2"/>
+      <c r="K59" s="20"/>
+    </row>
+    <row r="60" spans="2:11" ht="14.25">
+      <c r="C60" s="2"/>
+    </row>
+    <row r="61" spans="2:11" ht="14.25">
+      <c r="C61" s="2"/>
+    </row>
+    <row r="62" spans="2:11" ht="14.25">
+      <c r="C62" s="2"/>
+    </row>
+    <row r="63" spans="2:11" ht="14.25">
+      <c r="C63" s="2"/>
+    </row>
+    <row r="64" spans="2:11" ht="14.25">
+      <c r="C64" s="2"/>
     </row>
     <row r="65" spans="3:3" ht="14.25">
-      <c r="C65" s="9"/>
+      <c r="C65" s="2"/>
     </row>
     <row r="66" spans="3:3" ht="14.25">
-      <c r="C66" s="9"/>
+      <c r="C66" s="2"/>
     </row>
     <row r="67" spans="3:3" ht="14.25">
-      <c r="C67" s="9"/>
+      <c r="C67" s="2"/>
     </row>
     <row r="68" spans="3:3" ht="14.25">
-      <c r="C68" s="9"/>
+      <c r="C68" s="2"/>
     </row>
     <row r="69" spans="3:3" ht="14.25">
-      <c r="C69" s="9"/>
+      <c r="C69" s="2"/>
     </row>
     <row r="70" spans="3:3" ht="14.25">
-      <c r="C70" s="9"/>
+      <c r="C70" s="2"/>
     </row>
     <row r="71" spans="3:3" ht="14.25">
-      <c r="C71" s="9"/>
+      <c r="C71" s="2"/>
     </row>
     <row r="72" spans="3:3" ht="14.25">
-      <c r="C72" s="9"/>
+      <c r="C72" s="2"/>
     </row>
     <row r="73" spans="3:3" ht="14.25">
-      <c r="C73" s="9"/>
+      <c r="C73" s="2"/>
     </row>
     <row r="74" spans="3:3" ht="14.25">
-      <c r="C74" s="9"/>
+      <c r="C74" s="2"/>
     </row>
     <row r="75" spans="3:3" ht="14.25">
-      <c r="C75" s="9"/>
+      <c r="C75" s="2"/>
     </row>
     <row r="76" spans="3:3" ht="14.25">
-      <c r="C76" s="9"/>
+      <c r="C76" s="2"/>
     </row>
     <row r="77" spans="3:3" ht="14.25">
-      <c r="C77" s="9"/>
+      <c r="C77" s="2"/>
     </row>
     <row r="78" spans="3:3" ht="14.25">
-      <c r="C78" s="9"/>
+      <c r="C78" s="2"/>
     </row>
     <row r="79" spans="3:3" ht="14.25">
-      <c r="C79" s="9"/>
+      <c r="C79" s="2"/>
     </row>
     <row r="80" spans="3:3" ht="14.25">
-      <c r="C80" s="9"/>
+      <c r="C80" s="2"/>
     </row>
     <row r="81" spans="3:3" ht="14.25">
-      <c r="C81" s="9"/>
+      <c r="C81" s="2"/>
     </row>
     <row r="82" spans="3:3" ht="14.25">
-      <c r="C82" s="9"/>
+      <c r="C82" s="2"/>
     </row>
     <row r="83" spans="3:3" ht="14.25">
-      <c r="C83" s="9"/>
+      <c r="C83" s="2"/>
     </row>
     <row r="84" spans="3:3" ht="14.25">
-      <c r="C84" s="9"/>
+      <c r="C84" s="2"/>
     </row>
     <row r="85" spans="3:3" ht="14.25">
-      <c r="C85" s="9"/>
+      <c r="C85" s="2"/>
     </row>
     <row r="86" spans="3:3" ht="14.25">
-      <c r="C86" s="9"/>
+      <c r="C86" s="2"/>
     </row>
     <row r="87" spans="3:3" ht="14.25">
-      <c r="C87" s="9"/>
+      <c r="C87" s="2"/>
     </row>
     <row r="88" spans="3:3" ht="14.25">
-      <c r="C88" s="9"/>
+      <c r="C88" s="2"/>
     </row>
     <row r="89" spans="3:3" ht="14.25">
-      <c r="C89" s="9"/>
+      <c r="C89" s="2"/>
     </row>
     <row r="90" spans="3:3" ht="14.25">
-      <c r="C90" s="9"/>
+      <c r="C90" s="2"/>
     </row>
     <row r="91" spans="3:3" ht="14.25">
-      <c r="C91" s="9"/>
+      <c r="C91" s="2"/>
     </row>
     <row r="92" spans="3:3" ht="14.25">
-      <c r="C92" s="9"/>
+      <c r="C92" s="2"/>
     </row>
     <row r="93" spans="3:3" ht="14.25">
-      <c r="C93" s="9"/>
+      <c r="C93" s="2"/>
     </row>
     <row r="94" spans="3:3" ht="14.25">
-      <c r="C94" s="9"/>
+      <c r="C94" s="2"/>
     </row>
     <row r="95" spans="3:3" ht="14.25">
-      <c r="C95" s="9"/>
+      <c r="C95" s="2"/>
     </row>
     <row r="96" spans="3:3" ht="14.25">
-      <c r="C96" s="9"/>
+      <c r="C96" s="2"/>
     </row>
     <row r="97" spans="3:3" ht="14.25">
-      <c r="C97" s="9"/>
+      <c r="C97" s="2"/>
     </row>
     <row r="98" spans="3:3" ht="14.25">
-      <c r="C98" s="9"/>
+      <c r="C98" s="2"/>
     </row>
     <row r="99" spans="3:3" ht="14.25">
-      <c r="C99" s="9"/>
+      <c r="C99" s="2"/>
     </row>
     <row r="100" spans="3:3" ht="14.25">
-      <c r="C100" s="9"/>
+      <c r="C100" s="2"/>
     </row>
     <row r="101" spans="3:3" ht="14.25">
-      <c r="C101" s="9"/>
+      <c r="C101" s="2"/>
     </row>
     <row r="102" spans="3:3" ht="14.25">
-      <c r="C102" s="9"/>
+      <c r="C102" s="2"/>
     </row>
     <row r="103" spans="3:3" ht="14.25">
-      <c r="C103" s="9"/>
+      <c r="C103" s="2"/>
     </row>
     <row r="104" spans="3:3" ht="14.25">
-      <c r="C104" s="9"/>
+      <c r="C104" s="2"/>
     </row>
     <row r="105" spans="3:3" ht="14.25">
-      <c r="C105" s="9"/>
+      <c r="C105" s="2"/>
     </row>
     <row r="106" spans="3:3" ht="14.25">
-      <c r="C106" s="9"/>
+      <c r="C106" s="2"/>
     </row>
     <row r="107" spans="3:3" ht="14.25">
-      <c r="C107" s="9"/>
+      <c r="C107" s="2"/>
     </row>
     <row r="108" spans="3:3" ht="14.25">
-      <c r="C108" s="9"/>
+      <c r="C108" s="2"/>
     </row>
     <row r="109" spans="3:3" ht="14.25">
-      <c r="C109" s="9"/>
+      <c r="C109" s="2"/>
     </row>
     <row r="110" spans="3:3" ht="14.25">
-      <c r="C110" s="9"/>
+      <c r="C110" s="2"/>
     </row>
     <row r="111" spans="3:3" ht="14.25">
-      <c r="C111" s="9"/>
+      <c r="C111" s="2"/>
     </row>
     <row r="112" spans="3:3" ht="14.25">
-      <c r="C112" s="9"/>
+      <c r="C112" s="2"/>
     </row>
     <row r="113" spans="3:3" ht="14.25">
-      <c r="C113" s="9"/>
+      <c r="C113" s="2"/>
     </row>
     <row r="114" spans="3:3" ht="14.25">
-      <c r="C114" s="9"/>
+      <c r="C114" s="2"/>
     </row>
     <row r="115" spans="3:3" ht="14.25">
-      <c r="C115" s="9"/>
+      <c r="C115" s="2"/>
     </row>
     <row r="116" spans="3:3" ht="14.25">
-      <c r="C116" s="9"/>
+      <c r="C116" s="2"/>
     </row>
     <row r="117" spans="3:3" ht="14.25">
-      <c r="C117" s="9"/>
+      <c r="C117" s="2"/>
     </row>
     <row r="118" spans="3:3" ht="14.25">
-      <c r="C118" s="9"/>
+      <c r="C118" s="2"/>
     </row>
     <row r="119" spans="3:3" ht="14.25">
-      <c r="C119" s="9"/>
+      <c r="C119" s="2"/>
     </row>
     <row r="120" spans="3:3" ht="14.25">
-      <c r="C120" s="9"/>
+      <c r="C120" s="2"/>
     </row>
     <row r="121" spans="3:3" ht="14.25">
-      <c r="C121" s="9"/>
+      <c r="C121" s="2"/>
     </row>
     <row r="122" spans="3:3" ht="14.25">
-      <c r="C122" s="9"/>
+      <c r="C122" s="2"/>
     </row>
     <row r="123" spans="3:3" ht="14.25">
-      <c r="C123" s="9"/>
+      <c r="C123" s="2"/>
     </row>
     <row r="124" spans="3:3" ht="14.25">
-      <c r="C124" s="9"/>
+      <c r="C124" s="2"/>
     </row>
     <row r="125" spans="3:3" ht="14.25">
-      <c r="C125" s="9"/>
+      <c r="C125" s="2"/>
     </row>
     <row r="126" spans="3:3" ht="14.25">
-      <c r="C126" s="9"/>
+      <c r="C126" s="2"/>
     </row>
     <row r="127" spans="3:3" ht="14.25">
-      <c r="C127" s="9"/>
+      <c r="C127" s="2"/>
     </row>
     <row r="128" spans="3:3" ht="14.25">
-      <c r="C128" s="9"/>
+      <c r="C128" s="2"/>
     </row>
     <row r="129" spans="3:3" ht="14.25">
-      <c r="C129" s="9"/>
+      <c r="C129" s="2"/>
     </row>
     <row r="130" spans="3:3" ht="14.25">
-      <c r="C130" s="9"/>
+      <c r="C130" s="2"/>
     </row>
     <row r="131" spans="3:3" ht="14.25">
-      <c r="C131" s="9"/>
+      <c r="C131" s="2"/>
     </row>
     <row r="132" spans="3:3" ht="14.25">
-      <c r="C132" s="9"/>
+      <c r="C132" s="2"/>
     </row>
     <row r="133" spans="3:3" ht="14.25">
-      <c r="C133" s="9"/>
+      <c r="C133" s="2"/>
     </row>
     <row r="134" spans="3:3" ht="14.25">
-      <c r="C134" s="9"/>
+      <c r="C134" s="2"/>
     </row>
     <row r="135" spans="3:3" ht="14.25">
-      <c r="C135" s="9"/>
+      <c r="C135" s="2"/>
     </row>
     <row r="136" spans="3:3" ht="14.25">
-      <c r="C136" s="9"/>
+      <c r="C136" s="2"/>
     </row>
     <row r="137" spans="3:3" ht="14.25">
-      <c r="C137" s="9"/>
+      <c r="C137" s="2"/>
     </row>
     <row r="138" spans="3:3" ht="14.25">
-      <c r="C138" s="9"/>
+      <c r="C138" s="2"/>
     </row>
     <row r="139" spans="3:3" ht="14.25">
-      <c r="C139" s="9"/>
+      <c r="C139" s="2"/>
     </row>
     <row r="140" spans="3:3" ht="14.25">
-      <c r="C140" s="9"/>
+      <c r="C140" s="2"/>
     </row>
     <row r="141" spans="3:3" ht="14.25">
-      <c r="C141" s="9"/>
+      <c r="C141" s="2"/>
     </row>
     <row r="142" spans="3:3" ht="14.25">
-      <c r="C142" s="9"/>
+      <c r="C142" s="2"/>
     </row>
     <row r="143" spans="3:3" ht="14.25">
-      <c r="C143" s="9"/>
+      <c r="C143" s="2"/>
     </row>
     <row r="144" spans="3:3" ht="14.25">
-      <c r="C144" s="9"/>
+      <c r="C144" s="2"/>
     </row>
     <row r="145" spans="3:3" ht="14.25">
-      <c r="C145" s="9"/>
+      <c r="C145" s="2"/>
     </row>
     <row r="146" spans="3:3" ht="14.25">
-      <c r="C146" s="9"/>
+      <c r="C146" s="2"/>
     </row>
     <row r="147" spans="3:3" ht="14.25">
-      <c r="C147" s="9"/>
+      <c r="C147" s="2"/>
     </row>
     <row r="148" spans="3:3" ht="14.25">
-      <c r="C148" s="9"/>
+      <c r="C148" s="2"/>
     </row>
     <row r="149" spans="3:3" ht="14.25">
-      <c r="C149" s="9"/>
+      <c r="C149" s="2"/>
     </row>
     <row r="150" spans="3:3" ht="14.25">
-      <c r="C150" s="9"/>
+      <c r="C150" s="2"/>
     </row>
     <row r="151" spans="3:3" ht="14.25">
-      <c r="C151" s="9"/>
+      <c r="C151" s="2"/>
     </row>
     <row r="152" spans="3:3" ht="14.25">
-      <c r="C152" s="9"/>
+      <c r="C152" s="2"/>
     </row>
     <row r="153" spans="3:3" ht="14.25">
-      <c r="C153" s="9"/>
+      <c r="C153" s="2"/>
     </row>
     <row r="154" spans="3:3" ht="14.25">
-      <c r="C154" s="9"/>
+      <c r="C154" s="2"/>
     </row>
     <row r="155" spans="3:3" ht="14.25">
-      <c r="C155" s="9"/>
+      <c r="C155" s="2"/>
     </row>
     <row r="156" spans="3:3" ht="14.25">
-      <c r="C156" s="9"/>
+      <c r="C156" s="2"/>
     </row>
     <row r="157" spans="3:3" ht="14.25">
-      <c r="C157" s="9"/>
+      <c r="C157" s="2"/>
     </row>
     <row r="158" spans="3:3" ht="14.25">
-      <c r="C158" s="9"/>
+      <c r="C158" s="2"/>
     </row>
     <row r="159" spans="3:3" ht="14.25">
-      <c r="C159" s="9"/>
+      <c r="C159" s="2"/>
     </row>
     <row r="160" spans="3:3" ht="14.25">
-      <c r="C160" s="9"/>
+      <c r="C160" s="2"/>
     </row>
     <row r="161" spans="3:3" ht="14.25">
-      <c r="C161" s="9"/>
+      <c r="C161" s="2"/>
     </row>
     <row r="162" spans="3:3" ht="14.25">
-      <c r="C162" s="9"/>
+      <c r="C162" s="2"/>
     </row>
     <row r="163" spans="3:3" ht="14.25">
-      <c r="C163" s="9"/>
+      <c r="C163" s="2"/>
     </row>
     <row r="164" spans="3:3" ht="14.25">
-      <c r="C164" s="9"/>
+      <c r="C164" s="2"/>
     </row>
     <row r="165" spans="3:3" ht="14.25">
-      <c r="C165" s="9"/>
+      <c r="C165" s="2"/>
     </row>
     <row r="166" spans="3:3" ht="14.25">
-      <c r="C166" s="9"/>
+      <c r="C166" s="2"/>
     </row>
     <row r="167" spans="3:3" ht="14.25">
-      <c r="C167" s="9"/>
+      <c r="C167" s="2"/>
     </row>
     <row r="168" spans="3:3" ht="14.25">
-      <c r="C168" s="9"/>
+      <c r="C168" s="2"/>
     </row>
     <row r="169" spans="3:3" ht="14.25">
-      <c r="C169" s="9"/>
+      <c r="C169" s="2"/>
     </row>
     <row r="170" spans="3:3" ht="14.25">
-      <c r="C170" s="9"/>
+      <c r="C170" s="2"/>
     </row>
     <row r="171" spans="3:3" ht="14.25">
-      <c r="C171" s="9"/>
+      <c r="C171" s="2"/>
     </row>
     <row r="172" spans="3:3" ht="14.25">
-      <c r="C172" s="9"/>
+      <c r="C172" s="2"/>
     </row>
     <row r="173" spans="3:3" ht="14.25">
-      <c r="C173" s="9"/>
+      <c r="C173" s="2"/>
     </row>
     <row r="174" spans="3:3" ht="14.25">
-      <c r="C174" s="9"/>
+      <c r="C174" s="2"/>
     </row>
     <row r="175" spans="3:3" ht="14.25">
-      <c r="C175" s="9"/>
+      <c r="C175" s="2"/>
     </row>
     <row r="176" spans="3:3" ht="14.25">
-      <c r="C176" s="9"/>
+      <c r="C176" s="2"/>
     </row>
     <row r="177" spans="3:3" ht="14.25">
-      <c r="C177" s="9"/>
+      <c r="C177" s="2"/>
     </row>
     <row r="178" spans="3:3" ht="14.25">
-      <c r="C178" s="9"/>
+      <c r="C178" s="2"/>
     </row>
     <row r="179" spans="3:3" ht="14.25">
-      <c r="C179" s="9"/>
+      <c r="C179" s="2"/>
     </row>
     <row r="180" spans="3:3" ht="14.25">
-      <c r="C180" s="9"/>
+      <c r="C180" s="2"/>
     </row>
     <row r="181" spans="3:3" ht="14.25">
-      <c r="C181" s="9"/>
+      <c r="C181" s="2"/>
     </row>
     <row r="182" spans="3:3" ht="14.25">
-      <c r="C182" s="9"/>
+      <c r="C182" s="2"/>
     </row>
     <row r="183" spans="3:3" ht="14.25">
-      <c r="C183" s="9"/>
+      <c r="C183" s="2"/>
     </row>
     <row r="184" spans="3:3" ht="14.25">
-      <c r="C184" s="9"/>
+      <c r="C184" s="2"/>
     </row>
     <row r="185" spans="3:3" ht="14.25">
-      <c r="C185" s="9"/>
+      <c r="C185" s="2"/>
     </row>
     <row r="186" spans="3:3" ht="14.25">
-      <c r="C186" s="9"/>
+      <c r="C186" s="2"/>
     </row>
     <row r="187" spans="3:3" ht="14.25">
-      <c r="C187" s="9"/>
+      <c r="C187" s="2"/>
     </row>
     <row r="188" spans="3:3" ht="14.25">
-      <c r="C188" s="9"/>
+      <c r="C188" s="2"/>
     </row>
     <row r="189" spans="3:3" ht="14.25">
-      <c r="C189" s="9"/>
+      <c r="C189" s="2"/>
     </row>
     <row r="190" spans="3:3" ht="14.25">
-      <c r="C190" s="9"/>
+      <c r="C190" s="2"/>
     </row>
     <row r="191" spans="3:3" ht="14.25">
-      <c r="C191" s="9"/>
+      <c r="C191" s="2"/>
     </row>
     <row r="192" spans="3:3" ht="14.25">
-      <c r="C192" s="9"/>
+      <c r="C192" s="2"/>
     </row>
     <row r="193" spans="3:3" ht="14.25">
-      <c r="C193" s="9"/>
+      <c r="C193" s="2"/>
     </row>
     <row r="194" spans="3:3" ht="14.25">
-      <c r="C194" s="9"/>
+      <c r="C194" s="2"/>
     </row>
     <row r="195" spans="3:3" ht="14.25">
-      <c r="C195" s="9"/>
+      <c r="C195" s="2"/>
     </row>
     <row r="196" spans="3:3" ht="14.25">
-      <c r="C196" s="9"/>
+      <c r="C196" s="2"/>
     </row>
     <row r="197" spans="3:3" ht="14.25">
-      <c r="C197" s="9"/>
+      <c r="C197" s="2"/>
     </row>
     <row r="198" spans="3:3" ht="14.25">
-      <c r="C198" s="9"/>
+      <c r="C198" s="2"/>
     </row>
     <row r="199" spans="3:3" ht="14.25">
-      <c r="C199" s="9"/>
+      <c r="C199" s="2"/>
     </row>
     <row r="200" spans="3:3" ht="14.25">
-      <c r="C200" s="9"/>
+      <c r="C200" s="2"/>
     </row>
     <row r="201" spans="3:3" ht="14.25">
-      <c r="C201" s="9"/>
+      <c r="C201" s="2"/>
     </row>
     <row r="202" spans="3:3" ht="14.25">
-      <c r="C202" s="9"/>
+      <c r="C202" s="2"/>
     </row>
     <row r="203" spans="3:3" ht="14.25">
-      <c r="C203" s="9"/>
+      <c r="C203" s="2"/>
     </row>
     <row r="204" spans="3:3" ht="14.25">
-      <c r="C204" s="9"/>
+      <c r="C204" s="2"/>
     </row>
     <row r="205" spans="3:3" ht="14.25">
-      <c r="C205" s="9"/>
+      <c r="C205" s="2"/>
     </row>
     <row r="206" spans="3:3" ht="14.25">
-      <c r="C206" s="9"/>
+      <c r="C206" s="2"/>
     </row>
     <row r="207" spans="3:3" ht="14.25">
-      <c r="C207" s="9"/>
+      <c r="C207" s="2"/>
     </row>
     <row r="208" spans="3:3" ht="14.25">
-      <c r="C208" s="9"/>
+      <c r="C208" s="2"/>
     </row>
     <row r="209" spans="3:3" ht="14.25">
-      <c r="C209" s="9"/>
+      <c r="C209" s="2"/>
     </row>
     <row r="210" spans="3:3" ht="14.25">
-      <c r="C210" s="9"/>
+      <c r="C210" s="2"/>
     </row>
     <row r="211" spans="3:3" ht="14.25">
-      <c r="C211" s="9"/>
+      <c r="C211" s="2"/>
     </row>
     <row r="212" spans="3:3" ht="14.25">
-      <c r="C212" s="9"/>
+      <c r="C212" s="2"/>
     </row>
     <row r="213" spans="3:3" ht="14.25">
-      <c r="C213" s="9"/>
+      <c r="C213" s="2"/>
     </row>
     <row r="214" spans="3:3" ht="14.25">
-      <c r="C214" s="9"/>
+      <c r="C214" s="2"/>
     </row>
     <row r="215" spans="3:3" ht="14.25">
-      <c r="C215" s="9"/>
+      <c r="C215" s="2"/>
     </row>
     <row r="216" spans="3:3" ht="14.25">
-      <c r="C216" s="9"/>
+      <c r="C216" s="2"/>
     </row>
     <row r="217" spans="3:3" ht="14.25">
-      <c r="C217" s="9"/>
+      <c r="C217" s="2"/>
     </row>
     <row r="218" spans="3:3" ht="14.25">
-      <c r="C218" s="9"/>
+      <c r="C218" s="2"/>
     </row>
     <row r="219" spans="3:3" ht="14.25">
-      <c r="C219" s="9"/>
+      <c r="C219" s="2"/>
     </row>
     <row r="220" spans="3:3" ht="14.25">
-      <c r="C220" s="9"/>
+      <c r="C220" s="2"/>
     </row>
     <row r="221" spans="3:3" ht="14.25">
-      <c r="C221" s="9"/>
+      <c r="C221" s="2"/>
     </row>
     <row r="222" spans="3:3" ht="14.25">
-      <c r="C222" s="9"/>
+      <c r="C222" s="2"/>
     </row>
     <row r="223" spans="3:3" ht="14.25">
-      <c r="C223" s="9"/>
+      <c r="C223" s="2"/>
     </row>
     <row r="224" spans="3:3" ht="14.25">
-      <c r="C224" s="9"/>
+      <c r="C224" s="2"/>
     </row>
     <row r="225" spans="3:3" ht="14.25">
-      <c r="C225" s="9"/>
+      <c r="C225" s="2"/>
     </row>
     <row r="226" spans="3:3" ht="14.25">
-      <c r="C226" s="9"/>
+      <c r="C226" s="2"/>
     </row>
     <row r="227" spans="3:3" ht="14.25">
-      <c r="C227" s="9"/>
+      <c r="C227" s="2"/>
     </row>
     <row r="228" spans="3:3" ht="14.25">
-      <c r="C228" s="9"/>
+      <c r="C228" s="2"/>
     </row>
     <row r="229" spans="3:3" ht="14.25">
-      <c r="C229" s="9"/>
+      <c r="C229" s="2"/>
     </row>
     <row r="230" spans="3:3" ht="14.25">
-      <c r="C230" s="9"/>
+      <c r="C230" s="2"/>
     </row>
     <row r="231" spans="3:3" ht="14.25">
-      <c r="C231" s="9"/>
+      <c r="C231" s="2"/>
     </row>
     <row r="232" spans="3:3" ht="14.25">
-      <c r="C232" s="9"/>
+      <c r="C232" s="2"/>
     </row>
     <row r="233" spans="3:3" ht="14.25">
-      <c r="C233" s="9"/>
+      <c r="C233" s="2"/>
     </row>
     <row r="234" spans="3:3" ht="14.25">
-      <c r="C234" s="9"/>
+      <c r="C234" s="2"/>
     </row>
     <row r="235" spans="3:3" ht="14.25">
-      <c r="C235" s="9"/>
+      <c r="C235" s="2"/>
     </row>
     <row r="236" spans="3:3" ht="14.25">
-      <c r="C236" s="9"/>
+      <c r="C236" s="2"/>
     </row>
     <row r="237" spans="3:3" ht="14.25">
-      <c r="C237" s="9"/>
+      <c r="C237" s="2"/>
     </row>
     <row r="238" spans="3:3" ht="14.25">
-      <c r="C238" s="9"/>
+      <c r="C238" s="2"/>
     </row>
     <row r="239" spans="3:3" ht="14.25">
-      <c r="C239" s="9"/>
+      <c r="C239" s="2"/>
     </row>
     <row r="240" spans="3:3" ht="14.25">
-      <c r="C240" s="9"/>
+      <c r="C240" s="2"/>
     </row>
     <row r="241" spans="3:3" ht="14.25">
-      <c r="C241" s="9"/>
+      <c r="C241" s="2"/>
     </row>
     <row r="242" spans="3:3" ht="14.25">
-      <c r="C242" s="9"/>
+      <c r="C242" s="2"/>
     </row>
     <row r="243" spans="3:3" ht="14.25">
-      <c r="C243" s="9"/>
+      <c r="C243" s="2"/>
     </row>
     <row r="244" spans="3:3" ht="14.25">
-      <c r="C244" s="9"/>
+      <c r="C244" s="2"/>
     </row>
     <row r="245" spans="3:3" ht="14.25">
-      <c r="C245" s="9"/>
+      <c r="C245" s="2"/>
     </row>
     <row r="246" spans="3:3" ht="14.25">
-      <c r="C246" s="9"/>
+      <c r="C246" s="2"/>
     </row>
     <row r="247" spans="3:3" ht="14.25">
-      <c r="C247" s="9"/>
+      <c r="C247" s="2"/>
     </row>
     <row r="248" spans="3:3" ht="14.25">
-      <c r="C248" s="9"/>
+      <c r="C248" s="2"/>
     </row>
     <row r="249" spans="3:3" ht="14.25">
-      <c r="C249" s="9"/>
+      <c r="C249" s="2"/>
     </row>
     <row r="250" spans="3:3" ht="14.25">
-      <c r="C250" s="9"/>
+      <c r="C250" s="2"/>
     </row>
     <row r="251" spans="3:3" ht="14.25">
-      <c r="C251" s="9"/>
+      <c r="C251" s="2"/>
     </row>
     <row r="252" spans="3:3" ht="14.25">
-      <c r="C252" s="9"/>
+      <c r="C252" s="2"/>
     </row>
     <row r="253" spans="3:3" ht="14.25">
-      <c r="C253" s="9"/>
+      <c r="C253" s="2"/>
     </row>
     <row r="254" spans="3:3" ht="14.25">
-      <c r="C254" s="9"/>
+      <c r="C254" s="2"/>
     </row>
     <row r="255" spans="3:3" ht="14.25">
-      <c r="C255" s="9"/>
+      <c r="C255" s="2"/>
     </row>
     <row r="256" spans="3:3" ht="14.25">
-      <c r="C256" s="9"/>
+      <c r="C256" s="2"/>
     </row>
     <row r="257" spans="3:3" ht="14.25">
-      <c r="C257" s="9"/>
+      <c r="C257" s="2"/>
     </row>
     <row r="258" spans="3:3" ht="14.25">
-      <c r="C258" s="9"/>
+      <c r="C258" s="2"/>
     </row>
     <row r="259" spans="3:3" ht="14.25">
-      <c r="C259" s="9"/>
+      <c r="C259" s="2"/>
     </row>
     <row r="260" spans="3:3" ht="14.25">
-      <c r="C260" s="9"/>
+      <c r="C260" s="2"/>
     </row>
     <row r="261" spans="3:3" ht="14.25">
-      <c r="C261" s="9"/>
+      <c r="C261" s="2"/>
     </row>
     <row r="262" spans="3:3" ht="14.25">
-      <c r="C262" s="9"/>
+      <c r="C262" s="2"/>
     </row>
     <row r="263" spans="3:3" ht="14.25">
-      <c r="C263" s="9"/>
+      <c r="C263" s="2"/>
     </row>
     <row r="264" spans="3:3" ht="14.25">
-      <c r="C264" s="9"/>
+      <c r="C264" s="2"/>
     </row>
     <row r="265" spans="3:3" ht="14.25">
-      <c r="C265" s="9"/>
+      <c r="C265" s="2"/>
     </row>
     <row r="266" spans="3:3" ht="14.25">
-      <c r="C266" s="9"/>
+      <c r="C266" s="2"/>
     </row>
     <row r="267" spans="3:3" ht="14.25">
-      <c r="C267" s="9"/>
+      <c r="C267" s="2"/>
     </row>
     <row r="268" spans="3:3" ht="14.25">
-      <c r="C268" s="9"/>
+      <c r="C268" s="2"/>
     </row>
     <row r="269" spans="3:3" ht="14.25">
-      <c r="C269" s="9"/>
+      <c r="C269" s="2"/>
     </row>
     <row r="270" spans="3:3" ht="14.25">
-      <c r="C270" s="9"/>
+      <c r="C270" s="2"/>
     </row>
     <row r="271" spans="3:3" ht="14.25">
-      <c r="C271" s="9"/>
+      <c r="C271" s="2"/>
     </row>
     <row r="272" spans="3:3" ht="14.25">
-      <c r="C272" s="9"/>
+      <c r="C272" s="2"/>
     </row>
     <row r="273" spans="3:3" ht="14.25">
-      <c r="C273" s="9"/>
+      <c r="C273" s="2"/>
     </row>
     <row r="274" spans="3:3" ht="14.25">
-      <c r="C274" s="9"/>
+      <c r="C274" s="2"/>
     </row>
     <row r="275" spans="3:3" ht="14.25">
-      <c r="C275" s="9"/>
+      <c r="C275" s="2"/>
     </row>
     <row r="276" spans="3:3" ht="14.25">
-      <c r="C276" s="9"/>
+      <c r="C276" s="2"/>
     </row>
     <row r="277" spans="3:3" ht="14.25">
-      <c r="C277" s="9"/>
+      <c r="C277" s="2"/>
     </row>
     <row r="278" spans="3:3" ht="14.25">
-      <c r="C278" s="9"/>
+      <c r="C278" s="2"/>
     </row>
     <row r="279" spans="3:3" ht="14.25">
-      <c r="C279" s="9"/>
+      <c r="C279" s="2"/>
     </row>
     <row r="280" spans="3:3" ht="14.25">
-      <c r="C280" s="9"/>
+      <c r="C280" s="2"/>
     </row>
     <row r="281" spans="3:3" ht="14.25">
-      <c r="C281" s="9"/>
+      <c r="C281" s="2"/>
     </row>
     <row r="282" spans="3:3" ht="14.25">
-      <c r="C282" s="9"/>
+      <c r="C282" s="2"/>
     </row>
     <row r="283" spans="3:3" ht="14.25">
-      <c r="C283" s="9"/>
+      <c r="C283" s="2"/>
     </row>
     <row r="284" spans="3:3" ht="14.25">
-      <c r="C284" s="9"/>
+      <c r="C284" s="2"/>
     </row>
     <row r="285" spans="3:3" ht="14.25">
-      <c r="C285" s="9"/>
+      <c r="C285" s="2"/>
     </row>
     <row r="286" spans="3:3" ht="14.25">
-      <c r="C286" s="9"/>
+      <c r="C286" s="2"/>
     </row>
     <row r="287" spans="3:3" ht="14.25">
-      <c r="C287" s="9"/>
+      <c r="C287" s="2"/>
     </row>
     <row r="288" spans="3:3" ht="14.25">
-      <c r="C288" s="9"/>
+      <c r="C288" s="2"/>
     </row>
     <row r="289" spans="3:3" ht="14.25">
-      <c r="C289" s="9"/>
+      <c r="C289" s="2"/>
     </row>
     <row r="290" spans="3:3" ht="14.25">
-      <c r="C290" s="9"/>
+      <c r="C290" s="2"/>
     </row>
     <row r="291" spans="3:3" ht="14.25">
-      <c r="C291" s="9"/>
+      <c r="C291" s="2"/>
     </row>
     <row r="292" spans="3:3" ht="14.25">
-      <c r="C292" s="9"/>
+      <c r="C292" s="2"/>
     </row>
     <row r="293" spans="3:3" ht="14.25">
-      <c r="C293" s="9"/>
+      <c r="C293" s="2"/>
     </row>
     <row r="294" spans="3:3" ht="14.25">
-      <c r="C294" s="9"/>
+      <c r="C294" s="2"/>
     </row>
     <row r="295" spans="3:3" ht="14.25">
-      <c r="C295" s="9"/>
+      <c r="C295" s="2"/>
     </row>
     <row r="296" spans="3:3" ht="14.25">
-      <c r="C296" s="9"/>
+      <c r="C296" s="2"/>
     </row>
     <row r="297" spans="3:3" ht="14.25">
-      <c r="C297" s="9"/>
+      <c r="C297" s="2"/>
     </row>
     <row r="298" spans="3:3" ht="14.25">
-      <c r="C298" s="9"/>
+      <c r="C298" s="2"/>
     </row>
     <row r="299" spans="3:3" ht="14.25">
-      <c r="C299" s="9"/>
+      <c r="C299" s="2"/>
     </row>
     <row r="300" spans="3:3" ht="14.25">
-      <c r="C300" s="9"/>
+      <c r="C300" s="2"/>
     </row>
     <row r="301" spans="3:3" ht="14.25">
-      <c r="C301" s="9"/>
+      <c r="C301" s="2"/>
     </row>
     <row r="302" spans="3:3" ht="14.25">
-      <c r="C302" s="9"/>
+      <c r="C302" s="2"/>
     </row>
     <row r="303" spans="3:3" ht="14.25">
-      <c r="C303" s="9"/>
+      <c r="C303" s="2"/>
     </row>
     <row r="304" spans="3:3" ht="14.25">
-      <c r="C304" s="9"/>
+      <c r="C304" s="2"/>
     </row>
     <row r="305" spans="3:3" ht="14.25">
-      <c r="C305" s="9"/>
+      <c r="C305" s="2"/>
     </row>
     <row r="306" spans="3:3" ht="14.25">
-      <c r="C306" s="9"/>
+      <c r="C306" s="2"/>
     </row>
     <row r="307" spans="3:3" ht="14.25">
-      <c r="C307" s="9"/>
+      <c r="C307" s="2"/>
     </row>
     <row r="308" spans="3:3" ht="14.25">
-      <c r="C308" s="9"/>
+      <c r="C308" s="2"/>
     </row>
     <row r="309" spans="3:3" ht="14.25">
-      <c r="C309" s="9"/>
+      <c r="C309" s="2"/>
     </row>
     <row r="310" spans="3:3" ht="14.25">
-      <c r="C310" s="9"/>
+      <c r="C310" s="2"/>
     </row>
     <row r="311" spans="3:3" ht="14.25">
-      <c r="C311" s="9"/>
+      <c r="C311" s="2"/>
     </row>
     <row r="312" spans="3:3" ht="14.25">
-      <c r="C312" s="9"/>
+      <c r="C312" s="2"/>
     </row>
     <row r="313" spans="3:3" ht="14.25">
-      <c r="C313" s="9"/>
+      <c r="C313" s="2"/>
     </row>
     <row r="314" spans="3:3" ht="14.25">
-      <c r="C314" s="9"/>
+      <c r="C314" s="2"/>
     </row>
     <row r="315" spans="3:3" ht="14.25">
-      <c r="C315" s="9"/>
+      <c r="C315" s="2"/>
     </row>
     <row r="316" spans="3:3" ht="14.25">
-      <c r="C316" s="9"/>
+      <c r="C316" s="2"/>
     </row>
     <row r="317" spans="3:3" ht="14.25">
-      <c r="C317" s="9"/>
+      <c r="C317" s="2"/>
     </row>
     <row r="318" spans="3:3" ht="14.25">
-      <c r="C318" s="9"/>
+      <c r="C318" s="2"/>
     </row>
     <row r="319" spans="3:3" ht="14.25">
-      <c r="C319" s="9"/>
+      <c r="C319" s="2"/>
     </row>
     <row r="320" spans="3:3" ht="14.25">
-      <c r="C320" s="9"/>
+      <c r="C320" s="2"/>
     </row>
     <row r="321" spans="3:3" ht="14.25">
-      <c r="C321" s="9"/>
+      <c r="C321" s="2"/>
     </row>
     <row r="322" spans="3:3" ht="14.25">
-      <c r="C322" s="9"/>
+      <c r="C322" s="2"/>
     </row>
     <row r="323" spans="3:3" ht="14.25">
-      <c r="C323" s="9"/>
+      <c r="C323" s="2"/>
     </row>
     <row r="324" spans="3:3" ht="14.25">
-      <c r="C324" s="9"/>
+      <c r="C324" s="2"/>
     </row>
     <row r="325" spans="3:3" ht="14.25">
-      <c r="C325" s="9"/>
+      <c r="C325" s="2"/>
     </row>
     <row r="326" spans="3:3" ht="14.25">
-      <c r="C326" s="9"/>
+      <c r="C326" s="2"/>
     </row>
     <row r="327" spans="3:3" ht="14.25">
-      <c r="C327" s="9"/>
+      <c r="C327" s="2"/>
     </row>
     <row r="328" spans="3:3" ht="14.25">
-      <c r="C328" s="9"/>
+      <c r="C328" s="2"/>
     </row>
     <row r="329" spans="3:3" ht="14.25">
-      <c r="C329" s="9"/>
+      <c r="C329" s="2"/>
     </row>
     <row r="330" spans="3:3" ht="14.25">
-      <c r="C330" s="9"/>
+      <c r="C330" s="2"/>
     </row>
     <row r="331" spans="3:3" ht="14.25">
-      <c r="C331" s="9"/>
+      <c r="C331" s="2"/>
     </row>
     <row r="332" spans="3:3" ht="14.25">
-      <c r="C332" s="9"/>
+      <c r="C332" s="2"/>
     </row>
     <row r="333" spans="3:3" ht="14.25">
-      <c r="C333" s="9"/>
+      <c r="C333" s="2"/>
     </row>
     <row r="334" spans="3:3" ht="14.25">
-      <c r="C334" s="9"/>
+      <c r="C334" s="2"/>
     </row>
     <row r="335" spans="3:3" ht="14.25">
-      <c r="C335" s="9"/>
+      <c r="C335" s="2"/>
     </row>
     <row r="336" spans="3:3" ht="14.25">
-      <c r="C336" s="9"/>
+      <c r="C336" s="2"/>
     </row>
     <row r="337" spans="3:3" ht="14.25">
-      <c r="C337" s="9"/>
+      <c r="C337" s="2"/>
     </row>
     <row r="338" spans="3:3" ht="14.25">
-      <c r="C338" s="9"/>
+      <c r="C338" s="2"/>
     </row>
     <row r="339" spans="3:3" ht="14.25">
-      <c r="C339" s="9"/>
+      <c r="C339" s="2"/>
     </row>
     <row r="340" spans="3:3" ht="14.25">
-      <c r="C340" s="9"/>
+      <c r="C340" s="2"/>
     </row>
     <row r="341" spans="3:3" ht="14.25">
-      <c r="C341" s="9"/>
+      <c r="C341" s="2"/>
     </row>
     <row r="342" spans="3:3" ht="14.25">
-      <c r="C342" s="9"/>
+      <c r="C342" s="2"/>
     </row>
     <row r="343" spans="3:3" ht="14.25">
-      <c r="C343" s="9"/>
+      <c r="C343" s="2"/>
     </row>
     <row r="344" spans="3:3" ht="14.25">
-      <c r="C344" s="9"/>
+      <c r="C344" s="2"/>
     </row>
     <row r="345" spans="3:3" ht="14.25">
-      <c r="C345" s="9"/>
+      <c r="C345" s="2"/>
     </row>
     <row r="346" spans="3:3" ht="14.25">
-      <c r="C346" s="9"/>
+      <c r="C346" s="2"/>
     </row>
     <row r="347" spans="3:3" ht="14.25">
-      <c r="C347" s="9"/>
+      <c r="C347" s="2"/>
     </row>
     <row r="348" spans="3:3" ht="14.25">
-      <c r="C348" s="9"/>
+      <c r="C348" s="2"/>
     </row>
     <row r="349" spans="3:3" ht="14.25">
-      <c r="C349" s="9"/>
+      <c r="C349" s="2"/>
     </row>
     <row r="350" spans="3:3" ht="14.25">
-      <c r="C350" s="9"/>
+      <c r="C350" s="2"/>
     </row>
     <row r="351" spans="3:3" ht="14.25">
-      <c r="C351" s="9"/>
+      <c r="C351" s="2"/>
     </row>
     <row r="352" spans="3:3" ht="14.25">
-      <c r="C352" s="9"/>
+      <c r="C352" s="2"/>
     </row>
     <row r="353" spans="3:3" ht="14.25">
-      <c r="C353" s="9"/>
+      <c r="C353" s="2"/>
     </row>
     <row r="354" spans="3:3" ht="14.25">
-      <c r="C354" s="9"/>
+      <c r="C354" s="2"/>
     </row>
     <row r="355" spans="3:3" ht="14.25">
-      <c r="C355" s="9"/>
+      <c r="C355" s="2"/>
     </row>
     <row r="356" spans="3:3" ht="14.25">
-      <c r="C356" s="9"/>
+      <c r="C356" s="2"/>
     </row>
     <row r="357" spans="3:3" ht="14.25">
-      <c r="C357" s="9"/>
+      <c r="C357" s="2"/>
     </row>
     <row r="358" spans="3:3" ht="14.25">
-      <c r="C358" s="9"/>
+      <c r="C358" s="2"/>
     </row>
     <row r="359" spans="3:3" ht="14.25">
-      <c r="C359" s="9"/>
+      <c r="C359" s="2"/>
     </row>
     <row r="360" spans="3:3" ht="14.25">
-      <c r="C360" s="9"/>
+      <c r="C360" s="2"/>
     </row>
     <row r="361" spans="3:3" ht="14.25">
-      <c r="C361" s="9"/>
+      <c r="C361" s="2"/>
     </row>
     <row r="362" spans="3:3" ht="14.25">
-      <c r="C362" s="9"/>
+      <c r="C362" s="2"/>
     </row>
     <row r="363" spans="3:3" ht="14.25">
-      <c r="C363" s="9"/>
+      <c r="C363" s="2"/>
     </row>
     <row r="364" spans="3:3" ht="14.25">
-      <c r="C364" s="9"/>
+      <c r="C364" s="2"/>
     </row>
     <row r="365" spans="3:3" ht="14.25">
-      <c r="C365" s="9"/>
+      <c r="C365" s="2"/>
     </row>
     <row r="366" spans="3:3" ht="14.25">
-      <c r="C366" s="9"/>
+      <c r="C366" s="2"/>
     </row>
     <row r="367" spans="3:3" ht="14.25">
-      <c r="C367" s="9"/>
+      <c r="C367" s="2"/>
     </row>
     <row r="368" spans="3:3" ht="14.25">
-      <c r="C368" s="9"/>
+      <c r="C368" s="2"/>
     </row>
     <row r="369" spans="3:3" ht="14.25">
-      <c r="C369" s="9"/>
+      <c r="C369" s="2"/>
     </row>
     <row r="370" spans="3:3" ht="14.25">
-      <c r="C370" s="9"/>
+      <c r="C370" s="2"/>
     </row>
     <row r="371" spans="3:3" ht="14.25">
-      <c r="C371" s="9"/>
+      <c r="C371" s="2"/>
     </row>
     <row r="372" spans="3:3" ht="14.25">
-      <c r="C372" s="9"/>
+      <c r="C372" s="2"/>
     </row>
     <row r="373" spans="3:3" ht="14.25">
-      <c r="C373" s="9"/>
+      <c r="C373" s="2"/>
     </row>
     <row r="374" spans="3:3" ht="14.25">
-      <c r="C374" s="9"/>
+      <c r="C374" s="2"/>
     </row>
     <row r="375" spans="3:3" ht="14.25">
-      <c r="C375" s="9"/>
+      <c r="C375" s="2"/>
     </row>
     <row r="376" spans="3:3" ht="14.25">
-      <c r="C376" s="9"/>
+      <c r="C376" s="2"/>
     </row>
     <row r="377" spans="3:3" ht="14.25">
-      <c r="C377" s="9"/>
+      <c r="C377" s="2"/>
     </row>
     <row r="378" spans="3:3" ht="14.25">
-      <c r="C378" s="9"/>
+      <c r="C378" s="2"/>
     </row>
     <row r="379" spans="3:3" ht="14.25">
-      <c r="C379" s="9"/>
+      <c r="C379" s="2"/>
     </row>
     <row r="380" spans="3:3" ht="14.25">
-      <c r="C380" s="9"/>
+      <c r="C380" s="2"/>
     </row>
     <row r="381" spans="3:3" ht="14.25">
-      <c r="C381" s="9"/>
+      <c r="C381" s="2"/>
     </row>
     <row r="382" spans="3:3" ht="14.25">
-      <c r="C382" s="9"/>
+      <c r="C382" s="2"/>
     </row>
     <row r="383" spans="3:3" ht="14.25">
-      <c r="C383" s="9"/>
+      <c r="C383" s="2"/>
     </row>
     <row r="384" spans="3:3" ht="14.25">
-      <c r="C384" s="9"/>
+      <c r="C384" s="2"/>
     </row>
     <row r="385" spans="3:3" ht="14.25">
-      <c r="C385" s="9"/>
+      <c r="C385" s="2"/>
     </row>
     <row r="386" spans="3:3" ht="14.25">
-      <c r="C386" s="9"/>
+      <c r="C386" s="2"/>
     </row>
     <row r="387" spans="3:3" ht="14.25">
-      <c r="C387" s="9"/>
+      <c r="C387" s="2"/>
     </row>
     <row r="388" spans="3:3" ht="14.25">
-      <c r="C388" s="9"/>
+      <c r="C388" s="2"/>
     </row>
     <row r="389" spans="3:3" ht="14.25">
-      <c r="C389" s="9"/>
+      <c r="C389" s="2"/>
     </row>
     <row r="390" spans="3:3" ht="14.25">
-      <c r="C390" s="9"/>
+      <c r="C390" s="2"/>
     </row>
     <row r="391" spans="3:3" ht="14.25">
-      <c r="C391" s="9"/>
+      <c r="C391" s="2"/>
     </row>
     <row r="392" spans="3:3" ht="14.25">
-      <c r="C392" s="9"/>
+      <c r="C392" s="2"/>
     </row>
     <row r="393" spans="3:3" ht="14.25">
-      <c r="C393" s="9"/>
+      <c r="C393" s="2"/>
     </row>
     <row r="394" spans="3:3" ht="14.25">
-      <c r="C394" s="9"/>
+      <c r="C394" s="2"/>
     </row>
     <row r="395" spans="3:3" ht="14.25">
-      <c r="C395" s="9"/>
+      <c r="C395" s="2"/>
     </row>
     <row r="396" spans="3:3" ht="14.25">
-      <c r="C396" s="9"/>
+      <c r="C396" s="2"/>
     </row>
     <row r="397" spans="3:3" ht="14.25">
-      <c r="C397" s="9"/>
+      <c r="C397" s="2"/>
     </row>
     <row r="398" spans="3:3" ht="14.25">
-      <c r="C398" s="9"/>
+      <c r="C398" s="2"/>
     </row>
     <row r="399" spans="3:3" ht="14.25">
-      <c r="C399" s="9"/>
+      <c r="C399" s="2"/>
     </row>
     <row r="400" spans="3:3" ht="14.25">
-      <c r="C400" s="9"/>
+      <c r="C400" s="2"/>
     </row>
     <row r="401" spans="3:3" ht="14.25">
-      <c r="C401" s="9"/>
+      <c r="C401" s="2"/>
     </row>
     <row r="402" spans="3:3" ht="14.25">
-      <c r="C402" s="9"/>
+      <c r="C402" s="2"/>
     </row>
     <row r="403" spans="3:3" ht="14.25">
-      <c r="C403" s="9"/>
+      <c r="C403" s="2"/>
     </row>
     <row r="404" spans="3:3" ht="14.25">
-      <c r="C404" s="9"/>
+      <c r="C404" s="2"/>
     </row>
     <row r="405" spans="3:3" ht="14.25">
-      <c r="C405" s="9"/>
+      <c r="C405" s="2"/>
     </row>
     <row r="406" spans="3:3" ht="14.25">
-      <c r="C406" s="9"/>
+      <c r="C406" s="2"/>
     </row>
     <row r="407" spans="3:3" ht="14.25">
-      <c r="C407" s="9"/>
+      <c r="C407" s="2"/>
     </row>
     <row r="408" spans="3:3" ht="14.25">
-      <c r="C408" s="9"/>
+      <c r="C408" s="2"/>
     </row>
     <row r="409" spans="3:3" ht="14.25">
-      <c r="C409" s="9"/>
+      <c r="C409" s="2"/>
     </row>
     <row r="410" spans="3:3" ht="14.25">
-      <c r="C410" s="9"/>
+      <c r="C410" s="2"/>
     </row>
     <row r="411" spans="3:3" ht="14.25">
-      <c r="C411" s="9"/>
+      <c r="C411" s="2"/>
     </row>
     <row r="412" spans="3:3" ht="14.25">
-      <c r="C412" s="9"/>
+      <c r="C412" s="2"/>
     </row>
     <row r="413" spans="3:3" ht="14.25">
-      <c r="C413" s="9"/>
+      <c r="C413" s="2"/>
     </row>
     <row r="414" spans="3:3" ht="14.25">
-      <c r="C414" s="9"/>
+      <c r="C414" s="2"/>
     </row>
     <row r="415" spans="3:3" ht="14.25">
-      <c r="C415" s="9"/>
+      <c r="C415" s="2"/>
     </row>
     <row r="416" spans="3:3" ht="14.25">
-      <c r="C416" s="9"/>
+      <c r="C416" s="2"/>
     </row>
     <row r="417" spans="3:3" ht="14.25">
-      <c r="C417" s="9"/>
+      <c r="C417" s="2"/>
     </row>
     <row r="418" spans="3:3" ht="14.25">
-      <c r="C418" s="9"/>
+      <c r="C418" s="2"/>
     </row>
     <row r="419" spans="3:3" ht="14.25">
-      <c r="C419" s="9"/>
+      <c r="C419" s="2"/>
     </row>
     <row r="420" spans="3:3" ht="14.25">
-      <c r="C420" s="9"/>
+      <c r="C420" s="2"/>
     </row>
     <row r="421" spans="3:3" ht="14.25">
-      <c r="C421" s="9"/>
+      <c r="C421" s="2"/>
     </row>
     <row r="422" spans="3:3" ht="14.25">
-      <c r="C422" s="9"/>
+      <c r="C422" s="2"/>
     </row>
     <row r="423" spans="3:3" ht="14.25">
-      <c r="C423" s="9"/>
+      <c r="C423" s="2"/>
     </row>
     <row r="424" spans="3:3" ht="14.25">
-      <c r="C424" s="9"/>
+      <c r="C424" s="2"/>
     </row>
     <row r="425" spans="3:3" ht="14.25">
-      <c r="C425" s="9"/>
+      <c r="C425" s="2"/>
     </row>
     <row r="426" spans="3:3" ht="14.25">
-      <c r="C426" s="9"/>
+      <c r="C426" s="2"/>
     </row>
     <row r="427" spans="3:3" ht="14.25">
-      <c r="C427" s="9"/>
+      <c r="C427" s="2"/>
     </row>
     <row r="428" spans="3:3" ht="14.25">
-      <c r="C428" s="9"/>
+      <c r="C428" s="2"/>
     </row>
     <row r="429" spans="3:3" ht="14.25">
-      <c r="C429" s="9"/>
+      <c r="C429" s="2"/>
     </row>
     <row r="430" spans="3:3" ht="14.25">
-      <c r="C430" s="9"/>
+      <c r="C430" s="2"/>
     </row>
     <row r="431" spans="3:3" ht="14.25">
-      <c r="C431" s="9"/>
+      <c r="C431" s="2"/>
     </row>
     <row r="432" spans="3:3" ht="14.25">
-      <c r="C432" s="9"/>
+      <c r="C432" s="2"/>
     </row>
     <row r="433" spans="3:3" ht="14.25">
-      <c r="C433" s="9"/>
+      <c r="C433" s="2"/>
     </row>
     <row r="434" spans="3:3" ht="14.25">
-      <c r="C434" s="9"/>
+      <c r="C434" s="2"/>
     </row>
     <row r="435" spans="3:3" ht="14.25">
-      <c r="C435" s="9"/>
+      <c r="C435" s="2"/>
     </row>
     <row r="436" spans="3:3" ht="14.25">
-      <c r="C436" s="9"/>
+      <c r="C436" s="2"/>
     </row>
     <row r="437" spans="3:3" ht="14.25">
-      <c r="C437" s="9"/>
+      <c r="C437" s="2"/>
     </row>
     <row r="438" spans="3:3" ht="14.25">
-      <c r="C438" s="9"/>
+      <c r="C438" s="2"/>
     </row>
     <row r="439" spans="3:3" ht="14.25">
-      <c r="C439" s="9"/>
+      <c r="C439" s="2"/>
     </row>
     <row r="440" spans="3:3" ht="14.25">
-      <c r="C440" s="9"/>
+      <c r="C440" s="2"/>
     </row>
     <row r="441" spans="3:3" ht="14.25">
-      <c r="C441" s="9"/>
+      <c r="C441" s="2"/>
     </row>
     <row r="442" spans="3:3" ht="14.25">
-      <c r="C442" s="9"/>
+      <c r="C442" s="2"/>
     </row>
     <row r="443" spans="3:3" ht="14.25">
-      <c r="C443" s="9"/>
+      <c r="C443" s="2"/>
     </row>
     <row r="444" spans="3:3" ht="14.25">
-      <c r="C444" s="9"/>
+      <c r="C444" s="2"/>
     </row>
     <row r="445" spans="3:3" ht="14.25">
-      <c r="C445" s="9"/>
+      <c r="C445" s="2"/>
     </row>
     <row r="446" spans="3:3" ht="14.25">
-      <c r="C446" s="9"/>
+      <c r="C446" s="2"/>
     </row>
     <row r="447" spans="3:3" ht="14.25">
-      <c r="C447" s="9"/>
+      <c r="C447" s="2"/>
     </row>
     <row r="448" spans="3:3" ht="14.25">
-      <c r="C448" s="9"/>
+      <c r="C448" s="2"/>
     </row>
     <row r="449" spans="3:3" ht="14.25">
-      <c r="C449" s="9"/>
+      <c r="C449" s="2"/>
     </row>
     <row r="450" spans="3:3" ht="14.25">
-      <c r="C450" s="9"/>
+      <c r="C450" s="2"/>
     </row>
     <row r="451" spans="3:3" ht="14.25">
-      <c r="C451" s="9"/>
+      <c r="C451" s="2"/>
     </row>
     <row r="452" spans="3:3" ht="14.25">
-      <c r="C452" s="9"/>
+      <c r="C452" s="2"/>
     </row>
     <row r="453" spans="3:3" ht="14.25">
-      <c r="C453" s="9"/>
+      <c r="C453" s="2"/>
     </row>
     <row r="454" spans="3:3" ht="14.25">
-      <c r="C454" s="9"/>
+      <c r="C454" s="2"/>
     </row>
     <row r="455" spans="3:3" ht="14.25">
-      <c r="C455" s="9"/>
+      <c r="C455" s="2"/>
     </row>
     <row r="456" spans="3:3" ht="14.25">
-      <c r="C456" s="9"/>
+      <c r="C456" s="2"/>
     </row>
     <row r="457" spans="3:3" ht="14.25">
-      <c r="C457" s="9"/>
+      <c r="C457" s="2"/>
     </row>
     <row r="458" spans="3:3" ht="14.25">
-      <c r="C458" s="9"/>
+      <c r="C458" s="2"/>
     </row>
     <row r="459" spans="3:3" ht="14.25">
-      <c r="C459" s="9"/>
+      <c r="C459" s="2"/>
     </row>
     <row r="460" spans="3:3" ht="14.25">
-      <c r="C460" s="9"/>
+      <c r="C460" s="2"/>
     </row>
     <row r="461" spans="3:3" ht="14.25">
-      <c r="C461" s="9"/>
+      <c r="C461" s="2"/>
     </row>
     <row r="462" spans="3:3" ht="14.25">
-      <c r="C462" s="9"/>
+      <c r="C462" s="2"/>
     </row>
     <row r="463" spans="3:3" ht="14.25">
-      <c r="C463" s="9"/>
+      <c r="C463" s="2"/>
     </row>
     <row r="464" spans="3:3" ht="14.25">
-      <c r="C464" s="9"/>
+      <c r="C464" s="2"/>
     </row>
     <row r="465" spans="3:3" ht="14.25">
-      <c r="C465" s="9"/>
+      <c r="C465" s="2"/>
     </row>
     <row r="466" spans="3:3" ht="14.25">
-      <c r="C466" s="9"/>
+      <c r="C466" s="2"/>
     </row>
     <row r="467" spans="3:3" ht="14.25">
-      <c r="C467" s="9"/>
+      <c r="C467" s="2"/>
     </row>
     <row r="468" spans="3:3" ht="14.25">
-      <c r="C468" s="9"/>
+      <c r="C468" s="2"/>
     </row>
     <row r="469" spans="3:3" ht="14.25">
-      <c r="C469" s="9"/>
+      <c r="C469" s="2"/>
     </row>
     <row r="470" spans="3:3" ht="14.25">
-      <c r="C470" s="9"/>
+      <c r="C470" s="2"/>
     </row>
     <row r="471" spans="3:3" ht="14.25">
-      <c r="C471" s="9"/>
+      <c r="C471" s="2"/>
     </row>
     <row r="472" spans="3:3" ht="14.25">
-      <c r="C472" s="9"/>
+      <c r="C472" s="2"/>
     </row>
     <row r="473" spans="3:3" ht="14.25">
-      <c r="C473" s="9"/>
+      <c r="C473" s="2"/>
     </row>
     <row r="474" spans="3:3" ht="14.25">
-      <c r="C474" s="9"/>
+      <c r="C474" s="2"/>
     </row>
     <row r="475" spans="3:3" ht="14.25">
-      <c r="C475" s="9"/>
+      <c r="C475" s="2"/>
     </row>
     <row r="476" spans="3:3" ht="14.25">
-      <c r="C476" s="9"/>
+      <c r="C476" s="2"/>
     </row>
     <row r="477" spans="3:3" ht="14.25">
-      <c r="C477" s="9"/>
+      <c r="C477" s="2"/>
     </row>
     <row r="478" spans="3:3" ht="14.25">
-      <c r="C478" s="9"/>
+      <c r="C478" s="2"/>
     </row>
     <row r="479" spans="3:3" ht="14.25">
-      <c r="C479" s="9"/>
+      <c r="C479" s="2"/>
     </row>
     <row r="480" spans="3:3" ht="14.25">
-      <c r="C480" s="9"/>
+      <c r="C480" s="2"/>
     </row>
     <row r="481" spans="3:3" ht="14.25">
-      <c r="C481" s="9"/>
+      <c r="C481" s="2"/>
     </row>
     <row r="482" spans="3:3" ht="14.25">
-      <c r="C482" s="9"/>
+      <c r="C482" s="2"/>
     </row>
     <row r="483" spans="3:3" ht="14.25">
-      <c r="C483" s="9"/>
+      <c r="C483" s="2"/>
     </row>
     <row r="484" spans="3:3" ht="14.25">
-      <c r="C484" s="9"/>
+      <c r="C484" s="2"/>
     </row>
     <row r="485" spans="3:3" ht="14.25">
-      <c r="C485" s="9"/>
+      <c r="C485" s="2"/>
     </row>
     <row r="486" spans="3:3" ht="14.25">
-      <c r="C486" s="9"/>
+      <c r="C486" s="2"/>
     </row>
     <row r="487" spans="3:3" ht="14.25">
-      <c r="C487" s="9"/>
+      <c r="C487" s="2"/>
     </row>
     <row r="488" spans="3:3" ht="14.25">
-      <c r="C488" s="9"/>
+      <c r="C488" s="2"/>
     </row>
     <row r="489" spans="3:3" ht="14.25">
-      <c r="C489" s="9"/>
+      <c r="C489" s="2"/>
     </row>
     <row r="490" spans="3:3" ht="14.25">
-      <c r="C490" s="9"/>
+      <c r="C490" s="2"/>
     </row>
     <row r="491" spans="3:3" ht="14.25">
-      <c r="C491" s="9"/>
+      <c r="C491" s="2"/>
     </row>
     <row r="492" spans="3:3" ht="14.25">
-      <c r="C492" s="9"/>
+      <c r="C492" s="2"/>
     </row>
     <row r="493" spans="3:3" ht="14.25">
-      <c r="C493" s="9"/>
+      <c r="C493" s="2"/>
     </row>
     <row r="494" spans="3:3" ht="14.25">
-      <c r="C494" s="9"/>
+      <c r="C494" s="2"/>
     </row>
     <row r="495" spans="3:3" ht="14.25">
-      <c r="C495" s="9"/>
+      <c r="C495" s="2"/>
     </row>
     <row r="496" spans="3:3" ht="14.25">
-      <c r="C496" s="9"/>
+      <c r="C496" s="2"/>
     </row>
     <row r="497" spans="3:3" ht="14.25">
-      <c r="C497" s="9"/>
+      <c r="C497" s="2"/>
     </row>
     <row r="498" spans="3:3" ht="14.25">
-      <c r="C498" s="9"/>
+      <c r="C498" s="2"/>
     </row>
     <row r="499" spans="3:3" ht="14.25">
-      <c r="C499" s="9"/>
+      <c r="C499" s="2"/>
     </row>
     <row r="500" spans="3:3" ht="14.25">
-      <c r="C500" s="9"/>
+      <c r="C500" s="2"/>
     </row>
     <row r="501" spans="3:3" ht="14.25">
-      <c r="C501" s="9"/>
+      <c r="C501" s="2"/>
     </row>
     <row r="502" spans="3:3" ht="14.25">
-      <c r="C502" s="9"/>
+      <c r="C502" s="2"/>
     </row>
     <row r="503" spans="3:3" ht="14.25">
-      <c r="C503" s="9"/>
+      <c r="C503" s="2"/>
     </row>
     <row r="504" spans="3:3" ht="14.25">
-      <c r="C504" s="9"/>
+      <c r="C504" s="2"/>
     </row>
     <row r="505" spans="3:3" ht="14.25">
-      <c r="C505" s="9"/>
+      <c r="C505" s="2"/>
     </row>
     <row r="506" spans="3:3" ht="14.25">
-      <c r="C506" s="9"/>
+      <c r="C506" s="2"/>
     </row>
     <row r="507" spans="3:3" ht="14.25">
-      <c r="C507" s="9"/>
+      <c r="C507" s="2"/>
     </row>
     <row r="508" spans="3:3" ht="14.25">
-      <c r="C508" s="9"/>
+      <c r="C508" s="2"/>
     </row>
     <row r="509" spans="3:3" ht="14.25">
-      <c r="C509" s="9"/>
+      <c r="C509" s="2"/>
     </row>
     <row r="510" spans="3:3" ht="14.25">
-      <c r="C510" s="9"/>
+      <c r="C510" s="2"/>
     </row>
     <row r="511" spans="3:3" ht="14.25">
-      <c r="C511" s="9"/>
+      <c r="C511" s="2"/>
     </row>
     <row r="512" spans="3:3" ht="14.25">
-      <c r="C512" s="9"/>
+      <c r="C512" s="2"/>
     </row>
     <row r="513" spans="3:3" ht="14.25">
-      <c r="C513" s="9"/>
+      <c r="C513" s="2"/>
     </row>
     <row r="514" spans="3:3" ht="14.25">
-      <c r="C514" s="9"/>
+      <c r="C514" s="2"/>
     </row>
     <row r="515" spans="3:3" ht="14.25">
-      <c r="C515" s="9"/>
+      <c r="C515" s="2"/>
     </row>
     <row r="516" spans="3:3" ht="14.25">
-      <c r="C516" s="9"/>
+      <c r="C516" s="2"/>
     </row>
     <row r="517" spans="3:3" ht="14.25">
-      <c r="C517" s="9"/>
+      <c r="C517" s="2"/>
     </row>
     <row r="518" spans="3:3" ht="14.25">
-      <c r="C518" s="9"/>
+      <c r="C518" s="2"/>
     </row>
     <row r="519" spans="3:3" ht="14.25">
-      <c r="C519" s="9"/>
+      <c r="C519" s="2"/>
     </row>
     <row r="520" spans="3:3" ht="14.25">
-      <c r="C520" s="9"/>
+      <c r="C520" s="2"/>
     </row>
     <row r="521" spans="3:3" ht="14.25">
-      <c r="C521" s="9"/>
+      <c r="C521" s="2"/>
     </row>
     <row r="522" spans="3:3" ht="14.25">
-      <c r="C522" s="9"/>
+      <c r="C522" s="2"/>
     </row>
     <row r="523" spans="3:3" ht="14.25">
-      <c r="C523" s="9"/>
+      <c r="C523" s="2"/>
     </row>
     <row r="524" spans="3:3" ht="14.25">
-      <c r="C524" s="9"/>
+      <c r="C524" s="2"/>
     </row>
     <row r="525" spans="3:3" ht="14.25">
-      <c r="C525" s="9"/>
+      <c r="C525" s="2"/>
     </row>
     <row r="526" spans="3:3" ht="14.25">
-      <c r="C526" s="9"/>
+      <c r="C526" s="2"/>
     </row>
     <row r="527" spans="3:3" ht="14.25">
-      <c r="C527" s="9"/>
+      <c r="C527" s="2"/>
     </row>
     <row r="528" spans="3:3" ht="14.25">
-      <c r="C528" s="9"/>
+      <c r="C528" s="2"/>
     </row>
     <row r="529" spans="3:3" ht="14.25">
-      <c r="C529" s="9"/>
+      <c r="C529" s="2"/>
     </row>
     <row r="530" spans="3:3" ht="14.25">
-      <c r="C530" s="9"/>
+      <c r="C530" s="2"/>
     </row>
     <row r="531" spans="3:3" ht="14.25">
-      <c r="C531" s="9"/>
+      <c r="C531" s="2"/>
     </row>
     <row r="532" spans="3:3" ht="14.25">
-      <c r="C532" s="9"/>
+      <c r="C532" s="2"/>
     </row>
     <row r="533" spans="3:3" ht="14.25">
-      <c r="C533" s="9"/>
+      <c r="C533" s="2"/>
     </row>
     <row r="534" spans="3:3" ht="14.25">
-      <c r="C534" s="9"/>
+      <c r="C534" s="2"/>
     </row>
     <row r="535" spans="3:3" ht="14.25">
-      <c r="C535" s="9"/>
+      <c r="C535" s="2"/>
     </row>
     <row r="536" spans="3:3" ht="14.25">
-      <c r="C536" s="9"/>
+      <c r="C536" s="2"/>
     </row>
     <row r="537" spans="3:3" ht="14.25">
-      <c r="C537" s="9"/>
+      <c r="C537" s="2"/>
     </row>
     <row r="538" spans="3:3" ht="14.25">
-      <c r="C538" s="9"/>
+      <c r="C538" s="2"/>
     </row>
     <row r="539" spans="3:3" ht="14.25">
-      <c r="C539" s="9"/>
+      <c r="C539" s="2"/>
     </row>
     <row r="540" spans="3:3" ht="14.25">
-      <c r="C540" s="9"/>
+      <c r="C540" s="2"/>
     </row>
     <row r="541" spans="3:3" ht="14.25">
-      <c r="C541" s="9"/>
+      <c r="C541" s="2"/>
     </row>
     <row r="542" spans="3:3" ht="14.25">
-      <c r="C542" s="9"/>
+      <c r="C542" s="2"/>
     </row>
     <row r="543" spans="3:3" ht="14.25">
-      <c r="C543" s="9"/>
+      <c r="C543" s="2"/>
     </row>
     <row r="544" spans="3:3" ht="14.25">
-      <c r="C544" s="9"/>
+      <c r="C544" s="2"/>
     </row>
     <row r="545" spans="3:3" ht="14.25">
-      <c r="C545" s="9"/>
+      <c r="C545" s="2"/>
     </row>
     <row r="546" spans="3:3" ht="14.25">
-      <c r="C546" s="9"/>
+      <c r="C546" s="2"/>
     </row>
     <row r="547" spans="3:3" ht="14.25">
-      <c r="C547" s="9"/>
+      <c r="C547" s="2"/>
     </row>
     <row r="548" spans="3:3" ht="14.25">
-      <c r="C548" s="9"/>
+      <c r="C548" s="2"/>
     </row>
     <row r="549" spans="3:3" ht="14.25">
-      <c r="C549" s="9"/>
+      <c r="C549" s="2"/>
     </row>
     <row r="550" spans="3:3" ht="14.25">
-      <c r="C550" s="9"/>
+      <c r="C550" s="2"/>
     </row>
     <row r="551" spans="3:3" ht="14.25">
-      <c r="C551" s="9"/>
+      <c r="C551" s="2"/>
     </row>
     <row r="552" spans="3:3" ht="14.25">
-      <c r="C552" s="9"/>
+      <c r="C552" s="2"/>
     </row>
     <row r="553" spans="3:3" ht="14.25">
-      <c r="C553" s="9"/>
+      <c r="C553" s="2"/>
     </row>
     <row r="554" spans="3:3" ht="14.25">
-      <c r="C554" s="9"/>
+      <c r="C554" s="2"/>
     </row>
     <row r="555" spans="3:3" ht="14.25">
-      <c r="C555" s="9"/>
+      <c r="C555" s="2"/>
     </row>
     <row r="556" spans="3:3" ht="14.25">
-      <c r="C556" s="9"/>
+      <c r="C556" s="2"/>
     </row>
     <row r="557" spans="3:3" ht="14.25">
-      <c r="C557" s="9"/>
+      <c r="C557" s="2"/>
     </row>
     <row r="558" spans="3:3" ht="14.25">
-      <c r="C558" s="9"/>
+      <c r="C558" s="2"/>
     </row>
     <row r="559" spans="3:3" ht="14.25">
-      <c r="C559" s="9"/>
+      <c r="C559" s="2"/>
     </row>
     <row r="560" spans="3:3" ht="14.25">
-      <c r="C560" s="9"/>
+      <c r="C560" s="2"/>
     </row>
     <row r="561" spans="3:3" ht="14.25">
-      <c r="C561" s="9"/>
+      <c r="C561" s="2"/>
     </row>
     <row r="562" spans="3:3" ht="14.25">
-      <c r="C562" s="9"/>
+      <c r="C562" s="2"/>
     </row>
     <row r="563" spans="3:3" ht="14.25">
-      <c r="C563" s="9"/>
+      <c r="C563" s="2"/>
     </row>
     <row r="564" spans="3:3" ht="14.25">
-      <c r="C564" s="9"/>
+      <c r="C564" s="2"/>
     </row>
     <row r="565" spans="3:3" ht="14.25">
-      <c r="C565" s="9"/>
+      <c r="C565" s="2"/>
     </row>
     <row r="566" spans="3:3" ht="14.25">
-      <c r="C566" s="9"/>
+      <c r="C566" s="2"/>
     </row>
     <row r="567" spans="3:3" ht="14.25">
-      <c r="C567" s="9"/>
+      <c r="C567" s="2"/>
     </row>
     <row r="568" spans="3:3" ht="14.25">
-      <c r="C568" s="9"/>
+      <c r="C568" s="2"/>
     </row>
     <row r="569" spans="3:3" ht="14.25">
-      <c r="C569" s="9"/>
+      <c r="C569" s="2"/>
     </row>
     <row r="570" spans="3:3" ht="14.25">
-      <c r="C570" s="9"/>
+      <c r="C570" s="2"/>
     </row>
     <row r="571" spans="3:3" ht="14.25">
-      <c r="C571" s="9"/>
+      <c r="C571" s="2"/>
     </row>
     <row r="572" spans="3:3" ht="14.25">
-      <c r="C572" s="9"/>
+      <c r="C572" s="2"/>
     </row>
     <row r="573" spans="3:3" ht="14.25">
-      <c r="C573" s="9"/>
+      <c r="C573" s="2"/>
     </row>
     <row r="574" spans="3:3" ht="14.25">
-      <c r="C574" s="9"/>
+      <c r="C574" s="2"/>
     </row>
     <row r="575" spans="3:3" ht="14.25">
-      <c r="C575" s="9"/>
+      <c r="C575" s="2"/>
     </row>
     <row r="576" spans="3:3" ht="14.25">
-      <c r="C576" s="9"/>
+      <c r="C576" s="2"/>
     </row>
     <row r="577" spans="3:3" ht="14.25">
-      <c r="C577" s="9"/>
+      <c r="C577" s="2"/>
     </row>
     <row r="578" spans="3:3" ht="14.25">
-      <c r="C578" s="9"/>
+      <c r="C578" s="2"/>
     </row>
     <row r="579" spans="3:3" ht="14.25">
-      <c r="C579" s="9"/>
+      <c r="C579" s="2"/>
     </row>
     <row r="580" spans="3:3" ht="14.25">
-      <c r="C580" s="9"/>
+      <c r="C580" s="2"/>
     </row>
     <row r="581" spans="3:3" ht="14.25">
-      <c r="C581" s="9"/>
+      <c r="C581" s="2"/>
     </row>
     <row r="582" spans="3:3" ht="14.25">
-      <c r="C582" s="9"/>
+      <c r="C582" s="2"/>
     </row>
     <row r="583" spans="3:3" ht="14.25">
-      <c r="C583" s="9"/>
+      <c r="C583" s="2"/>
     </row>
     <row r="584" spans="3:3" ht="14.25">
-      <c r="C584" s="9"/>
+      <c r="C584" s="2"/>
     </row>
     <row r="585" spans="3:3" ht="14.25">
-      <c r="C585" s="9"/>
+      <c r="C585" s="2"/>
     </row>
     <row r="586" spans="3:3" ht="14.25">
-      <c r="C586" s="9"/>
+      <c r="C586" s="2"/>
     </row>
     <row r="587" spans="3:3" ht="14.25">
-      <c r="C587" s="9"/>
+      <c r="C587" s="2"/>
     </row>
     <row r="588" spans="3:3" ht="14.25">
-      <c r="C588" s="9"/>
+      <c r="C588" s="2"/>
     </row>
     <row r="589" spans="3:3" ht="14.25">
-      <c r="C589" s="9"/>
+      <c r="C589" s="2"/>
     </row>
     <row r="590" spans="3:3" ht="14.25">
-      <c r="C590" s="9"/>
+      <c r="C590" s="2"/>
     </row>
     <row r="591" spans="3:3" ht="14.25">
-      <c r="C591" s="9"/>
+      <c r="C591" s="2"/>
     </row>
     <row r="592" spans="3:3" ht="14.25">
-      <c r="C592" s="9"/>
+      <c r="C592" s="2"/>
     </row>
     <row r="593" spans="3:3" ht="14.25">
-      <c r="C593" s="9"/>
+      <c r="C593" s="2"/>
     </row>
     <row r="594" spans="3:3" ht="14.25">
-      <c r="C594" s="9"/>
+      <c r="C594" s="2"/>
     </row>
     <row r="595" spans="3:3" ht="14.25">
-      <c r="C595" s="9"/>
+      <c r="C595" s="2"/>
     </row>
     <row r="596" spans="3:3" ht="14.25">
-      <c r="C596" s="9"/>
+      <c r="C596" s="2"/>
     </row>
     <row r="597" spans="3:3" ht="14.25">
-      <c r="C597" s="9"/>
+      <c r="C597" s="2"/>
     </row>
     <row r="598" spans="3:3" ht="14.25">
-      <c r="C598" s="9"/>
+      <c r="C598" s="2"/>
     </row>
     <row r="599" spans="3:3" ht="14.25">
-      <c r="C599" s="9"/>
+      <c r="C599" s="2"/>
     </row>
     <row r="600" spans="3:3" ht="14.25">
-      <c r="C600" s="9"/>
+      <c r="C600" s="2"/>
     </row>
     <row r="601" spans="3:3" ht="14.25">
-      <c r="C601" s="9"/>
+      <c r="C601" s="2"/>
     </row>
     <row r="602" spans="3:3" ht="14.25">
-      <c r="C602" s="9"/>
+      <c r="C602" s="2"/>
     </row>
     <row r="603" spans="3:3" ht="14.25">
-      <c r="C603" s="9"/>
+      <c r="C603" s="2"/>
     </row>
     <row r="604" spans="3:3" ht="14.25">
-      <c r="C604" s="9"/>
+      <c r="C604" s="2"/>
     </row>
     <row r="605" spans="3:3" ht="14.25">
-      <c r="C605" s="9"/>
+      <c r="C605" s="2"/>
     </row>
     <row r="606" spans="3:3" ht="14.25">
-      <c r="C606" s="9"/>
+      <c r="C606" s="2"/>
     </row>
     <row r="607" spans="3:3" ht="14.25">
-      <c r="C607" s="9"/>
+      <c r="C607" s="2"/>
     </row>
     <row r="608" spans="3:3" ht="14.25">
-      <c r="C608" s="9"/>
+      <c r="C608" s="2"/>
     </row>
     <row r="609" spans="3:3" ht="14.25">
-      <c r="C609" s="9"/>
+      <c r="C609" s="2"/>
     </row>
     <row r="610" spans="3:3" ht="14.25">
-      <c r="C610" s="9"/>
+      <c r="C610" s="2"/>
     </row>
     <row r="611" spans="3:3" ht="14.25">
-      <c r="C611" s="9"/>
+      <c r="C611" s="2"/>
     </row>
     <row r="612" spans="3:3" ht="14.25">
-      <c r="C612" s="9"/>
+      <c r="C612" s="2"/>
     </row>
     <row r="613" spans="3:3" ht="14.25">
-      <c r="C613" s="9"/>
+      <c r="C613" s="2"/>
     </row>
     <row r="614" spans="3:3" ht="14.25">
-      <c r="C614" s="9"/>
+      <c r="C614" s="2"/>
     </row>
     <row r="615" spans="3:3" ht="14.25">
-      <c r="C615" s="9"/>
+      <c r="C615" s="2"/>
     </row>
     <row r="616" spans="3:3" ht="14.25">
-      <c r="C616" s="9"/>
+      <c r="C616" s="2"/>
     </row>
     <row r="617" spans="3:3" ht="14.25">
-      <c r="C617" s="9"/>
+      <c r="C617" s="2"/>
     </row>
     <row r="618" spans="3:3" ht="14.25">
-      <c r="C618" s="9"/>
+      <c r="C618" s="2"/>
     </row>
     <row r="619" spans="3:3" ht="14.25">
-      <c r="C619" s="9"/>
+      <c r="C619" s="2"/>
     </row>
     <row r="620" spans="3:3" ht="14.25">
-      <c r="C620" s="9"/>
+      <c r="C620" s="2"/>
     </row>
     <row r="621" spans="3:3" ht="14.25">
-      <c r="C621" s="9"/>
+      <c r="C621" s="2"/>
     </row>
     <row r="622" spans="3:3" ht="14.25">
-      <c r="C622" s="9"/>
+      <c r="C622" s="2"/>
     </row>
     <row r="623" spans="3:3" ht="14.25">
-      <c r="C623" s="9"/>
+      <c r="C623" s="2"/>
     </row>
     <row r="624" spans="3:3" ht="14.25">
-      <c r="C624" s="9"/>
+      <c r="C624" s="2"/>
     </row>
     <row r="625" spans="3:3" ht="14.25">
-      <c r="C625" s="9"/>
+      <c r="C625" s="2"/>
     </row>
     <row r="626" spans="3:3" ht="14.25">
-      <c r="C626" s="9"/>
+      <c r="C626" s="2"/>
     </row>
     <row r="627" spans="3:3" ht="14.25">
-      <c r="C627" s="9"/>
+      <c r="C627" s="2"/>
     </row>
     <row r="628" spans="3:3" ht="14.25">
-      <c r="C628" s="9"/>
+      <c r="C628" s="2"/>
     </row>
     <row r="629" spans="3:3" ht="14.25">
-      <c r="C629" s="9"/>
+      <c r="C629" s="2"/>
     </row>
     <row r="630" spans="3:3" ht="14.25">
-      <c r="C630" s="9"/>
+      <c r="C630" s="2"/>
     </row>
     <row r="631" spans="3:3" ht="14.25">
-      <c r="C631" s="9"/>
+      <c r="C631" s="2"/>
     </row>
     <row r="632" spans="3:3" ht="14.25">
-      <c r="C632" s="9"/>
+      <c r="C632" s="2"/>
     </row>
     <row r="633" spans="3:3" ht="14.25">
-      <c r="C633" s="9"/>
+      <c r="C633" s="2"/>
     </row>
     <row r="634" spans="3:3" ht="14.25">
-      <c r="C634" s="9"/>
+      <c r="C634" s="2"/>
     </row>
     <row r="635" spans="3:3" ht="14.25">
-      <c r="C635" s="9"/>
+      <c r="C635" s="2"/>
     </row>
     <row r="636" spans="3:3" ht="14.25">
-      <c r="C636" s="9"/>
+      <c r="C636" s="2"/>
     </row>
     <row r="637" spans="3:3" ht="14.25">
-      <c r="C637" s="9"/>
+      <c r="C637" s="2"/>
     </row>
     <row r="638" spans="3:3" ht="14.25">
-      <c r="C638" s="9"/>
+      <c r="C638" s="2"/>
     </row>
     <row r="639" spans="3:3" ht="14.25">
-      <c r="C639" s="9"/>
+      <c r="C639" s="2"/>
     </row>
     <row r="640" spans="3:3" ht="14.25">
-      <c r="C640" s="9"/>
+      <c r="C640" s="2"/>
     </row>
     <row r="641" spans="3:3" ht="14.25">
-      <c r="C641" s="9"/>
+      <c r="C641" s="2"/>
     </row>
     <row r="642" spans="3:3" ht="14.25">
-      <c r="C642" s="9"/>
+      <c r="C642" s="2"/>
     </row>
     <row r="643" spans="3:3" ht="14.25">
-      <c r="C643" s="9"/>
+      <c r="C643" s="2"/>
     </row>
     <row r="644" spans="3:3" ht="14.25">
-      <c r="C644" s="9"/>
+      <c r="C644" s="2"/>
     </row>
     <row r="645" spans="3:3" ht="14.25">
-      <c r="C645" s="9"/>
+      <c r="C645" s="2"/>
     </row>
     <row r="646" spans="3:3" ht="14.25">
-      <c r="C646" s="9"/>
+      <c r="C646" s="2"/>
     </row>
     <row r="647" spans="3:3" ht="14.25">
-      <c r="C647" s="9"/>
+      <c r="C647" s="2"/>
     </row>
     <row r="648" spans="3:3" ht="14.25">
-      <c r="C648" s="9"/>
+      <c r="C648" s="2"/>
     </row>
     <row r="649" spans="3:3" ht="14.25">
-      <c r="C649" s="9"/>
+      <c r="C649" s="2"/>
     </row>
     <row r="650" spans="3:3" ht="14.25">
-      <c r="C650" s="9"/>
+      <c r="C650" s="2"/>
     </row>
     <row r="651" spans="3:3" ht="14.25">
-      <c r="C651" s="9"/>
+      <c r="C651" s="2"/>
     </row>
     <row r="652" spans="3:3" ht="14.25">
-      <c r="C652" s="9"/>
+      <c r="C652" s="2"/>
     </row>
     <row r="653" spans="3:3" ht="14.25">
-      <c r="C653" s="9"/>
+      <c r="C653" s="2"/>
     </row>
     <row r="654" spans="3:3" ht="14.25">
-      <c r="C654" s="9"/>
+      <c r="C654" s="2"/>
     </row>
     <row r="655" spans="3:3" ht="14.25">
-      <c r="C655" s="9"/>
+      <c r="C655" s="2"/>
     </row>
     <row r="656" spans="3:3" ht="14.25">
-      <c r="C656" s="9"/>
+      <c r="C656" s="2"/>
     </row>
     <row r="657" spans="3:3" ht="14.25">
-      <c r="C657" s="9"/>
+      <c r="C657" s="2"/>
     </row>
     <row r="658" spans="3:3" ht="14.25">
-      <c r="C658" s="9"/>
+      <c r="C658" s="2"/>
     </row>
     <row r="659" spans="3:3" ht="14.25">
-      <c r="C659" s="9"/>
+      <c r="C659" s="2"/>
     </row>
     <row r="660" spans="3:3" ht="14.25">
-      <c r="C660" s="9"/>
+      <c r="C660" s="2"/>
     </row>
     <row r="661" spans="3:3" ht="14.25">
-      <c r="C661" s="9"/>
+      <c r="C661" s="2"/>
     </row>
     <row r="662" spans="3:3" ht="14.25">
-      <c r="C662" s="9"/>
+      <c r="C662" s="2"/>
     </row>
     <row r="663" spans="3:3" ht="14.25">
-      <c r="C663" s="9"/>
+      <c r="C663" s="2"/>
     </row>
     <row r="664" spans="3:3" ht="14.25">
-      <c r="C664" s="9"/>
+      <c r="C664" s="2"/>
     </row>
     <row r="665" spans="3:3" ht="14.25">
-      <c r="C665" s="9"/>
+      <c r="C665" s="2"/>
     </row>
     <row r="666" spans="3:3" ht="14.25">
-      <c r="C666" s="9"/>
+      <c r="C666" s="2"/>
     </row>
     <row r="667" spans="3:3" ht="14.25">
-      <c r="C667" s="9"/>
+      <c r="C667" s="2"/>
     </row>
     <row r="668" spans="3:3" ht="14.25">
-      <c r="C668" s="9"/>
+      <c r="C668" s="2"/>
     </row>
     <row r="669" spans="3:3" ht="14.25">
-      <c r="C669" s="9"/>
+      <c r="C669" s="2"/>
     </row>
     <row r="670" spans="3:3" ht="14.25">
-      <c r="C670" s="9"/>
+      <c r="C670" s="2"/>
     </row>
     <row r="671" spans="3:3" ht="14.25">
-      <c r="C671" s="9"/>
+      <c r="C671" s="2"/>
     </row>
     <row r="672" spans="3:3" ht="14.25">
-      <c r="C672" s="9"/>
+      <c r="C672" s="2"/>
     </row>
     <row r="673" spans="3:3" ht="14.25">
-      <c r="C673" s="9"/>
+      <c r="C673" s="2"/>
     </row>
     <row r="674" spans="3:3" ht="14.25">
-      <c r="C674" s="9"/>
+      <c r="C674" s="2"/>
     </row>
     <row r="675" spans="3:3" ht="14.25">
-      <c r="C675" s="9"/>
+      <c r="C675" s="2"/>
     </row>
     <row r="676" spans="3:3" ht="14.25">
-      <c r="C676" s="9"/>
+      <c r="C676" s="2"/>
     </row>
     <row r="677" spans="3:3" ht="14.25">
-      <c r="C677" s="9"/>
+      <c r="C677" s="2"/>
     </row>
     <row r="678" spans="3:3" ht="14.25">
-      <c r="C678" s="9"/>
+      <c r="C678" s="2"/>
     </row>
     <row r="679" spans="3:3" ht="14.25">
-      <c r="C679" s="9"/>
+      <c r="C679" s="2"/>
     </row>
     <row r="680" spans="3:3" ht="14.25">
-      <c r="C680" s="9"/>
+      <c r="C680" s="2"/>
     </row>
     <row r="681" spans="3:3" ht="14.25">
-      <c r="C681" s="9"/>
+      <c r="C681" s="2"/>
     </row>
     <row r="682" spans="3:3" ht="14.25">
-      <c r="C682" s="9"/>
+      <c r="C682" s="2"/>
     </row>
     <row r="683" spans="3:3" ht="14.25">
-      <c r="C683" s="9"/>
+      <c r="C683" s="2"/>
     </row>
     <row r="684" spans="3:3" ht="14.25">
-      <c r="C684" s="9"/>
+      <c r="C684" s="2"/>
     </row>
     <row r="685" spans="3:3" ht="14.25">
-      <c r="C685" s="9"/>
+      <c r="C685" s="2"/>
     </row>
     <row r="686" spans="3:3" ht="14.25">
-      <c r="C686" s="9"/>
+      <c r="C686" s="2"/>
     </row>
     <row r="687" spans="3:3" ht="14.25">
-      <c r="C687" s="9"/>
+      <c r="C687" s="2"/>
     </row>
     <row r="688" spans="3:3" ht="14.25">
-      <c r="C688" s="9"/>
+      <c r="C688" s="2"/>
     </row>
     <row r="689" spans="3:3" ht="14.25">
-      <c r="C689" s="9"/>
+      <c r="C689" s="2"/>
     </row>
     <row r="690" spans="3:3" ht="14.25">
-      <c r="C690" s="9"/>
+      <c r="C690" s="2"/>
     </row>
     <row r="691" spans="3:3" ht="14.25">
-      <c r="C691" s="9"/>
+      <c r="C691" s="2"/>
     </row>
     <row r="692" spans="3:3" ht="14.25">
-      <c r="C692" s="9"/>
+      <c r="C692" s="2"/>
     </row>
     <row r="693" spans="3:3" ht="14.25">
-      <c r="C693" s="9"/>
+      <c r="C693" s="2"/>
     </row>
     <row r="694" spans="3:3" ht="14.25">
-      <c r="C694" s="9"/>
+      <c r="C694" s="2"/>
     </row>
     <row r="695" spans="3:3" ht="14.25">
-      <c r="C695" s="9"/>
+      <c r="C695" s="2"/>
     </row>
     <row r="696" spans="3:3" ht="14.25">
-      <c r="C696" s="9"/>
+      <c r="C696" s="2"/>
     </row>
     <row r="697" spans="3:3" ht="14.25">
-      <c r="C697" s="9"/>
+      <c r="C697" s="2"/>
     </row>
     <row r="698" spans="3:3" ht="14.25">
-      <c r="C698" s="9"/>
+      <c r="C698" s="2"/>
     </row>
     <row r="699" spans="3:3" ht="14.25">
-      <c r="C699" s="9"/>
+      <c r="C699" s="2"/>
     </row>
     <row r="700" spans="3:3" ht="14.25">
-      <c r="C700" s="9"/>
+      <c r="C700" s="2"/>
     </row>
     <row r="701" spans="3:3" ht="14.25">
-      <c r="C701" s="9"/>
+      <c r="C701" s="2"/>
     </row>
     <row r="702" spans="3:3" ht="14.25">
-      <c r="C702" s="9"/>
+      <c r="C702" s="2"/>
     </row>
     <row r="703" spans="3:3" ht="14.25">
-      <c r="C703" s="9"/>
+      <c r="C703" s="2"/>
     </row>
     <row r="704" spans="3:3" ht="14.25">
-      <c r="C704" s="9"/>
+      <c r="C704" s="2"/>
     </row>
     <row r="705" spans="3:3" ht="14.25">
-      <c r="C705" s="9"/>
+      <c r="C705" s="2"/>
     </row>
     <row r="706" spans="3:3" ht="14.25">
-      <c r="C706" s="9"/>
+      <c r="C706" s="2"/>
     </row>
     <row r="707" spans="3:3" ht="14.25">
-      <c r="C707" s="9"/>
+      <c r="C707" s="2"/>
     </row>
     <row r="708" spans="3:3" ht="14.25">
-      <c r="C708" s="9"/>
+      <c r="C708" s="2"/>
     </row>
     <row r="709" spans="3:3" ht="14.25">
-      <c r="C709" s="9"/>
+      <c r="C709" s="2"/>
     </row>
     <row r="710" spans="3:3" ht="14.25">
-      <c r="C710" s="9"/>
+      <c r="C710" s="2"/>
     </row>
     <row r="711" spans="3:3" ht="14.25">
-      <c r="C711" s="9"/>
+      <c r="C711" s="2"/>
     </row>
     <row r="712" spans="3:3" ht="14.25">
-      <c r="C712" s="9"/>
+      <c r="C712" s="2"/>
     </row>
     <row r="713" spans="3:3" ht="14.25">
-      <c r="C713" s="9"/>
+      <c r="C713" s="2"/>
     </row>
     <row r="714" spans="3:3" ht="14.25">
-      <c r="C714" s="9"/>
+      <c r="C714" s="2"/>
     </row>
     <row r="715" spans="3:3" ht="14.25">
-      <c r="C715" s="9"/>
+      <c r="C715" s="2"/>
     </row>
     <row r="716" spans="3:3" ht="14.25">
-      <c r="C716" s="9"/>
+      <c r="C716" s="2"/>
     </row>
     <row r="717" spans="3:3" ht="14.25">
-      <c r="C717" s="9"/>
+      <c r="C717" s="2"/>
     </row>
     <row r="718" spans="3:3" ht="14.25">
-      <c r="C718" s="9"/>
+      <c r="C718" s="2"/>
     </row>
     <row r="719" spans="3:3" ht="14.25">
-      <c r="C719" s="9"/>
+      <c r="C719" s="2"/>
     </row>
     <row r="720" spans="3:3" ht="14.25">
-      <c r="C720" s="9"/>
+      <c r="C720" s="2"/>
     </row>
     <row r="721" spans="3:3" ht="14.25">
-      <c r="C721" s="9"/>
+      <c r="C721" s="2"/>
     </row>
     <row r="722" spans="3:3" ht="14.25">
-      <c r="C722" s="9"/>
+      <c r="C722" s="2"/>
     </row>
     <row r="723" spans="3:3" ht="14.25">
-      <c r="C723" s="9"/>
+      <c r="C723" s="2"/>
     </row>
     <row r="724" spans="3:3" ht="14.25">
-      <c r="C724" s="9"/>
+      <c r="C724" s="2"/>
     </row>
     <row r="725" spans="3:3" ht="14.25">
-      <c r="C725" s="9"/>
+      <c r="C725" s="2"/>
     </row>
     <row r="726" spans="3:3" ht="14.25">
-      <c r="C726" s="9"/>
+      <c r="C726" s="2"/>
     </row>
     <row r="727" spans="3:3" ht="14.25">
-      <c r="C727" s="9"/>
+      <c r="C727" s="2"/>
     </row>
     <row r="728" spans="3:3" ht="14.25">
-      <c r="C728" s="9"/>
+      <c r="C728" s="2"/>
     </row>
     <row r="729" spans="3:3" ht="14.25">
-      <c r="C729" s="9"/>
+      <c r="C729" s="2"/>
     </row>
     <row r="730" spans="3:3" ht="14.25">
-      <c r="C730" s="9"/>
+      <c r="C730" s="2"/>
     </row>
     <row r="731" spans="3:3" ht="14.25">
-      <c r="C731" s="9"/>
+      <c r="C731" s="2"/>
     </row>
     <row r="732" spans="3:3" ht="14.25">
-      <c r="C732" s="9"/>
+      <c r="C732" s="2"/>
     </row>
     <row r="733" spans="3:3" ht="14.25">
-      <c r="C733" s="9"/>
+      <c r="C733" s="2"/>
     </row>
     <row r="734" spans="3:3" ht="14.25">
-      <c r="C734" s="9"/>
+      <c r="C734" s="2"/>
     </row>
     <row r="735" spans="3:3" ht="14.25">
-      <c r="C735" s="9"/>
+      <c r="C735" s="2"/>
     </row>
     <row r="736" spans="3:3" ht="14.25">
-      <c r="C736" s="9"/>
+      <c r="C736" s="2"/>
     </row>
     <row r="737" spans="3:3" ht="14.25">
-      <c r="C737" s="9"/>
+      <c r="C737" s="2"/>
     </row>
     <row r="738" spans="3:3" ht="14.25">
-      <c r="C738" s="9"/>
+      <c r="C738" s="2"/>
     </row>
     <row r="739" spans="3:3" ht="14.25">
-      <c r="C739" s="9"/>
+      <c r="C739" s="2"/>
     </row>
     <row r="740" spans="3:3" ht="14.25">
-      <c r="C740" s="9"/>
+      <c r="C740" s="2"/>
     </row>
     <row r="741" spans="3:3" ht="14.25">
-      <c r="C741" s="9"/>
+      <c r="C741" s="2"/>
     </row>
     <row r="742" spans="3:3" ht="14.25">
-      <c r="C742" s="9"/>
+      <c r="C742" s="2"/>
     </row>
     <row r="743" spans="3:3" ht="14.25">
-      <c r="C743" s="9"/>
+      <c r="C743" s="2"/>
     </row>
     <row r="744" spans="3:3" ht="14.25">
-      <c r="C744" s="9"/>
+      <c r="C744" s="2"/>
     </row>
     <row r="745" spans="3:3" ht="14.25">
-      <c r="C745" s="9"/>
+      <c r="C745" s="2"/>
     </row>
     <row r="746" spans="3:3" ht="14.25">
-      <c r="C746" s="9"/>
+      <c r="C746" s="2"/>
     </row>
     <row r="747" spans="3:3" ht="14.25">
-      <c r="C747" s="9"/>
+      <c r="C747" s="2"/>
     </row>
     <row r="748" spans="3:3" ht="14.25">
-      <c r="C748" s="9"/>
+      <c r="C748" s="2"/>
     </row>
     <row r="749" spans="3:3" ht="14.25">
-      <c r="C749" s="9"/>
+      <c r="C749" s="2"/>
     </row>
     <row r="750" spans="3:3" ht="14.25">
-      <c r="C750" s="9"/>
+      <c r="C750" s="2"/>
     </row>
     <row r="751" spans="3:3" ht="14.25">
-      <c r="C751" s="9"/>
+      <c r="C751" s="2"/>
     </row>
     <row r="752" spans="3:3" ht="14.25">
-      <c r="C752" s="9"/>
+      <c r="C752" s="2"/>
     </row>
     <row r="753" spans="3:3" ht="14.25">
-      <c r="C753" s="9"/>
+      <c r="C753" s="2"/>
     </row>
     <row r="754" spans="3:3" ht="14.25">
-      <c r="C754" s="9"/>
+      <c r="C754" s="2"/>
     </row>
     <row r="755" spans="3:3" ht="14.25">
-      <c r="C755" s="9"/>
+      <c r="C755" s="2"/>
     </row>
     <row r="756" spans="3:3" ht="14.25">
-      <c r="C756" s="9"/>
+      <c r="C756" s="2"/>
     </row>
     <row r="757" spans="3:3" ht="14.25">
-      <c r="C757" s="9"/>
+      <c r="C757" s="2"/>
     </row>
     <row r="758" spans="3:3" ht="14.25">
-      <c r="C758" s="9"/>
+      <c r="C758" s="2"/>
     </row>
     <row r="759" spans="3:3" ht="14.25">
-      <c r="C759" s="9"/>
+      <c r="C759" s="2"/>
     </row>
     <row r="760" spans="3:3" ht="14.25">
-      <c r="C760" s="9"/>
+      <c r="C760" s="2"/>
     </row>
     <row r="761" spans="3:3" ht="14.25">
-      <c r="C761" s="9"/>
+      <c r="C761" s="2"/>
     </row>
     <row r="762" spans="3:3" ht="14.25">
-      <c r="C762" s="9"/>
+      <c r="C762" s="2"/>
     </row>
     <row r="763" spans="3:3" ht="14.25">
-      <c r="C763" s="9"/>
+      <c r="C763" s="2"/>
     </row>
     <row r="764" spans="3:3" ht="14.25">
-      <c r="C764" s="9"/>
+      <c r="C764" s="2"/>
     </row>
     <row r="765" spans="3:3" ht="14.25">
-      <c r="C765" s="9"/>
+      <c r="C765" s="2"/>
     </row>
     <row r="766" spans="3:3" ht="14.25">
-      <c r="C766" s="9"/>
+      <c r="C766" s="2"/>
     </row>
     <row r="767" spans="3:3" ht="14.25">
-      <c r="C767" s="9"/>
+      <c r="C767" s="2"/>
     </row>
     <row r="768" spans="3:3" ht="14.25">
-      <c r="C768" s="9"/>
+      <c r="C768" s="2"/>
     </row>
     <row r="769" spans="3:3" ht="14.25">
-      <c r="C769" s="9"/>
+      <c r="C769" s="2"/>
     </row>
     <row r="770" spans="3:3" ht="14.25">
-      <c r="C770" s="9"/>
+      <c r="C770" s="2"/>
     </row>
     <row r="771" spans="3:3" ht="14.25">
-      <c r="C771" s="9"/>
+      <c r="C771" s="2"/>
     </row>
     <row r="772" spans="3:3" ht="14.25">
-      <c r="C772" s="9"/>
+      <c r="C772" s="2"/>
     </row>
     <row r="773" spans="3:3" ht="14.25">
-      <c r="C773" s="9"/>
+      <c r="C773" s="2"/>
     </row>
     <row r="774" spans="3:3" ht="14.25">
-      <c r="C774" s="9"/>
+      <c r="C774" s="2"/>
     </row>
     <row r="775" spans="3:3" ht="14.25">
-      <c r="C775" s="9"/>
+      <c r="C775" s="2"/>
     </row>
     <row r="776" spans="3:3" ht="14.25">
-      <c r="C776" s="9"/>
+      <c r="C776" s="2"/>
     </row>
     <row r="777" spans="3:3" ht="14.25">
-      <c r="C777" s="9"/>
+      <c r="C777" s="2"/>
     </row>
     <row r="778" spans="3:3" ht="14.25">
-      <c r="C778" s="9"/>
+      <c r="C778" s="2"/>
     </row>
     <row r="779" spans="3:3" ht="14.25">
-      <c r="C779" s="9"/>
+      <c r="C779" s="2"/>
     </row>
     <row r="780" spans="3:3" ht="14.25">
-      <c r="C780" s="9"/>
+      <c r="C780" s="2"/>
     </row>
     <row r="781" spans="3:3" ht="14.25">
-      <c r="C781" s="9"/>
+      <c r="C781" s="2"/>
     </row>
     <row r="782" spans="3:3" ht="14.25">
-      <c r="C782" s="9"/>
+      <c r="C782" s="2"/>
     </row>
     <row r="783" spans="3:3" ht="14.25">
-      <c r="C783" s="9"/>
+      <c r="C783" s="2"/>
     </row>
     <row r="784" spans="3:3" ht="14.25">
-      <c r="C784" s="9"/>
+      <c r="C784" s="2"/>
     </row>
     <row r="785" spans="3:3" ht="14.25">
-      <c r="C785" s="9"/>
+      <c r="C785" s="2"/>
     </row>
     <row r="786" spans="3:3" ht="14.25">
-      <c r="C786" s="9"/>
+      <c r="C786" s="2"/>
     </row>
     <row r="787" spans="3:3" ht="14.25">
-      <c r="C787" s="9"/>
+      <c r="C787" s="2"/>
     </row>
     <row r="788" spans="3:3" ht="14.25">
-      <c r="C788" s="9"/>
+      <c r="C788" s="2"/>
     </row>
     <row r="789" spans="3:3" ht="14.25">
-      <c r="C789" s="9"/>
+      <c r="C789" s="2"/>
     </row>
     <row r="790" spans="3:3" ht="14.25">
-      <c r="C790" s="9"/>
+      <c r="C790" s="2"/>
     </row>
     <row r="791" spans="3:3" ht="14.25">
-      <c r="C791" s="9"/>
+      <c r="C791" s="2"/>
     </row>
     <row r="792" spans="3:3" ht="14.25">
-      <c r="C792" s="9"/>
+      <c r="C792" s="2"/>
     </row>
     <row r="793" spans="3:3" ht="14.25">
-      <c r="C793" s="9"/>
+      <c r="C793" s="2"/>
     </row>
     <row r="794" spans="3:3" ht="14.25">
-      <c r="C794" s="9"/>
+      <c r="C794" s="2"/>
     </row>
     <row r="795" spans="3:3" ht="14.25">
-      <c r="C795" s="9"/>
+      <c r="C795" s="2"/>
     </row>
     <row r="796" spans="3:3" ht="14.25">
-      <c r="C796" s="9"/>
+      <c r="C796" s="2"/>
     </row>
     <row r="797" spans="3:3" ht="14.25">
-      <c r="C797" s="9"/>
+      <c r="C797" s="2"/>
     </row>
     <row r="798" spans="3:3" ht="14.25">
-      <c r="C798" s="9"/>
+      <c r="C798" s="2"/>
     </row>
     <row r="799" spans="3:3" ht="14.25">
-      <c r="C799" s="9"/>
+      <c r="C799" s="2"/>
     </row>
     <row r="800" spans="3:3" ht="14.25">
-      <c r="C800" s="9"/>
+      <c r="C800" s="2"/>
     </row>
     <row r="801" spans="3:3" ht="14.25">
-      <c r="C801" s="9"/>
+      <c r="C801" s="2"/>
     </row>
     <row r="802" spans="3:3" ht="14.25">
-      <c r="C802" s="9"/>
+      <c r="C802" s="2"/>
     </row>
     <row r="803" spans="3:3" ht="14.25">
-      <c r="C803" s="9"/>
+      <c r="C803" s="2"/>
     </row>
     <row r="804" spans="3:3" ht="14.25">
-      <c r="C804" s="9"/>
+      <c r="C804" s="2"/>
     </row>
     <row r="805" spans="3:3" ht="14.25">
-      <c r="C805" s="9"/>
+      <c r="C805" s="2"/>
     </row>
     <row r="806" spans="3:3" ht="14.25">
-      <c r="C806" s="9"/>
+      <c r="C806" s="2"/>
     </row>
     <row r="807" spans="3:3" ht="14.25">
-      <c r="C807" s="9"/>
+      <c r="C807" s="2"/>
     </row>
     <row r="808" spans="3:3" ht="14.25">
-      <c r="C808" s="9"/>
+      <c r="C808" s="2"/>
     </row>
     <row r="809" spans="3:3" ht="14.25">
-      <c r="C809" s="9"/>
+      <c r="C809" s="2"/>
     </row>
     <row r="810" spans="3:3" ht="14.25">
-      <c r="C810" s="9"/>
+      <c r="C810" s="2"/>
     </row>
     <row r="811" spans="3:3" ht="14.25">
-      <c r="C811" s="9"/>
+      <c r="C811" s="2"/>
     </row>
     <row r="812" spans="3:3" ht="14.25">
-      <c r="C812" s="9"/>
+      <c r="C812" s="2"/>
     </row>
     <row r="813" spans="3:3" ht="14.25">
-      <c r="C813" s="9"/>
+      <c r="C813" s="2"/>
     </row>
     <row r="814" spans="3:3" ht="14.25">
-      <c r="C814" s="9"/>
+      <c r="C814" s="2"/>
     </row>
     <row r="815" spans="3:3" ht="14.25">
-      <c r="C815" s="9"/>
+      <c r="C815" s="2"/>
     </row>
     <row r="816" spans="3:3" ht="14.25">
-      <c r="C816" s="9"/>
+      <c r="C816" s="2"/>
     </row>
     <row r="817" spans="3:3" ht="14.25">
-      <c r="C817" s="9"/>
+      <c r="C817" s="2"/>
     </row>
     <row r="818" spans="3:3" ht="14.25">
-      <c r="C818" s="9"/>
+      <c r="C818" s="2"/>
     </row>
     <row r="819" spans="3:3" ht="14.25">
-      <c r="C819" s="9"/>
+      <c r="C819" s="2"/>
     </row>
     <row r="820" spans="3:3" ht="14.25">
-      <c r="C820" s="9"/>
+      <c r="C820" s="2"/>
     </row>
     <row r="821" spans="3:3" ht="14.25">
-      <c r="C821" s="9"/>
+      <c r="C821" s="2"/>
     </row>
     <row r="822" spans="3:3" ht="14.25">
-      <c r="C822" s="9"/>
+      <c r="C822" s="2"/>
     </row>
     <row r="823" spans="3:3" ht="14.25">
-      <c r="C823" s="9"/>
+      <c r="C823" s="2"/>
     </row>
     <row r="824" spans="3:3" ht="14.25">
-      <c r="C824" s="9"/>
+      <c r="C824" s="2"/>
     </row>
     <row r="825" spans="3:3" ht="14.25">
-      <c r="C825" s="9"/>
+      <c r="C825" s="2"/>
     </row>
     <row r="826" spans="3:3" ht="14.25">
-      <c r="C826" s="9"/>
+      <c r="C826" s="2"/>
     </row>
     <row r="827" spans="3:3" ht="14.25">
-      <c r="C827" s="9"/>
+      <c r="C827" s="2"/>
     </row>
     <row r="828" spans="3:3" ht="14.25">
-      <c r="C828" s="9"/>
+      <c r="C828" s="2"/>
     </row>
     <row r="829" spans="3:3" ht="14.25">
-      <c r="C829" s="9"/>
+      <c r="C829" s="2"/>
     </row>
     <row r="830" spans="3:3" ht="14.25">
-      <c r="C830" s="9"/>
+      <c r="C830" s="2"/>
     </row>
     <row r="831" spans="3:3" ht="14.25">
-      <c r="C831" s="9"/>
+      <c r="C831" s="2"/>
     </row>
     <row r="832" spans="3:3" ht="14.25">
-      <c r="C832" s="9"/>
+      <c r="C832" s="2"/>
     </row>
     <row r="833" spans="3:3" ht="14.25">
-      <c r="C833" s="9"/>
+      <c r="C833" s="2"/>
     </row>
     <row r="834" spans="3:3" ht="14.25">
-      <c r="C834" s="9"/>
+      <c r="C834" s="2"/>
     </row>
     <row r="835" spans="3:3" ht="14.25">
-      <c r="C835" s="9"/>
+      <c r="C835" s="2"/>
     </row>
     <row r="836" spans="3:3" ht="14.25">
-      <c r="C836" s="9"/>
+      <c r="C836" s="2"/>
     </row>
     <row r="837" spans="3:3" ht="14.25">
-      <c r="C837" s="9"/>
+      <c r="C837" s="2"/>
     </row>
     <row r="838" spans="3:3" ht="14.25">
-      <c r="C838" s="9"/>
+      <c r="C838" s="2"/>
     </row>
     <row r="839" spans="3:3" ht="14.25">
-      <c r="C839" s="9"/>
+      <c r="C839" s="2"/>
     </row>
     <row r="840" spans="3:3" ht="14.25">
-      <c r="C840" s="9"/>
+      <c r="C840" s="2"/>
     </row>
     <row r="841" spans="3:3" ht="14.25">
-      <c r="C841" s="9"/>
+      <c r="C841" s="2"/>
     </row>
     <row r="842" spans="3:3" ht="14.25">
-      <c r="C842" s="9"/>
+      <c r="C842" s="2"/>
     </row>
     <row r="843" spans="3:3" ht="14.25">
-      <c r="C843" s="9"/>
+      <c r="C843" s="2"/>
     </row>
     <row r="844" spans="3:3" ht="14.25">
-      <c r="C844" s="9"/>
+      <c r="C844" s="2"/>
     </row>
     <row r="845" spans="3:3" ht="14.25">
-      <c r="C845" s="9"/>
+      <c r="C845" s="2"/>
     </row>
     <row r="846" spans="3:3" ht="14.25">
-      <c r="C846" s="9"/>
+      <c r="C846" s="2"/>
     </row>
     <row r="847" spans="3:3" ht="14.25">
-      <c r="C847" s="9"/>
+      <c r="C847" s="2"/>
     </row>
     <row r="848" spans="3:3" ht="14.25">
-      <c r="C848" s="9"/>
+      <c r="C848" s="2"/>
     </row>
     <row r="849" spans="3:3" ht="14.25">
-      <c r="C849" s="9"/>
+      <c r="C849" s="2"/>
     </row>
     <row r="850" spans="3:3" ht="14.25">
-      <c r="C850" s="9"/>
+      <c r="C850" s="2"/>
     </row>
     <row r="851" spans="3:3" ht="14.25">
-      <c r="C851" s="9"/>
+      <c r="C851" s="2"/>
     </row>
     <row r="852" spans="3:3" ht="14.25">
-      <c r="C852" s="9"/>
+      <c r="C852" s="2"/>
     </row>
     <row r="853" spans="3:3" ht="14.25">
-      <c r="C853" s="9"/>
+      <c r="C853" s="2"/>
     </row>
     <row r="854" spans="3:3" ht="14.25">
-      <c r="C854" s="9"/>
+      <c r="C854" s="2"/>
     </row>
     <row r="855" spans="3:3" ht="14.25">
-      <c r="C855" s="9"/>
+      <c r="C855" s="2"/>
     </row>
     <row r="856" spans="3:3" ht="14.25">
-      <c r="C856" s="9"/>
+      <c r="C856" s="2"/>
     </row>
     <row r="857" spans="3:3" ht="14.25">
-      <c r="C857" s="9"/>
+      <c r="C857" s="2"/>
     </row>
     <row r="858" spans="3:3" ht="14.25">
-      <c r="C858" s="9"/>
+      <c r="C858" s="2"/>
     </row>
     <row r="859" spans="3:3" ht="14.25">
-      <c r="C859" s="9"/>
+      <c r="C859" s="2"/>
     </row>
     <row r="860" spans="3:3" ht="14.25">
-      <c r="C860" s="9"/>
+      <c r="C860" s="2"/>
     </row>
     <row r="861" spans="3:3" ht="14.25">
-      <c r="C861" s="9"/>
+      <c r="C861" s="2"/>
     </row>
     <row r="862" spans="3:3" ht="14.25">
-      <c r="C862" s="9"/>
+      <c r="C862" s="2"/>
     </row>
     <row r="863" spans="3:3" ht="14.25">
-      <c r="C863" s="9"/>
+      <c r="C863" s="2"/>
     </row>
     <row r="864" spans="3:3" ht="14.25">
-      <c r="C864" s="9"/>
+      <c r="C864" s="2"/>
     </row>
     <row r="865" spans="3:3" ht="14.25">
-      <c r="C865" s="9"/>
+      <c r="C865" s="2"/>
     </row>
     <row r="866" spans="3:3" ht="14.25">
-      <c r="C866" s="9"/>
+      <c r="C866" s="2"/>
     </row>
     <row r="867" spans="3:3" ht="14.25">
-      <c r="C867" s="9"/>
+      <c r="C867" s="2"/>
     </row>
     <row r="868" spans="3:3" ht="14.25">
-      <c r="C868" s="9"/>
+      <c r="C868" s="2"/>
     </row>
     <row r="869" spans="3:3" ht="14.25">
-      <c r="C869" s="9"/>
+      <c r="C869" s="2"/>
     </row>
     <row r="870" spans="3:3" ht="14.25">
-      <c r="C870" s="9"/>
+      <c r="C870" s="2"/>
     </row>
     <row r="871" spans="3:3" ht="14.25">
-      <c r="C871" s="9"/>
+      <c r="C871" s="2"/>
     </row>
     <row r="872" spans="3:3" ht="14.25">
-      <c r="C872" s="9"/>
+      <c r="C872" s="2"/>
     </row>
     <row r="873" spans="3:3" ht="14.25">
-      <c r="C873" s="9"/>
+      <c r="C873" s="2"/>
     </row>
     <row r="874" spans="3:3" ht="14.25">
-      <c r="C874" s="9"/>
+      <c r="C874" s="2"/>
     </row>
     <row r="875" spans="3:3" ht="14.25">
-      <c r="C875" s="9"/>
+      <c r="C875" s="2"/>
     </row>
     <row r="876" spans="3:3" ht="14.25">
-      <c r="C876" s="9"/>
+      <c r="C876" s="2"/>
     </row>
     <row r="877" spans="3:3" ht="14.25">
-      <c r="C877" s="9"/>
+      <c r="C877" s="2"/>
     </row>
     <row r="878" spans="3:3" ht="14.25">
-      <c r="C878" s="9"/>
+      <c r="C878" s="2"/>
     </row>
     <row r="879" spans="3:3" ht="14.25">
-      <c r="C879" s="9"/>
+      <c r="C879" s="2"/>
     </row>
     <row r="880" spans="3:3" ht="14.25">
-      <c r="C880" s="9"/>
+      <c r="C880" s="2"/>
     </row>
     <row r="881" spans="3:3" ht="14.25">
-      <c r="C881" s="9"/>
+      <c r="C881" s="2"/>
     </row>
     <row r="882" spans="3:3" ht="14.25">
-      <c r="C882" s="9"/>
+      <c r="C882" s="2"/>
     </row>
     <row r="883" spans="3:3" ht="14.25">
-      <c r="C883" s="9"/>
+      <c r="C883" s="2"/>
     </row>
     <row r="884" spans="3:3" ht="14.25">
-      <c r="C884" s="9"/>
+      <c r="C884" s="2"/>
     </row>
     <row r="885" spans="3:3" ht="14.25">
-      <c r="C885" s="9"/>
+      <c r="C885" s="2"/>
     </row>
     <row r="886" spans="3:3" ht="14.25">
-      <c r="C886" s="9"/>
+      <c r="C886" s="2"/>
     </row>
     <row r="887" spans="3:3" ht="14.25">
-      <c r="C887" s="9"/>
+      <c r="C887" s="2"/>
     </row>
     <row r="888" spans="3:3" ht="14.25">
-      <c r="C888" s="9"/>
+      <c r="C888" s="2"/>
     </row>
     <row r="889" spans="3:3" ht="14.25">
-      <c r="C889" s="9"/>
+      <c r="C889" s="2"/>
     </row>
     <row r="890" spans="3:3" ht="14.25">
-      <c r="C890" s="9"/>
+      <c r="C890" s="2"/>
     </row>
     <row r="891" spans="3:3" ht="14.25">
-      <c r="C891" s="9"/>
+      <c r="C891" s="2"/>
     </row>
     <row r="892" spans="3:3" ht="14.25">
-      <c r="C892" s="9"/>
+      <c r="C892" s="2"/>
     </row>
     <row r="893" spans="3:3" ht="14.25">
-      <c r="C893" s="9"/>
+      <c r="C893" s="2"/>
     </row>
     <row r="894" spans="3:3" ht="14.25">
-      <c r="C894" s="9"/>
+      <c r="C894" s="2"/>
     </row>
     <row r="895" spans="3:3" ht="14.25">
-      <c r="C895" s="9"/>
+      <c r="C895" s="2"/>
     </row>
     <row r="896" spans="3:3" ht="14.25">
-      <c r="C896" s="9"/>
+      <c r="C896" s="2"/>
     </row>
     <row r="897" spans="3:3" ht="14.25">
-      <c r="C897" s="9"/>
+      <c r="C897" s="2"/>
     </row>
     <row r="898" spans="3:3" ht="14.25">
-      <c r="C898" s="9"/>
+      <c r="C898" s="2"/>
     </row>
     <row r="899" spans="3:3" ht="14.25">
-      <c r="C899" s="9"/>
+      <c r="C899" s="2"/>
     </row>
     <row r="900" spans="3:3" ht="14.25">
-      <c r="C900" s="9"/>
+      <c r="C900" s="2"/>
     </row>
     <row r="901" spans="3:3" ht="14.25">
-      <c r="C901" s="9"/>
+      <c r="C901" s="2"/>
     </row>
     <row r="902" spans="3:3" ht="14.25">
-      <c r="C902" s="9"/>
+      <c r="C902" s="2"/>
     </row>
     <row r="903" spans="3:3" ht="14.25">
-      <c r="C903" s="9"/>
+      <c r="C903" s="2"/>
     </row>
     <row r="904" spans="3:3" ht="14.25">
-      <c r="C904" s="9"/>
+      <c r="C904" s="2"/>
     </row>
     <row r="905" spans="3:3" ht="14.25">
-      <c r="C905" s="9"/>
+      <c r="C905" s="2"/>
     </row>
     <row r="906" spans="3:3" ht="14.25">
-      <c r="C906" s="9"/>
+      <c r="C906" s="2"/>
     </row>
     <row r="907" spans="3:3" ht="14.25">
-      <c r="C907" s="9"/>
+      <c r="C907" s="2"/>
     </row>
     <row r="908" spans="3:3" ht="14.25">
-      <c r="C908" s="9"/>
+      <c r="C908" s="2"/>
     </row>
     <row r="909" spans="3:3" ht="14.25">
-      <c r="C909" s="9"/>
+      <c r="C909" s="2"/>
     </row>
     <row r="910" spans="3:3" ht="14.25">
-      <c r="C910" s="9"/>
+      <c r="C910" s="2"/>
     </row>
     <row r="911" spans="3:3" ht="14.25">
-      <c r="C911" s="9"/>
+      <c r="C911" s="2"/>
     </row>
     <row r="912" spans="3:3" ht="14.25">
-      <c r="C912" s="9"/>
+      <c r="C912" s="2"/>
     </row>
     <row r="913" spans="3:3" ht="14.25">
-      <c r="C913" s="9"/>
+      <c r="C913" s="2"/>
     </row>
     <row r="914" spans="3:3" ht="14.25">
-      <c r="C914" s="9"/>
+      <c r="C914" s="2"/>
     </row>
     <row r="915" spans="3:3" ht="14.25">
-      <c r="C915" s="9"/>
+      <c r="C915" s="2"/>
     </row>
     <row r="916" spans="3:3" ht="14.25">
-      <c r="C916" s="9"/>
+      <c r="C916" s="2"/>
     </row>
     <row r="917" spans="3:3" ht="14.25">
-      <c r="C917" s="9"/>
+      <c r="C917" s="2"/>
     </row>
     <row r="918" spans="3:3" ht="14.25">
-      <c r="C918" s="9"/>
+      <c r="C918" s="2"/>
     </row>
     <row r="919" spans="3:3" ht="14.25">
-      <c r="C919" s="9"/>
+      <c r="C919" s="2"/>
     </row>
     <row r="920" spans="3:3" ht="14.25">
-      <c r="C920" s="9"/>
+      <c r="C920" s="2"/>
     </row>
     <row r="921" spans="3:3" ht="14.25">
-      <c r="C921" s="9"/>
+      <c r="C921" s="2"/>
     </row>
     <row r="922" spans="3:3" ht="14.25">
-      <c r="C922" s="9"/>
+      <c r="C922" s="2"/>
     </row>
     <row r="923" spans="3:3" ht="14.25">
-      <c r="C923" s="9"/>
+      <c r="C923" s="2"/>
     </row>
     <row r="924" spans="3:3" ht="14.25">
-      <c r="C924" s="9"/>
+      <c r="C924" s="2"/>
     </row>
     <row r="925" spans="3:3" ht="14.25">
-      <c r="C925" s="9"/>
+      <c r="C925" s="2"/>
     </row>
     <row r="926" spans="3:3" ht="14.25">
-      <c r="C926" s="9"/>
+      <c r="C926" s="2"/>
     </row>
     <row r="927" spans="3:3" ht="14.25">
-      <c r="C927" s="9"/>
+      <c r="C927" s="2"/>
     </row>
     <row r="928" spans="3:3" ht="14.25">
-      <c r="C928" s="9"/>
+      <c r="C928" s="2"/>
     </row>
     <row r="929" spans="3:3" ht="14.25">
-      <c r="C929" s="9"/>
+      <c r="C929" s="2"/>
     </row>
     <row r="930" spans="3:3" ht="14.25">
-      <c r="C930" s="9"/>
+      <c r="C930" s="2"/>
     </row>
     <row r="931" spans="3:3" ht="14.25">
-      <c r="C931" s="9"/>
+      <c r="C931" s="2"/>
     </row>
     <row r="932" spans="3:3" ht="14.25">
-      <c r="C932" s="9"/>
+      <c r="C932" s="2"/>
     </row>
     <row r="933" spans="3:3" ht="14.25">
-      <c r="C933" s="9"/>
+      <c r="C933" s="2"/>
     </row>
     <row r="934" spans="3:3" ht="14.25">
-      <c r="C934" s="9"/>
+      <c r="C934" s="2"/>
     </row>
     <row r="935" spans="3:3" ht="14.25">
-      <c r="C935" s="9"/>
+      <c r="C935" s="2"/>
     </row>
     <row r="936" spans="3:3" ht="14.25">
-      <c r="C936" s="9"/>
+      <c r="C936" s="2"/>
     </row>
     <row r="937" spans="3:3" ht="14.25">
-      <c r="C937" s="9"/>
+      <c r="C937" s="2"/>
     </row>
     <row r="938" spans="3:3" ht="14.25">
-      <c r="C938" s="9"/>
+      <c r="C938" s="2"/>
     </row>
     <row r="939" spans="3:3" ht="14.25">
-      <c r="C939" s="9"/>
+      <c r="C939" s="2"/>
     </row>
     <row r="940" spans="3:3" ht="14.25">
-      <c r="C940" s="9"/>
+      <c r="C940" s="2"/>
     </row>
     <row r="941" spans="3:3" ht="14.25">
-      <c r="C941" s="9"/>
+      <c r="C941" s="2"/>
     </row>
     <row r="942" spans="3:3" ht="14.25">
-      <c r="C942" s="9"/>
+      <c r="C942" s="2"/>
     </row>
     <row r="943" spans="3:3" ht="14.25">
-      <c r="C943" s="9"/>
+      <c r="C943" s="2"/>
     </row>
     <row r="944" spans="3:3" ht="14.25">
-      <c r="C944" s="9"/>
+      <c r="C944" s="2"/>
     </row>
     <row r="945" spans="3:3" ht="14.25">
-      <c r="C945" s="9"/>
+      <c r="C945" s="2"/>
     </row>
     <row r="946" spans="3:3" ht="14.25">
-      <c r="C946" s="9"/>
+      <c r="C946" s="2"/>
     </row>
     <row r="947" spans="3:3" ht="14.25">
-      <c r="C947" s="9"/>
+      <c r="C947" s="2"/>
     </row>
     <row r="948" spans="3:3" ht="14.25">
-      <c r="C948" s="9"/>
+      <c r="C948" s="2"/>
     </row>
     <row r="949" spans="3:3" ht="14.25">
-      <c r="C949" s="9"/>
+      <c r="C949" s="2"/>
     </row>
     <row r="950" spans="3:3" ht="14.25">
-      <c r="C950" s="9"/>
+      <c r="C950" s="2"/>
     </row>
     <row r="951" spans="3:3" ht="14.25">
-      <c r="C951" s="9"/>
+      <c r="C951" s="2"/>
     </row>
     <row r="952" spans="3:3" ht="14.25">
-      <c r="C952" s="9"/>
+      <c r="C952" s="2"/>
     </row>
     <row r="953" spans="3:3" ht="14.25">
-      <c r="C953" s="9"/>
+      <c r="C953" s="2"/>
     </row>
     <row r="954" spans="3:3" ht="14.25">
-      <c r="C954" s="9"/>
+      <c r="C954" s="2"/>
     </row>
     <row r="955" spans="3:3" ht="14.25">
-      <c r="C955" s="9"/>
+      <c r="C955" s="2"/>
     </row>
     <row r="956" spans="3:3" ht="14.25">
-      <c r="C956" s="9"/>
+      <c r="C956" s="2"/>
     </row>
     <row r="957" spans="3:3" ht="14.25">
-      <c r="C957" s="9"/>
+      <c r="C957" s="2"/>
     </row>
     <row r="958" spans="3:3" ht="14.25">
-      <c r="C958" s="9"/>
+      <c r="C958" s="2"/>
     </row>
     <row r="959" spans="3:3" ht="14.25">
-      <c r="C959" s="9"/>
+      <c r="C959" s="2"/>
     </row>
     <row r="960" spans="3:3" ht="14.25">
-      <c r="C960" s="9"/>
+      <c r="C960" s="2"/>
     </row>
     <row r="961" spans="3:3" ht="14.25">
-      <c r="C961" s="9"/>
+      <c r="C961" s="2"/>
     </row>
     <row r="962" spans="3:3" ht="14.25">
-      <c r="C962" s="9"/>
+      <c r="C962" s="2"/>
     </row>
     <row r="963" spans="3:3" ht="14.25">
-      <c r="C963" s="9"/>
+      <c r="C963" s="2"/>
     </row>
     <row r="964" spans="3:3" ht="14.25">
-      <c r="C964" s="9"/>
+      <c r="C964" s="2"/>
     </row>
     <row r="965" spans="3:3" ht="14.25">
-      <c r="C965" s="9"/>
+      <c r="C965" s="2"/>
     </row>
     <row r="966" spans="3:3" ht="14.25">
-      <c r="C966" s="9"/>
+      <c r="C966" s="2"/>
     </row>
     <row r="967" spans="3:3" ht="14.25">
-      <c r="C967" s="9"/>
+      <c r="C967" s="2"/>
     </row>
     <row r="968" spans="3:3" ht="14.25">
-      <c r="C968" s="9"/>
+      <c r="C968" s="2"/>
     </row>
     <row r="969" spans="3:3" ht="14.25">
-      <c r="C969" s="9"/>
+      <c r="C969" s="2"/>
     </row>
     <row r="970" spans="3:3" ht="14.25">
-      <c r="C970" s="9"/>
+      <c r="C970" s="2"/>
     </row>
     <row r="971" spans="3:3" ht="14.25">
-      <c r="C971" s="9"/>
+      <c r="C971" s="2"/>
     </row>
     <row r="972" spans="3:3" ht="14.25">
-      <c r="C972" s="9"/>
+      <c r="C972" s="2"/>
     </row>
     <row r="973" spans="3:3" ht="14.25">
-      <c r="C973" s="9"/>
+      <c r="C973" s="2"/>
     </row>
     <row r="974" spans="3:3" ht="14.25">
-      <c r="C974" s="9"/>
+      <c r="C974" s="2"/>
     </row>
     <row r="975" spans="3:3" ht="14.25">
-      <c r="C975" s="9"/>
+      <c r="C975" s="2"/>
     </row>
     <row r="976" spans="3:3" ht="14.25">
-      <c r="C976" s="9"/>
+      <c r="C976" s="2"/>
     </row>
     <row r="977" spans="3:3" ht="14.25">
-      <c r="C977" s="9"/>
+      <c r="C977" s="2"/>
     </row>
     <row r="978" spans="3:3" ht="14.25">
-      <c r="C978" s="9"/>
+      <c r="C978" s="2"/>
     </row>
     <row r="979" spans="3:3" ht="14.25">
-      <c r="C979" s="9"/>
+      <c r="C979" s="2"/>
     </row>
     <row r="980" spans="3:3" ht="14.25">
-      <c r="C980" s="9"/>
+      <c r="C980" s="2"/>
     </row>
     <row r="981" spans="3:3" ht="14.25">
-      <c r="C981" s="9"/>
+      <c r="C981" s="2"/>
     </row>
     <row r="982" spans="3:3" ht="14.25">
-      <c r="C982" s="9"/>
+      <c r="C982" s="2"/>
     </row>
     <row r="983" spans="3:3" ht="14.25">
-      <c r="C983" s="9"/>
+      <c r="C983" s="2"/>
     </row>
     <row r="984" spans="3:3" ht="14.25">
-      <c r="C984" s="9"/>
+      <c r="C984" s="2"/>
     </row>
     <row r="985" spans="3:3" ht="14.25">
-      <c r="C985" s="9"/>
+      <c r="C985" s="2"/>
     </row>
     <row r="986" spans="3:3" ht="14.25">
-      <c r="C986" s="9"/>
+      <c r="C986" s="2"/>
     </row>
     <row r="987" spans="3:3" ht="14.25">
-      <c r="C987" s="9"/>
+      <c r="C987" s="2"/>
     </row>
     <row r="988" spans="3:3" ht="14.25">
-      <c r="C988" s="9"/>
+      <c r="C988" s="2"/>
     </row>
     <row r="989" spans="3:3" ht="14.25">
-      <c r="C989" s="9"/>
+      <c r="C989" s="2"/>
     </row>
     <row r="990" spans="3:3" ht="14.25">
-      <c r="C990" s="9"/>
+      <c r="C990" s="2"/>
     </row>
     <row r="991" spans="3:3" ht="14.25">
-      <c r="C991" s="9"/>
+      <c r="C991" s="2"/>
     </row>
     <row r="992" spans="3:3" ht="14.25">
-      <c r="C992" s="9"/>
+      <c r="C992" s="2"/>
     </row>
     <row r="993" spans="3:3" ht="14.25">
-      <c r="C993" s="9"/>
+      <c r="C993" s="2"/>
     </row>
     <row r="994" spans="3:3" ht="14.25">
-      <c r="C994" s="9"/>
+      <c r="C994" s="2"/>
     </row>
     <row r="995" spans="3:3" ht="14.25">
-      <c r="C995" s="9"/>
+      <c r="C995" s="2"/>
     </row>
     <row r="996" spans="3:3" ht="14.25">
-      <c r="C996" s="9"/>
+      <c r="C996" s="2"/>
     </row>
     <row r="997" spans="3:3" ht="14.25">
-      <c r="C997" s="9"/>
+      <c r="C997" s="2"/>
     </row>
     <row r="998" spans="3:3" ht="14.25">
-      <c r="C998" s="9"/>
+      <c r="C998" s="2"/>
     </row>
     <row r="999" spans="3:3" ht="14.25">
-      <c r="C999" s="9"/>
+      <c r="C999" s="2"/>
     </row>
     <row r="1000" spans="3:3" ht="14.25">
-      <c r="C1000" s="9"/>
+      <c r="C1000" s="2"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -4906,5 +5654,6 @@
     <hyperlink ref="L22" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
   </hyperlinks>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
+  <pageSetup orientation="portrait" r:id="rId19"/>
 </worksheet>
 </file>
--- a/SplitBelt Studies.xlsx
+++ b/SplitBelt Studies.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/33ab2cc4ec646a75/Documents/GitHub/Treadmill/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="44" documentId="8_{9B8E492B-0E78-4C94-A44A-5323969E6F8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3C8DB6C4-18E7-481C-A2A5-A63C8B02414B}"/>
+  <xr:revisionPtr revIDLastSave="55" documentId="8_{9B8E492B-0E78-4C94-A44A-5323969E6F8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D02AF3EF-A3C3-4E40-897E-A23E0194379C}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="14400" windowHeight="15600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="292">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="298">
   <si>
     <t>SPLIT BELT PAPERS</t>
   </si>
@@ -753,6 +753,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">: used step symmetry index (left - right) where right leg was manipulated to be + 9% and left was -9%; adaptation in stp sym index was greater (~7%) in the instruction group than in the no instruction group (~ 4.5 %); no difference during the catch trial, but retuned to similar differences withh return of visual feedback (indicates a small similar sized aftereffect); </t>
@@ -773,6 +774,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>: learning, some deccy during the (continue walking as you had been), return to near symmetry during normal walking retenction, recovered most of learning during the walk as you did during learning block. verbal instructions and distorted visual feedback impact learning and aftereffects in split-belt walking. Distorted visual feedback results largely in explicit learning with some implicit</t>
@@ -959,12 +961,34 @@
   <si>
     <t>Associations between asymmetry and reactive balance control during split-belt walking</t>
   </si>
+  <si>
+    <t>increasing the gradient of energetic cost does not initiate adaptation in human walking</t>
+  </si>
+  <si>
+    <t>Simha, Wong, Selinger, Abram, Donelan</t>
+  </si>
+  <si>
+    <t>Roemmich, Leech, Conzalez, Bastian</t>
+  </si>
+  <si>
+    <t>Trading symmetry for energy cost during walking in healthy adults and persons post-stroke</t>
+  </si>
+  <si>
+    <t>tied belts: asymmetry was induced with instructions and targets on the treadmill - “walk so that your left leg is 3 targets ahead of the right”
+EXP 1: paired symmetry levels with specific tied belt speed (ex tied at 0.5 m/s; small left limp at 2 m/s; etc); treadmill controller changed the treadmill speed to the speed paired with the asymmetry used most in the prior 10 strides they were allowed to explore for 10 minutes (guided exploration for the first half) - then walked on controller for 5 minutes using their prefered combination
+9 of 12 participants chose to walk asymmetrically at a non preffered speed, which was at or near the minimum cost of transport
+EXP 2: people tend to walk set distances not set times, similar to exp 1 except that instead of walking 5 minutes participants walked on controller at preferred for 1km (distance shown on display) and asymetry / speed conditions were shuffled
+11 of 20 participants chose the low cost of transport combination</t>
+  </si>
+  <si>
+    <t>compared aftereffects between groups with implicitly distorted visual feedback, no feelback, and veridal feedback with instructions to see which generated more lasting after effects - seems like it might be the implicit visual feedback, but analysis and stats are very weird</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -986,15 +1010,24 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1002,6 +1035,7 @@
       <sz val="10"/>
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -1106,60 +1140,60 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -1167,6 +1201,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1387,7 +1424,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:P1000"/>
-  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3.5703125" style="9" customWidth="1"/>
     <col min="2" max="2" width="12.5703125" style="9"/>
@@ -1404,7 +1441,7 @@
     <col min="16" max="16384" width="12.5703125" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="25.5">
+    <row r="1" spans="1:16" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A1" s="1"/>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -1424,7 +1461,7 @@
       <c r="O1" s="1"/>
       <c r="P1" s="1"/>
     </row>
-    <row r="2" spans="1:16" ht="51.75">
+    <row r="2" spans="1:16" ht="51.75" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
       <c r="B2" s="13" t="s">
         <v>1</v>
@@ -1466,7 +1503,7 @@
       </c>
       <c r="P2" s="1"/>
     </row>
-    <row r="3" spans="1:16" ht="63.75">
+    <row r="3" spans="1:16" ht="63.75" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -1508,7 +1545,7 @@
       <c r="O3" s="1"/>
       <c r="P3" s="1"/>
     </row>
-    <row r="4" spans="1:16" ht="89.25">
+    <row r="4" spans="1:16" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A4" s="18">
         <v>2</v>
       </c>
@@ -1556,7 +1593,7 @@
       </c>
       <c r="P4" s="1"/>
     </row>
-    <row r="5" spans="1:16" ht="102">
+    <row r="5" spans="1:16" ht="102" x14ac:dyDescent="0.2">
       <c r="A5" s="18">
         <v>3</v>
       </c>
@@ -1598,7 +1635,7 @@
       <c r="O5" s="1"/>
       <c r="P5" s="1"/>
     </row>
-    <row r="6" spans="1:16" ht="76.5">
+    <row r="6" spans="1:16" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>4</v>
       </c>
@@ -1640,7 +1677,7 @@
       <c r="O6" s="1"/>
       <c r="P6" s="1"/>
     </row>
-    <row r="7" spans="1:16" ht="89.25">
+    <row r="7" spans="1:16" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>5</v>
       </c>
@@ -1688,7 +1725,7 @@
       </c>
       <c r="P7" s="1"/>
     </row>
-    <row r="8" spans="1:16" ht="140.25">
+    <row r="8" spans="1:16" ht="140.25" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <v>6</v>
       </c>
@@ -1734,7 +1771,7 @@
       <c r="O8" s="1"/>
       <c r="P8" s="1"/>
     </row>
-    <row r="9" spans="1:16" ht="114.75">
+    <row r="9" spans="1:16" ht="114.75" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <v>7</v>
       </c>
@@ -1780,7 +1817,7 @@
       <c r="O9" s="1"/>
       <c r="P9" s="1"/>
     </row>
-    <row r="10" spans="1:16" ht="42.75">
+    <row r="10" spans="1:16" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
         <v>8</v>
       </c>
@@ -1808,7 +1845,7 @@
       <c r="O10" s="1"/>
       <c r="P10" s="1"/>
     </row>
-    <row r="11" spans="1:16" ht="76.5">
+    <row r="11" spans="1:16" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
         <v>9</v>
       </c>
@@ -1854,7 +1891,7 @@
       </c>
       <c r="P11" s="1"/>
     </row>
-    <row r="12" spans="1:16" ht="293.25">
+    <row r="12" spans="1:16" ht="293.25" x14ac:dyDescent="0.2">
       <c r="A12" s="7">
         <v>10</v>
       </c>
@@ -1900,7 +1937,7 @@
       <c r="O12" s="1"/>
       <c r="P12" s="1"/>
     </row>
-    <row r="13" spans="1:16" ht="255">
+    <row r="13" spans="1:16" ht="255" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
         <v>11</v>
       </c>
@@ -1946,7 +1983,7 @@
       <c r="O13" s="1"/>
       <c r="P13" s="1"/>
     </row>
-    <row r="14" spans="1:16" ht="114.75">
+    <row r="14" spans="1:16" ht="114.75" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
         <v>12</v>
       </c>
@@ -1990,7 +2027,7 @@
       <c r="O14" s="1"/>
       <c r="P14" s="1"/>
     </row>
-    <row r="15" spans="1:16" ht="165.75">
+    <row r="15" spans="1:16" ht="165.75" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
         <v>13</v>
       </c>
@@ -2034,7 +2071,7 @@
       <c r="O15" s="1"/>
       <c r="P15" s="1"/>
     </row>
-    <row r="16" spans="1:16" ht="76.5">
+    <row r="16" spans="1:16" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
         <v>14</v>
       </c>
@@ -2062,7 +2099,7 @@
       <c r="O16" s="1"/>
       <c r="P16" s="1"/>
     </row>
-    <row r="17" spans="1:16" ht="153">
+    <row r="17" spans="1:16" ht="153" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
         <v>15</v>
       </c>
@@ -2108,7 +2145,7 @@
       <c r="O17" s="1"/>
       <c r="P17" s="1"/>
     </row>
-    <row r="18" spans="1:16" ht="63.75">
+    <row r="18" spans="1:16" ht="63.75" x14ac:dyDescent="0.2">
       <c r="A18" s="1">
         <v>16</v>
       </c>
@@ -2136,7 +2173,7 @@
       <c r="O18" s="1"/>
       <c r="P18" s="1"/>
     </row>
-    <row r="19" spans="1:16" ht="127.5">
+    <row r="19" spans="1:16" ht="127.5" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
         <v>17</v>
       </c>
@@ -2182,7 +2219,7 @@
       <c r="O19" s="1"/>
       <c r="P19" s="1"/>
     </row>
-    <row r="20" spans="1:16" ht="42.75">
+    <row r="20" spans="1:16" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A20" s="1">
         <v>18</v>
       </c>
@@ -2208,7 +2245,7 @@
       <c r="O20" s="1"/>
       <c r="P20" s="1"/>
     </row>
-    <row r="21" spans="1:16" ht="38.25">
+    <row r="21" spans="1:16" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
         <v>19</v>
       </c>
@@ -2233,7 +2270,7 @@
       <c r="L21" s="1"/>
       <c r="M21" s="1"/>
     </row>
-    <row r="22" spans="1:16" ht="89.25">
+    <row r="22" spans="1:16" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A22" s="1">
         <v>20</v>
       </c>
@@ -2275,7 +2312,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="23" spans="1:16" ht="63.75">
+    <row r="23" spans="1:16" ht="63.75" x14ac:dyDescent="0.2">
       <c r="A23" s="1">
         <v>21</v>
       </c>
@@ -2298,7 +2335,7 @@
       <c r="L23" s="1"/>
       <c r="M23" s="1"/>
     </row>
-    <row r="24" spans="1:16" ht="102">
+    <row r="24" spans="1:16" ht="102" x14ac:dyDescent="0.2">
       <c r="A24" s="1"/>
       <c r="B24" s="1" t="s">
         <v>184</v>
@@ -2334,7 +2371,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="25" spans="1:16" ht="89.25">
+    <row r="25" spans="1:16" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A25" s="1"/>
       <c r="B25" s="1" t="s">
         <v>193</v>
@@ -2367,7 +2404,7 @@
       <c r="L25" s="1"/>
       <c r="M25" s="1"/>
     </row>
-    <row r="26" spans="1:16" ht="191.25">
+    <row r="26" spans="1:16" ht="191.25" x14ac:dyDescent="0.2">
       <c r="A26" s="1"/>
       <c r="B26" s="1" t="s">
         <v>194</v>
@@ -2402,7 +2439,7 @@
       <c r="L26" s="1"/>
       <c r="M26" s="1"/>
     </row>
-    <row r="27" spans="1:16" ht="42.75">
+    <row r="27" spans="1:16" ht="42.75" x14ac:dyDescent="0.2">
       <c r="B27" s="9" t="s">
         <v>196</v>
       </c>
@@ -2416,7 +2453,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="28" spans="1:16" ht="242.25">
+    <row r="28" spans="1:16" ht="242.25" x14ac:dyDescent="0.2">
       <c r="B28" s="9" t="s">
         <v>197</v>
       </c>
@@ -2439,7 +2476,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="29" spans="1:16" ht="42.75">
+    <row r="29" spans="1:16" ht="42.75" x14ac:dyDescent="0.2">
       <c r="B29" s="9" t="s">
         <v>199</v>
       </c>
@@ -2453,7 +2490,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="30" spans="1:16" ht="57">
+    <row r="30" spans="1:16" ht="57" x14ac:dyDescent="0.2">
       <c r="B30" s="9" t="s">
         <v>201</v>
       </c>
@@ -2464,7 +2501,7 @@
         <v>2010</v>
       </c>
     </row>
-    <row r="31" spans="1:16" ht="51">
+    <row r="31" spans="1:16" ht="51" x14ac:dyDescent="0.2">
       <c r="B31" s="11" t="s">
         <v>203</v>
       </c>
@@ -2478,7 +2515,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="32" spans="1:16" ht="42.75">
+    <row r="32" spans="1:16" ht="42.75" x14ac:dyDescent="0.2">
       <c r="B32" s="11" t="s">
         <v>205</v>
       </c>
@@ -2489,7 +2526,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="33" spans="1:15" ht="57">
+    <row r="33" spans="1:15" ht="57" x14ac:dyDescent="0.2">
       <c r="B33" s="11" t="s">
         <v>207</v>
       </c>
@@ -2497,7 +2534,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="34" spans="1:15" ht="71.25">
+    <row r="34" spans="1:15" ht="71.25" x14ac:dyDescent="0.2">
       <c r="B34" s="11" t="s">
         <v>209</v>
       </c>
@@ -2508,7 +2545,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="35" spans="1:15" ht="57">
+    <row r="35" spans="1:15" ht="57" x14ac:dyDescent="0.2">
       <c r="B35" s="11" t="s">
         <v>211</v>
       </c>
@@ -2518,8 +2555,11 @@
       <c r="D35" s="9">
         <v>2022</v>
       </c>
-    </row>
-    <row r="36" spans="1:15" ht="51">
+      <c r="E35" s="9" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" ht="51" x14ac:dyDescent="0.2">
       <c r="B36" s="11" t="s">
         <v>213</v>
       </c>
@@ -2530,7 +2570,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="37" spans="1:15" ht="63.75">
+    <row r="37" spans="1:15" ht="63.75" x14ac:dyDescent="0.2">
       <c r="B37" s="11" t="s">
         <v>215</v>
       </c>
@@ -2541,7 +2581,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="38" spans="1:15" ht="89.25">
+    <row r="38" spans="1:15" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A38" s="19"/>
       <c r="B38" s="11" t="s">
         <v>217</v>
@@ -2562,7 +2602,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="39" spans="1:15" ht="71.25">
+    <row r="39" spans="1:15" ht="71.25" x14ac:dyDescent="0.2">
       <c r="B39" s="11" t="s">
         <v>219</v>
       </c>
@@ -2573,7 +2613,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="40" spans="1:15" ht="85.5">
+    <row r="40" spans="1:15" ht="85.5" x14ac:dyDescent="0.2">
       <c r="B40" s="11" t="s">
         <v>225</v>
       </c>
@@ -2587,7 +2627,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="41" spans="1:15" ht="85.5">
+    <row r="41" spans="1:15" ht="85.5" x14ac:dyDescent="0.2">
       <c r="B41" s="9" t="s">
         <v>239</v>
       </c>
@@ -2601,7 +2641,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="42" spans="1:15" ht="38.25">
+    <row r="42" spans="1:15" ht="38.25" x14ac:dyDescent="0.2">
       <c r="B42" s="11" t="s">
         <v>245</v>
       </c>
@@ -2618,7 +2658,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="43" spans="1:15" ht="42.75">
+    <row r="43" spans="1:15" ht="42.75" x14ac:dyDescent="0.2">
       <c r="B43" s="9" t="s">
         <v>251</v>
       </c>
@@ -2629,7 +2669,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="44" spans="1:15" ht="51">
+    <row r="44" spans="1:15" ht="51" x14ac:dyDescent="0.2">
       <c r="B44" s="9" t="s">
         <v>270</v>
       </c>
@@ -2643,7 +2683,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="45" spans="1:15" ht="28.5">
+    <row r="45" spans="1:15" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B45" s="9" t="s">
         <v>254</v>
       </c>
@@ -2654,7 +2694,7 @@
         <v>2011</v>
       </c>
     </row>
-    <row r="46" spans="1:15" ht="38.25">
+    <row r="46" spans="1:15" ht="38.25" x14ac:dyDescent="0.2">
       <c r="B46" s="9" t="s">
         <v>256</v>
       </c>
@@ -2665,7 +2705,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="47" spans="1:15" ht="38.25">
+    <row r="47" spans="1:15" ht="38.25" x14ac:dyDescent="0.2">
       <c r="B47" s="9" t="s">
         <v>258</v>
       </c>
@@ -2676,7 +2716,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="48" spans="1:15" ht="42.75">
+    <row r="48" spans="1:15" ht="42.75" x14ac:dyDescent="0.2">
       <c r="B48" s="9" t="s">
         <v>260</v>
       </c>
@@ -2687,7 +2727,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="49" spans="2:11" ht="57">
+    <row r="49" spans="2:11" ht="57" x14ac:dyDescent="0.2">
       <c r="B49" s="9" t="s">
         <v>266</v>
       </c>
@@ -2701,8 +2741,8 @@
         <v>268</v>
       </c>
     </row>
-    <row r="50" spans="2:11" ht="57">
-      <c r="B50" s="9" t="s">
+    <row r="50" spans="2:11" ht="57" x14ac:dyDescent="0.2">
+      <c r="B50" s="11" t="s">
         <v>271</v>
       </c>
       <c r="C50" s="2" t="s">
@@ -2715,7 +2755,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="51" spans="2:11" ht="204">
+    <row r="51" spans="2:11" ht="204" x14ac:dyDescent="0.2">
       <c r="B51" s="9" t="s">
         <v>275</v>
       </c>
@@ -2744,7 +2784,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="52" spans="2:11" ht="63.75">
+    <row r="52" spans="2:11" ht="63.75" x14ac:dyDescent="0.2">
       <c r="B52" s="9" t="s">
         <v>282</v>
       </c>
@@ -2759,7 +2799,7 @@
       </c>
       <c r="K52" s="20"/>
     </row>
-    <row r="53" spans="2:11" ht="76.5">
+    <row r="53" spans="2:11" ht="76.5" x14ac:dyDescent="0.2">
       <c r="B53" s="9" t="s">
         <v>285</v>
       </c>
@@ -2777,7 +2817,7 @@
       </c>
       <c r="K53" s="20"/>
     </row>
-    <row r="54" spans="2:11" ht="42.75">
+    <row r="54" spans="2:11" ht="42.75" x14ac:dyDescent="0.2">
       <c r="B54" s="9" t="s">
         <v>290</v>
       </c>
@@ -2789,2847 +2829,2866 @@
       </c>
       <c r="K54" s="20"/>
     </row>
-    <row r="55" spans="2:11" ht="14.25">
-      <c r="C55" s="2"/>
+    <row r="55" spans="2:11" ht="63.75" x14ac:dyDescent="0.2">
+      <c r="B55" s="9" t="s">
+        <v>293</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="D55" s="9">
+        <v>2021</v>
+      </c>
       <c r="K55" s="20"/>
     </row>
-    <row r="56" spans="2:11" ht="14.25">
-      <c r="C56" s="2"/>
+    <row r="56" spans="2:11" ht="216.75" x14ac:dyDescent="0.2">
+      <c r="B56" s="11" t="s">
+        <v>294</v>
+      </c>
+      <c r="C56" s="21" t="s">
+        <v>295</v>
+      </c>
+      <c r="D56" s="9">
+        <v>2019</v>
+      </c>
+      <c r="E56" s="11" t="s">
+        <v>296</v>
+      </c>
       <c r="K56" s="20"/>
     </row>
-    <row r="57" spans="2:11" ht="14.25">
+    <row r="57" spans="2:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C57" s="2"/>
       <c r="K57" s="20"/>
     </row>
-    <row r="58" spans="2:11" ht="14.25">
+    <row r="58" spans="2:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C58" s="2"/>
       <c r="K58" s="20"/>
     </row>
-    <row r="59" spans="2:11" ht="14.25">
+    <row r="59" spans="2:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C59" s="2"/>
       <c r="K59" s="20"/>
     </row>
-    <row r="60" spans="2:11" ht="14.25">
+    <row r="60" spans="2:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C60" s="2"/>
     </row>
-    <row r="61" spans="2:11" ht="14.25">
+    <row r="61" spans="2:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C61" s="2"/>
     </row>
-    <row r="62" spans="2:11" ht="14.25">
+    <row r="62" spans="2:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C62" s="2"/>
     </row>
-    <row r="63" spans="2:11" ht="14.25">
+    <row r="63" spans="2:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C63" s="2"/>
     </row>
-    <row r="64" spans="2:11" ht="14.25">
+    <row r="64" spans="2:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C64" s="2"/>
     </row>
-    <row r="65" spans="3:3" ht="14.25">
+    <row r="65" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C65" s="2"/>
     </row>
-    <row r="66" spans="3:3" ht="14.25">
+    <row r="66" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C66" s="2"/>
     </row>
-    <row r="67" spans="3:3" ht="14.25">
+    <row r="67" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C67" s="2"/>
     </row>
-    <row r="68" spans="3:3" ht="14.25">
+    <row r="68" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C68" s="2"/>
     </row>
-    <row r="69" spans="3:3" ht="14.25">
+    <row r="69" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C69" s="2"/>
     </row>
-    <row r="70" spans="3:3" ht="14.25">
+    <row r="70" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C70" s="2"/>
     </row>
-    <row r="71" spans="3:3" ht="14.25">
+    <row r="71" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C71" s="2"/>
     </row>
-    <row r="72" spans="3:3" ht="14.25">
+    <row r="72" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C72" s="2"/>
     </row>
-    <row r="73" spans="3:3" ht="14.25">
+    <row r="73" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C73" s="2"/>
     </row>
-    <row r="74" spans="3:3" ht="14.25">
+    <row r="74" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C74" s="2"/>
     </row>
-    <row r="75" spans="3:3" ht="14.25">
+    <row r="75" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C75" s="2"/>
     </row>
-    <row r="76" spans="3:3" ht="14.25">
+    <row r="76" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C76" s="2"/>
     </row>
-    <row r="77" spans="3:3" ht="14.25">
+    <row r="77" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C77" s="2"/>
     </row>
-    <row r="78" spans="3:3" ht="14.25">
+    <row r="78" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C78" s="2"/>
     </row>
-    <row r="79" spans="3:3" ht="14.25">
+    <row r="79" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C79" s="2"/>
     </row>
-    <row r="80" spans="3:3" ht="14.25">
+    <row r="80" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C80" s="2"/>
     </row>
-    <row r="81" spans="3:3" ht="14.25">
+    <row r="81" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C81" s="2"/>
     </row>
-    <row r="82" spans="3:3" ht="14.25">
+    <row r="82" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C82" s="2"/>
     </row>
-    <row r="83" spans="3:3" ht="14.25">
+    <row r="83" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C83" s="2"/>
     </row>
-    <row r="84" spans="3:3" ht="14.25">
+    <row r="84" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C84" s="2"/>
     </row>
-    <row r="85" spans="3:3" ht="14.25">
+    <row r="85" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C85" s="2"/>
     </row>
-    <row r="86" spans="3:3" ht="14.25">
+    <row r="86" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C86" s="2"/>
     </row>
-    <row r="87" spans="3:3" ht="14.25">
+    <row r="87" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C87" s="2"/>
     </row>
-    <row r="88" spans="3:3" ht="14.25">
+    <row r="88" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C88" s="2"/>
     </row>
-    <row r="89" spans="3:3" ht="14.25">
+    <row r="89" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C89" s="2"/>
     </row>
-    <row r="90" spans="3:3" ht="14.25">
+    <row r="90" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C90" s="2"/>
     </row>
-    <row r="91" spans="3:3" ht="14.25">
+    <row r="91" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C91" s="2"/>
     </row>
-    <row r="92" spans="3:3" ht="14.25">
+    <row r="92" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C92" s="2"/>
     </row>
-    <row r="93" spans="3:3" ht="14.25">
+    <row r="93" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C93" s="2"/>
     </row>
-    <row r="94" spans="3:3" ht="14.25">
+    <row r="94" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C94" s="2"/>
     </row>
-    <row r="95" spans="3:3" ht="14.25">
+    <row r="95" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C95" s="2"/>
     </row>
-    <row r="96" spans="3:3" ht="14.25">
+    <row r="96" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C96" s="2"/>
     </row>
-    <row r="97" spans="3:3" ht="14.25">
+    <row r="97" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C97" s="2"/>
     </row>
-    <row r="98" spans="3:3" ht="14.25">
+    <row r="98" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C98" s="2"/>
     </row>
-    <row r="99" spans="3:3" ht="14.25">
+    <row r="99" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C99" s="2"/>
     </row>
-    <row r="100" spans="3:3" ht="14.25">
+    <row r="100" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C100" s="2"/>
     </row>
-    <row r="101" spans="3:3" ht="14.25">
+    <row r="101" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C101" s="2"/>
     </row>
-    <row r="102" spans="3:3" ht="14.25">
+    <row r="102" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C102" s="2"/>
     </row>
-    <row r="103" spans="3:3" ht="14.25">
+    <row r="103" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C103" s="2"/>
     </row>
-    <row r="104" spans="3:3" ht="14.25">
+    <row r="104" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C104" s="2"/>
     </row>
-    <row r="105" spans="3:3" ht="14.25">
+    <row r="105" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C105" s="2"/>
     </row>
-    <row r="106" spans="3:3" ht="14.25">
+    <row r="106" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C106" s="2"/>
     </row>
-    <row r="107" spans="3:3" ht="14.25">
+    <row r="107" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C107" s="2"/>
     </row>
-    <row r="108" spans="3:3" ht="14.25">
+    <row r="108" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C108" s="2"/>
     </row>
-    <row r="109" spans="3:3" ht="14.25">
+    <row r="109" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C109" s="2"/>
     </row>
-    <row r="110" spans="3:3" ht="14.25">
+    <row r="110" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C110" s="2"/>
     </row>
-    <row r="111" spans="3:3" ht="14.25">
+    <row r="111" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C111" s="2"/>
     </row>
-    <row r="112" spans="3:3" ht="14.25">
+    <row r="112" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C112" s="2"/>
     </row>
-    <row r="113" spans="3:3" ht="14.25">
+    <row r="113" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C113" s="2"/>
     </row>
-    <row r="114" spans="3:3" ht="14.25">
+    <row r="114" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C114" s="2"/>
     </row>
-    <row r="115" spans="3:3" ht="14.25">
+    <row r="115" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C115" s="2"/>
     </row>
-    <row r="116" spans="3:3" ht="14.25">
+    <row r="116" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C116" s="2"/>
     </row>
-    <row r="117" spans="3:3" ht="14.25">
+    <row r="117" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C117" s="2"/>
     </row>
-    <row r="118" spans="3:3" ht="14.25">
+    <row r="118" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C118" s="2"/>
     </row>
-    <row r="119" spans="3:3" ht="14.25">
+    <row r="119" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C119" s="2"/>
     </row>
-    <row r="120" spans="3:3" ht="14.25">
+    <row r="120" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C120" s="2"/>
     </row>
-    <row r="121" spans="3:3" ht="14.25">
+    <row r="121" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C121" s="2"/>
     </row>
-    <row r="122" spans="3:3" ht="14.25">
+    <row r="122" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C122" s="2"/>
     </row>
-    <row r="123" spans="3:3" ht="14.25">
+    <row r="123" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C123" s="2"/>
     </row>
-    <row r="124" spans="3:3" ht="14.25">
+    <row r="124" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C124" s="2"/>
     </row>
-    <row r="125" spans="3:3" ht="14.25">
+    <row r="125" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C125" s="2"/>
     </row>
-    <row r="126" spans="3:3" ht="14.25">
+    <row r="126" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C126" s="2"/>
     </row>
-    <row r="127" spans="3:3" ht="14.25">
+    <row r="127" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C127" s="2"/>
     </row>
-    <row r="128" spans="3:3" ht="14.25">
+    <row r="128" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C128" s="2"/>
     </row>
-    <row r="129" spans="3:3" ht="14.25">
+    <row r="129" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C129" s="2"/>
     </row>
-    <row r="130" spans="3:3" ht="14.25">
+    <row r="130" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C130" s="2"/>
     </row>
-    <row r="131" spans="3:3" ht="14.25">
+    <row r="131" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C131" s="2"/>
     </row>
-    <row r="132" spans="3:3" ht="14.25">
+    <row r="132" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C132" s="2"/>
     </row>
-    <row r="133" spans="3:3" ht="14.25">
+    <row r="133" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C133" s="2"/>
     </row>
-    <row r="134" spans="3:3" ht="14.25">
+    <row r="134" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C134" s="2"/>
     </row>
-    <row r="135" spans="3:3" ht="14.25">
+    <row r="135" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C135" s="2"/>
     </row>
-    <row r="136" spans="3:3" ht="14.25">
+    <row r="136" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C136" s="2"/>
     </row>
-    <row r="137" spans="3:3" ht="14.25">
+    <row r="137" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C137" s="2"/>
     </row>
-    <row r="138" spans="3:3" ht="14.25">
+    <row r="138" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C138" s="2"/>
     </row>
-    <row r="139" spans="3:3" ht="14.25">
+    <row r="139" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C139" s="2"/>
     </row>
-    <row r="140" spans="3:3" ht="14.25">
+    <row r="140" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C140" s="2"/>
     </row>
-    <row r="141" spans="3:3" ht="14.25">
+    <row r="141" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C141" s="2"/>
     </row>
-    <row r="142" spans="3:3" ht="14.25">
+    <row r="142" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C142" s="2"/>
     </row>
-    <row r="143" spans="3:3" ht="14.25">
+    <row r="143" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C143" s="2"/>
     </row>
-    <row r="144" spans="3:3" ht="14.25">
+    <row r="144" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C144" s="2"/>
     </row>
-    <row r="145" spans="3:3" ht="14.25">
+    <row r="145" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C145" s="2"/>
     </row>
-    <row r="146" spans="3:3" ht="14.25">
+    <row r="146" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C146" s="2"/>
     </row>
-    <row r="147" spans="3:3" ht="14.25">
+    <row r="147" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C147" s="2"/>
     </row>
-    <row r="148" spans="3:3" ht="14.25">
+    <row r="148" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C148" s="2"/>
     </row>
-    <row r="149" spans="3:3" ht="14.25">
+    <row r="149" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C149" s="2"/>
     </row>
-    <row r="150" spans="3:3" ht="14.25">
+    <row r="150" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C150" s="2"/>
     </row>
-    <row r="151" spans="3:3" ht="14.25">
+    <row r="151" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C151" s="2"/>
     </row>
-    <row r="152" spans="3:3" ht="14.25">
+    <row r="152" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C152" s="2"/>
     </row>
-    <row r="153" spans="3:3" ht="14.25">
+    <row r="153" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C153" s="2"/>
     </row>
-    <row r="154" spans="3:3" ht="14.25">
+    <row r="154" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C154" s="2"/>
     </row>
-    <row r="155" spans="3:3" ht="14.25">
+    <row r="155" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C155" s="2"/>
     </row>
-    <row r="156" spans="3:3" ht="14.25">
+    <row r="156" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C156" s="2"/>
     </row>
-    <row r="157" spans="3:3" ht="14.25">
+    <row r="157" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C157" s="2"/>
     </row>
-    <row r="158" spans="3:3" ht="14.25">
+    <row r="158" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C158" s="2"/>
     </row>
-    <row r="159" spans="3:3" ht="14.25">
+    <row r="159" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C159" s="2"/>
     </row>
-    <row r="160" spans="3:3" ht="14.25">
+    <row r="160" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C160" s="2"/>
     </row>
-    <row r="161" spans="3:3" ht="14.25">
+    <row r="161" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C161" s="2"/>
     </row>
-    <row r="162" spans="3:3" ht="14.25">
+    <row r="162" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C162" s="2"/>
     </row>
-    <row r="163" spans="3:3" ht="14.25">
+    <row r="163" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C163" s="2"/>
     </row>
-    <row r="164" spans="3:3" ht="14.25">
+    <row r="164" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C164" s="2"/>
     </row>
-    <row r="165" spans="3:3" ht="14.25">
+    <row r="165" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C165" s="2"/>
     </row>
-    <row r="166" spans="3:3" ht="14.25">
+    <row r="166" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C166" s="2"/>
     </row>
-    <row r="167" spans="3:3" ht="14.25">
+    <row r="167" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C167" s="2"/>
     </row>
-    <row r="168" spans="3:3" ht="14.25">
+    <row r="168" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C168" s="2"/>
     </row>
-    <row r="169" spans="3:3" ht="14.25">
+    <row r="169" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C169" s="2"/>
     </row>
-    <row r="170" spans="3:3" ht="14.25">
+    <row r="170" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C170" s="2"/>
     </row>
-    <row r="171" spans="3:3" ht="14.25">
+    <row r="171" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C171" s="2"/>
     </row>
-    <row r="172" spans="3:3" ht="14.25">
+    <row r="172" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C172" s="2"/>
     </row>
-    <row r="173" spans="3:3" ht="14.25">
+    <row r="173" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C173" s="2"/>
     </row>
-    <row r="174" spans="3:3" ht="14.25">
+    <row r="174" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C174" s="2"/>
     </row>
-    <row r="175" spans="3:3" ht="14.25">
+    <row r="175" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C175" s="2"/>
     </row>
-    <row r="176" spans="3:3" ht="14.25">
+    <row r="176" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C176" s="2"/>
     </row>
-    <row r="177" spans="3:3" ht="14.25">
+    <row r="177" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C177" s="2"/>
     </row>
-    <row r="178" spans="3:3" ht="14.25">
+    <row r="178" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C178" s="2"/>
     </row>
-    <row r="179" spans="3:3" ht="14.25">
+    <row r="179" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C179" s="2"/>
     </row>
-    <row r="180" spans="3:3" ht="14.25">
+    <row r="180" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C180" s="2"/>
     </row>
-    <row r="181" spans="3:3" ht="14.25">
+    <row r="181" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C181" s="2"/>
     </row>
-    <row r="182" spans="3:3" ht="14.25">
+    <row r="182" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C182" s="2"/>
     </row>
-    <row r="183" spans="3:3" ht="14.25">
+    <row r="183" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C183" s="2"/>
     </row>
-    <row r="184" spans="3:3" ht="14.25">
+    <row r="184" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C184" s="2"/>
     </row>
-    <row r="185" spans="3:3" ht="14.25">
+    <row r="185" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C185" s="2"/>
     </row>
-    <row r="186" spans="3:3" ht="14.25">
+    <row r="186" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C186" s="2"/>
     </row>
-    <row r="187" spans="3:3" ht="14.25">
+    <row r="187" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C187" s="2"/>
     </row>
-    <row r="188" spans="3:3" ht="14.25">
+    <row r="188" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C188" s="2"/>
     </row>
-    <row r="189" spans="3:3" ht="14.25">
+    <row r="189" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C189" s="2"/>
     </row>
-    <row r="190" spans="3:3" ht="14.25">
+    <row r="190" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C190" s="2"/>
     </row>
-    <row r="191" spans="3:3" ht="14.25">
+    <row r="191" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C191" s="2"/>
     </row>
-    <row r="192" spans="3:3" ht="14.25">
+    <row r="192" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C192" s="2"/>
     </row>
-    <row r="193" spans="3:3" ht="14.25">
+    <row r="193" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C193" s="2"/>
     </row>
-    <row r="194" spans="3:3" ht="14.25">
+    <row r="194" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C194" s="2"/>
     </row>
-    <row r="195" spans="3:3" ht="14.25">
+    <row r="195" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C195" s="2"/>
     </row>
-    <row r="196" spans="3:3" ht="14.25">
+    <row r="196" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C196" s="2"/>
     </row>
-    <row r="197" spans="3:3" ht="14.25">
+    <row r="197" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C197" s="2"/>
     </row>
-    <row r="198" spans="3:3" ht="14.25">
+    <row r="198" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C198" s="2"/>
     </row>
-    <row r="199" spans="3:3" ht="14.25">
+    <row r="199" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C199" s="2"/>
     </row>
-    <row r="200" spans="3:3" ht="14.25">
+    <row r="200" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C200" s="2"/>
     </row>
-    <row r="201" spans="3:3" ht="14.25">
+    <row r="201" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C201" s="2"/>
     </row>
-    <row r="202" spans="3:3" ht="14.25">
+    <row r="202" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C202" s="2"/>
     </row>
-    <row r="203" spans="3:3" ht="14.25">
+    <row r="203" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C203" s="2"/>
     </row>
-    <row r="204" spans="3:3" ht="14.25">
+    <row r="204" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C204" s="2"/>
     </row>
-    <row r="205" spans="3:3" ht="14.25">
+    <row r="205" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C205" s="2"/>
     </row>
-    <row r="206" spans="3:3" ht="14.25">
+    <row r="206" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C206" s="2"/>
     </row>
-    <row r="207" spans="3:3" ht="14.25">
+    <row r="207" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C207" s="2"/>
     </row>
-    <row r="208" spans="3:3" ht="14.25">
+    <row r="208" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C208" s="2"/>
     </row>
-    <row r="209" spans="3:3" ht="14.25">
+    <row r="209" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C209" s="2"/>
     </row>
-    <row r="210" spans="3:3" ht="14.25">
+    <row r="210" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C210" s="2"/>
     </row>
-    <row r="211" spans="3:3" ht="14.25">
+    <row r="211" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C211" s="2"/>
     </row>
-    <row r="212" spans="3:3" ht="14.25">
+    <row r="212" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C212" s="2"/>
     </row>
-    <row r="213" spans="3:3" ht="14.25">
+    <row r="213" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C213" s="2"/>
     </row>
-    <row r="214" spans="3:3" ht="14.25">
+    <row r="214" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C214" s="2"/>
     </row>
-    <row r="215" spans="3:3" ht="14.25">
+    <row r="215" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C215" s="2"/>
     </row>
-    <row r="216" spans="3:3" ht="14.25">
+    <row r="216" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C216" s="2"/>
     </row>
-    <row r="217" spans="3:3" ht="14.25">
+    <row r="217" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C217" s="2"/>
     </row>
-    <row r="218" spans="3:3" ht="14.25">
+    <row r="218" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C218" s="2"/>
     </row>
-    <row r="219" spans="3:3" ht="14.25">
+    <row r="219" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C219" s="2"/>
     </row>
-    <row r="220" spans="3:3" ht="14.25">
+    <row r="220" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C220" s="2"/>
     </row>
-    <row r="221" spans="3:3" ht="14.25">
+    <row r="221" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C221" s="2"/>
     </row>
-    <row r="222" spans="3:3" ht="14.25">
+    <row r="222" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C222" s="2"/>
     </row>
-    <row r="223" spans="3:3" ht="14.25">
+    <row r="223" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C223" s="2"/>
     </row>
-    <row r="224" spans="3:3" ht="14.25">
+    <row r="224" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C224" s="2"/>
     </row>
-    <row r="225" spans="3:3" ht="14.25">
+    <row r="225" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C225" s="2"/>
     </row>
-    <row r="226" spans="3:3" ht="14.25">
+    <row r="226" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C226" s="2"/>
     </row>
-    <row r="227" spans="3:3" ht="14.25">
+    <row r="227" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C227" s="2"/>
     </row>
-    <row r="228" spans="3:3" ht="14.25">
+    <row r="228" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C228" s="2"/>
     </row>
-    <row r="229" spans="3:3" ht="14.25">
+    <row r="229" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C229" s="2"/>
     </row>
-    <row r="230" spans="3:3" ht="14.25">
+    <row r="230" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C230" s="2"/>
     </row>
-    <row r="231" spans="3:3" ht="14.25">
+    <row r="231" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C231" s="2"/>
     </row>
-    <row r="232" spans="3:3" ht="14.25">
+    <row r="232" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C232" s="2"/>
     </row>
-    <row r="233" spans="3:3" ht="14.25">
+    <row r="233" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C233" s="2"/>
     </row>
-    <row r="234" spans="3:3" ht="14.25">
+    <row r="234" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C234" s="2"/>
     </row>
-    <row r="235" spans="3:3" ht="14.25">
+    <row r="235" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C235" s="2"/>
     </row>
-    <row r="236" spans="3:3" ht="14.25">
+    <row r="236" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C236" s="2"/>
     </row>
-    <row r="237" spans="3:3" ht="14.25">
+    <row r="237" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C237" s="2"/>
     </row>
-    <row r="238" spans="3:3" ht="14.25">
+    <row r="238" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C238" s="2"/>
     </row>
-    <row r="239" spans="3:3" ht="14.25">
+    <row r="239" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C239" s="2"/>
     </row>
-    <row r="240" spans="3:3" ht="14.25">
+    <row r="240" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C240" s="2"/>
     </row>
-    <row r="241" spans="3:3" ht="14.25">
+    <row r="241" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C241" s="2"/>
     </row>
-    <row r="242" spans="3:3" ht="14.25">
+    <row r="242" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C242" s="2"/>
     </row>
-    <row r="243" spans="3:3" ht="14.25">
+    <row r="243" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C243" s="2"/>
     </row>
-    <row r="244" spans="3:3" ht="14.25">
+    <row r="244" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C244" s="2"/>
     </row>
-    <row r="245" spans="3:3" ht="14.25">
+    <row r="245" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C245" s="2"/>
     </row>
-    <row r="246" spans="3:3" ht="14.25">
+    <row r="246" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C246" s="2"/>
     </row>
-    <row r="247" spans="3:3" ht="14.25">
+    <row r="247" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C247" s="2"/>
     </row>
-    <row r="248" spans="3:3" ht="14.25">
+    <row r="248" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C248" s="2"/>
     </row>
-    <row r="249" spans="3:3" ht="14.25">
+    <row r="249" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C249" s="2"/>
     </row>
-    <row r="250" spans="3:3" ht="14.25">
+    <row r="250" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C250" s="2"/>
     </row>
-    <row r="251" spans="3:3" ht="14.25">
+    <row r="251" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C251" s="2"/>
     </row>
-    <row r="252" spans="3:3" ht="14.25">
+    <row r="252" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C252" s="2"/>
     </row>
-    <row r="253" spans="3:3" ht="14.25">
+    <row r="253" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C253" s="2"/>
     </row>
-    <row r="254" spans="3:3" ht="14.25">
+    <row r="254" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C254" s="2"/>
     </row>
-    <row r="255" spans="3:3" ht="14.25">
+    <row r="255" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C255" s="2"/>
     </row>
-    <row r="256" spans="3:3" ht="14.25">
+    <row r="256" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C256" s="2"/>
     </row>
-    <row r="257" spans="3:3" ht="14.25">
+    <row r="257" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C257" s="2"/>
     </row>
-    <row r="258" spans="3:3" ht="14.25">
+    <row r="258" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C258" s="2"/>
     </row>
-    <row r="259" spans="3:3" ht="14.25">
+    <row r="259" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C259" s="2"/>
     </row>
-    <row r="260" spans="3:3" ht="14.25">
+    <row r="260" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C260" s="2"/>
     </row>
-    <row r="261" spans="3:3" ht="14.25">
+    <row r="261" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C261" s="2"/>
     </row>
-    <row r="262" spans="3:3" ht="14.25">
+    <row r="262" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C262" s="2"/>
     </row>
-    <row r="263" spans="3:3" ht="14.25">
+    <row r="263" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C263" s="2"/>
     </row>
-    <row r="264" spans="3:3" ht="14.25">
+    <row r="264" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C264" s="2"/>
     </row>
-    <row r="265" spans="3:3" ht="14.25">
+    <row r="265" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C265" s="2"/>
     </row>
-    <row r="266" spans="3:3" ht="14.25">
+    <row r="266" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C266" s="2"/>
     </row>
-    <row r="267" spans="3:3" ht="14.25">
+    <row r="267" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C267" s="2"/>
     </row>
-    <row r="268" spans="3:3" ht="14.25">
+    <row r="268" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C268" s="2"/>
     </row>
-    <row r="269" spans="3:3" ht="14.25">
+    <row r="269" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C269" s="2"/>
     </row>
-    <row r="270" spans="3:3" ht="14.25">
+    <row r="270" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C270" s="2"/>
     </row>
-    <row r="271" spans="3:3" ht="14.25">
+    <row r="271" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C271" s="2"/>
     </row>
-    <row r="272" spans="3:3" ht="14.25">
+    <row r="272" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C272" s="2"/>
     </row>
-    <row r="273" spans="3:3" ht="14.25">
+    <row r="273" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C273" s="2"/>
     </row>
-    <row r="274" spans="3:3" ht="14.25">
+    <row r="274" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C274" s="2"/>
     </row>
-    <row r="275" spans="3:3" ht="14.25">
+    <row r="275" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C275" s="2"/>
     </row>
-    <row r="276" spans="3:3" ht="14.25">
+    <row r="276" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C276" s="2"/>
     </row>
-    <row r="277" spans="3:3" ht="14.25">
+    <row r="277" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C277" s="2"/>
     </row>
-    <row r="278" spans="3:3" ht="14.25">
+    <row r="278" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C278" s="2"/>
     </row>
-    <row r="279" spans="3:3" ht="14.25">
+    <row r="279" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C279" s="2"/>
     </row>
-    <row r="280" spans="3:3" ht="14.25">
+    <row r="280" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C280" s="2"/>
     </row>
-    <row r="281" spans="3:3" ht="14.25">
+    <row r="281" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C281" s="2"/>
     </row>
-    <row r="282" spans="3:3" ht="14.25">
+    <row r="282" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C282" s="2"/>
     </row>
-    <row r="283" spans="3:3" ht="14.25">
+    <row r="283" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C283" s="2"/>
     </row>
-    <row r="284" spans="3:3" ht="14.25">
+    <row r="284" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C284" s="2"/>
     </row>
-    <row r="285" spans="3:3" ht="14.25">
+    <row r="285" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C285" s="2"/>
     </row>
-    <row r="286" spans="3:3" ht="14.25">
+    <row r="286" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C286" s="2"/>
     </row>
-    <row r="287" spans="3:3" ht="14.25">
+    <row r="287" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C287" s="2"/>
     </row>
-    <row r="288" spans="3:3" ht="14.25">
+    <row r="288" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C288" s="2"/>
     </row>
-    <row r="289" spans="3:3" ht="14.25">
+    <row r="289" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C289" s="2"/>
     </row>
-    <row r="290" spans="3:3" ht="14.25">
+    <row r="290" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C290" s="2"/>
     </row>
-    <row r="291" spans="3:3" ht="14.25">
+    <row r="291" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C291" s="2"/>
     </row>
-    <row r="292" spans="3:3" ht="14.25">
+    <row r="292" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C292" s="2"/>
     </row>
-    <row r="293" spans="3:3" ht="14.25">
+    <row r="293" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C293" s="2"/>
     </row>
-    <row r="294" spans="3:3" ht="14.25">
+    <row r="294" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C294" s="2"/>
     </row>
-    <row r="295" spans="3:3" ht="14.25">
+    <row r="295" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C295" s="2"/>
     </row>
-    <row r="296" spans="3:3" ht="14.25">
+    <row r="296" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C296" s="2"/>
     </row>
-    <row r="297" spans="3:3" ht="14.25">
+    <row r="297" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C297" s="2"/>
     </row>
-    <row r="298" spans="3:3" ht="14.25">
+    <row r="298" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C298" s="2"/>
     </row>
-    <row r="299" spans="3:3" ht="14.25">
+    <row r="299" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C299" s="2"/>
     </row>
-    <row r="300" spans="3:3" ht="14.25">
+    <row r="300" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C300" s="2"/>
     </row>
-    <row r="301" spans="3:3" ht="14.25">
+    <row r="301" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C301" s="2"/>
     </row>
-    <row r="302" spans="3:3" ht="14.25">
+    <row r="302" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C302" s="2"/>
     </row>
-    <row r="303" spans="3:3" ht="14.25">
+    <row r="303" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C303" s="2"/>
     </row>
-    <row r="304" spans="3:3" ht="14.25">
+    <row r="304" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C304" s="2"/>
     </row>
-    <row r="305" spans="3:3" ht="14.25">
+    <row r="305" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C305" s="2"/>
     </row>
-    <row r="306" spans="3:3" ht="14.25">
+    <row r="306" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C306" s="2"/>
     </row>
-    <row r="307" spans="3:3" ht="14.25">
+    <row r="307" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C307" s="2"/>
     </row>
-    <row r="308" spans="3:3" ht="14.25">
+    <row r="308" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C308" s="2"/>
     </row>
-    <row r="309" spans="3:3" ht="14.25">
+    <row r="309" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C309" s="2"/>
     </row>
-    <row r="310" spans="3:3" ht="14.25">
+    <row r="310" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C310" s="2"/>
     </row>
-    <row r="311" spans="3:3" ht="14.25">
+    <row r="311" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C311" s="2"/>
     </row>
-    <row r="312" spans="3:3" ht="14.25">
+    <row r="312" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C312" s="2"/>
     </row>
-    <row r="313" spans="3:3" ht="14.25">
+    <row r="313" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C313" s="2"/>
     </row>
-    <row r="314" spans="3:3" ht="14.25">
+    <row r="314" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C314" s="2"/>
     </row>
-    <row r="315" spans="3:3" ht="14.25">
+    <row r="315" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C315" s="2"/>
     </row>
-    <row r="316" spans="3:3" ht="14.25">
+    <row r="316" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C316" s="2"/>
     </row>
-    <row r="317" spans="3:3" ht="14.25">
+    <row r="317" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C317" s="2"/>
     </row>
-    <row r="318" spans="3:3" ht="14.25">
+    <row r="318" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C318" s="2"/>
     </row>
-    <row r="319" spans="3:3" ht="14.25">
+    <row r="319" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C319" s="2"/>
     </row>
-    <row r="320" spans="3:3" ht="14.25">
+    <row r="320" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C320" s="2"/>
     </row>
-    <row r="321" spans="3:3" ht="14.25">
+    <row r="321" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C321" s="2"/>
     </row>
-    <row r="322" spans="3:3" ht="14.25">
+    <row r="322" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C322" s="2"/>
     </row>
-    <row r="323" spans="3:3" ht="14.25">
+    <row r="323" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C323" s="2"/>
     </row>
-    <row r="324" spans="3:3" ht="14.25">
+    <row r="324" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C324" s="2"/>
     </row>
-    <row r="325" spans="3:3" ht="14.25">
+    <row r="325" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C325" s="2"/>
     </row>
-    <row r="326" spans="3:3" ht="14.25">
+    <row r="326" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C326" s="2"/>
     </row>
-    <row r="327" spans="3:3" ht="14.25">
+    <row r="327" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C327" s="2"/>
     </row>
-    <row r="328" spans="3:3" ht="14.25">
+    <row r="328" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C328" s="2"/>
     </row>
-    <row r="329" spans="3:3" ht="14.25">
+    <row r="329" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C329" s="2"/>
     </row>
-    <row r="330" spans="3:3" ht="14.25">
+    <row r="330" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C330" s="2"/>
     </row>
-    <row r="331" spans="3:3" ht="14.25">
+    <row r="331" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C331" s="2"/>
     </row>
-    <row r="332" spans="3:3" ht="14.25">
+    <row r="332" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C332" s="2"/>
     </row>
-    <row r="333" spans="3:3" ht="14.25">
+    <row r="333" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C333" s="2"/>
     </row>
-    <row r="334" spans="3:3" ht="14.25">
+    <row r="334" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C334" s="2"/>
     </row>
-    <row r="335" spans="3:3" ht="14.25">
+    <row r="335" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C335" s="2"/>
     </row>
-    <row r="336" spans="3:3" ht="14.25">
+    <row r="336" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C336" s="2"/>
     </row>
-    <row r="337" spans="3:3" ht="14.25">
+    <row r="337" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C337" s="2"/>
     </row>
-    <row r="338" spans="3:3" ht="14.25">
+    <row r="338" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C338" s="2"/>
     </row>
-    <row r="339" spans="3:3" ht="14.25">
+    <row r="339" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C339" s="2"/>
     </row>
-    <row r="340" spans="3:3" ht="14.25">
+    <row r="340" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C340" s="2"/>
     </row>
-    <row r="341" spans="3:3" ht="14.25">
+    <row r="341" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C341" s="2"/>
     </row>
-    <row r="342" spans="3:3" ht="14.25">
+    <row r="342" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C342" s="2"/>
     </row>
-    <row r="343" spans="3:3" ht="14.25">
+    <row r="343" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C343" s="2"/>
     </row>
-    <row r="344" spans="3:3" ht="14.25">
+    <row r="344" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C344" s="2"/>
     </row>
-    <row r="345" spans="3:3" ht="14.25">
+    <row r="345" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C345" s="2"/>
     </row>
-    <row r="346" spans="3:3" ht="14.25">
+    <row r="346" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C346" s="2"/>
     </row>
-    <row r="347" spans="3:3" ht="14.25">
+    <row r="347" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C347" s="2"/>
     </row>
-    <row r="348" spans="3:3" ht="14.25">
+    <row r="348" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C348" s="2"/>
     </row>
-    <row r="349" spans="3:3" ht="14.25">
+    <row r="349" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C349" s="2"/>
     </row>
-    <row r="350" spans="3:3" ht="14.25">
+    <row r="350" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C350" s="2"/>
     </row>
-    <row r="351" spans="3:3" ht="14.25">
+    <row r="351" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C351" s="2"/>
     </row>
-    <row r="352" spans="3:3" ht="14.25">
+    <row r="352" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C352" s="2"/>
     </row>
-    <row r="353" spans="3:3" ht="14.25">
+    <row r="353" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C353" s="2"/>
     </row>
-    <row r="354" spans="3:3" ht="14.25">
+    <row r="354" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C354" s="2"/>
     </row>
-    <row r="355" spans="3:3" ht="14.25">
+    <row r="355" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C355" s="2"/>
     </row>
-    <row r="356" spans="3:3" ht="14.25">
+    <row r="356" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C356" s="2"/>
     </row>
-    <row r="357" spans="3:3" ht="14.25">
+    <row r="357" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C357" s="2"/>
     </row>
-    <row r="358" spans="3:3" ht="14.25">
+    <row r="358" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C358" s="2"/>
     </row>
-    <row r="359" spans="3:3" ht="14.25">
+    <row r="359" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C359" s="2"/>
     </row>
-    <row r="360" spans="3:3" ht="14.25">
+    <row r="360" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C360" s="2"/>
     </row>
-    <row r="361" spans="3:3" ht="14.25">
+    <row r="361" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C361" s="2"/>
     </row>
-    <row r="362" spans="3:3" ht="14.25">
+    <row r="362" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C362" s="2"/>
     </row>
-    <row r="363" spans="3:3" ht="14.25">
+    <row r="363" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C363" s="2"/>
     </row>
-    <row r="364" spans="3:3" ht="14.25">
+    <row r="364" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C364" s="2"/>
     </row>
-    <row r="365" spans="3:3" ht="14.25">
+    <row r="365" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C365" s="2"/>
     </row>
-    <row r="366" spans="3:3" ht="14.25">
+    <row r="366" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C366" s="2"/>
     </row>
-    <row r="367" spans="3:3" ht="14.25">
+    <row r="367" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C367" s="2"/>
     </row>
-    <row r="368" spans="3:3" ht="14.25">
+    <row r="368" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C368" s="2"/>
     </row>
-    <row r="369" spans="3:3" ht="14.25">
+    <row r="369" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C369" s="2"/>
     </row>
-    <row r="370" spans="3:3" ht="14.25">
+    <row r="370" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C370" s="2"/>
     </row>
-    <row r="371" spans="3:3" ht="14.25">
+    <row r="371" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C371" s="2"/>
     </row>
-    <row r="372" spans="3:3" ht="14.25">
+    <row r="372" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C372" s="2"/>
     </row>
-    <row r="373" spans="3:3" ht="14.25">
+    <row r="373" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C373" s="2"/>
     </row>
-    <row r="374" spans="3:3" ht="14.25">
+    <row r="374" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C374" s="2"/>
     </row>
-    <row r="375" spans="3:3" ht="14.25">
+    <row r="375" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C375" s="2"/>
     </row>
-    <row r="376" spans="3:3" ht="14.25">
+    <row r="376" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C376" s="2"/>
     </row>
-    <row r="377" spans="3:3" ht="14.25">
+    <row r="377" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C377" s="2"/>
     </row>
-    <row r="378" spans="3:3" ht="14.25">
+    <row r="378" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C378" s="2"/>
     </row>
-    <row r="379" spans="3:3" ht="14.25">
+    <row r="379" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C379" s="2"/>
     </row>
-    <row r="380" spans="3:3" ht="14.25">
+    <row r="380" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C380" s="2"/>
     </row>
-    <row r="381" spans="3:3" ht="14.25">
+    <row r="381" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C381" s="2"/>
     </row>
-    <row r="382" spans="3:3" ht="14.25">
+    <row r="382" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C382" s="2"/>
     </row>
-    <row r="383" spans="3:3" ht="14.25">
+    <row r="383" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C383" s="2"/>
     </row>
-    <row r="384" spans="3:3" ht="14.25">
+    <row r="384" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C384" s="2"/>
     </row>
-    <row r="385" spans="3:3" ht="14.25">
+    <row r="385" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C385" s="2"/>
     </row>
-    <row r="386" spans="3:3" ht="14.25">
+    <row r="386" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C386" s="2"/>
     </row>
-    <row r="387" spans="3:3" ht="14.25">
+    <row r="387" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C387" s="2"/>
     </row>
-    <row r="388" spans="3:3" ht="14.25">
+    <row r="388" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C388" s="2"/>
     </row>
-    <row r="389" spans="3:3" ht="14.25">
+    <row r="389" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C389" s="2"/>
     </row>
-    <row r="390" spans="3:3" ht="14.25">
+    <row r="390" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C390" s="2"/>
     </row>
-    <row r="391" spans="3:3" ht="14.25">
+    <row r="391" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C391" s="2"/>
     </row>
-    <row r="392" spans="3:3" ht="14.25">
+    <row r="392" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C392" s="2"/>
     </row>
-    <row r="393" spans="3:3" ht="14.25">
+    <row r="393" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C393" s="2"/>
     </row>
-    <row r="394" spans="3:3" ht="14.25">
+    <row r="394" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C394" s="2"/>
     </row>
-    <row r="395" spans="3:3" ht="14.25">
+    <row r="395" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C395" s="2"/>
     </row>
-    <row r="396" spans="3:3" ht="14.25">
+    <row r="396" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C396" s="2"/>
     </row>
-    <row r="397" spans="3:3" ht="14.25">
+    <row r="397" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C397" s="2"/>
     </row>
-    <row r="398" spans="3:3" ht="14.25">
+    <row r="398" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C398" s="2"/>
     </row>
-    <row r="399" spans="3:3" ht="14.25">
+    <row r="399" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C399" s="2"/>
     </row>
-    <row r="400" spans="3:3" ht="14.25">
+    <row r="400" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C400" s="2"/>
     </row>
-    <row r="401" spans="3:3" ht="14.25">
+    <row r="401" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C401" s="2"/>
     </row>
-    <row r="402" spans="3:3" ht="14.25">
+    <row r="402" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C402" s="2"/>
     </row>
-    <row r="403" spans="3:3" ht="14.25">
+    <row r="403" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C403" s="2"/>
     </row>
-    <row r="404" spans="3:3" ht="14.25">
+    <row r="404" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C404" s="2"/>
     </row>
-    <row r="405" spans="3:3" ht="14.25">
+    <row r="405" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C405" s="2"/>
     </row>
-    <row r="406" spans="3:3" ht="14.25">
+    <row r="406" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C406" s="2"/>
     </row>
-    <row r="407" spans="3:3" ht="14.25">
+    <row r="407" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C407" s="2"/>
     </row>
-    <row r="408" spans="3:3" ht="14.25">
+    <row r="408" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C408" s="2"/>
     </row>
-    <row r="409" spans="3:3" ht="14.25">
+    <row r="409" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C409" s="2"/>
     </row>
-    <row r="410" spans="3:3" ht="14.25">
+    <row r="410" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C410" s="2"/>
     </row>
-    <row r="411" spans="3:3" ht="14.25">
+    <row r="411" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C411" s="2"/>
     </row>
-    <row r="412" spans="3:3" ht="14.25">
+    <row r="412" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C412" s="2"/>
     </row>
-    <row r="413" spans="3:3" ht="14.25">
+    <row r="413" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C413" s="2"/>
     </row>
-    <row r="414" spans="3:3" ht="14.25">
+    <row r="414" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C414" s="2"/>
     </row>
-    <row r="415" spans="3:3" ht="14.25">
+    <row r="415" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C415" s="2"/>
     </row>
-    <row r="416" spans="3:3" ht="14.25">
+    <row r="416" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C416" s="2"/>
     </row>
-    <row r="417" spans="3:3" ht="14.25">
+    <row r="417" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C417" s="2"/>
     </row>
-    <row r="418" spans="3:3" ht="14.25">
+    <row r="418" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C418" s="2"/>
     </row>
-    <row r="419" spans="3:3" ht="14.25">
+    <row r="419" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C419" s="2"/>
     </row>
-    <row r="420" spans="3:3" ht="14.25">
+    <row r="420" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C420" s="2"/>
     </row>
-    <row r="421" spans="3:3" ht="14.25">
+    <row r="421" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C421" s="2"/>
     </row>
-    <row r="422" spans="3:3" ht="14.25">
+    <row r="422" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C422" s="2"/>
     </row>
-    <row r="423" spans="3:3" ht="14.25">
+    <row r="423" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C423" s="2"/>
     </row>
-    <row r="424" spans="3:3" ht="14.25">
+    <row r="424" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C424" s="2"/>
     </row>
-    <row r="425" spans="3:3" ht="14.25">
+    <row r="425" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C425" s="2"/>
     </row>
-    <row r="426" spans="3:3" ht="14.25">
+    <row r="426" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C426" s="2"/>
     </row>
-    <row r="427" spans="3:3" ht="14.25">
+    <row r="427" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C427" s="2"/>
     </row>
-    <row r="428" spans="3:3" ht="14.25">
+    <row r="428" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C428" s="2"/>
     </row>
-    <row r="429" spans="3:3" ht="14.25">
+    <row r="429" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C429" s="2"/>
     </row>
-    <row r="430" spans="3:3" ht="14.25">
+    <row r="430" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C430" s="2"/>
     </row>
-    <row r="431" spans="3:3" ht="14.25">
+    <row r="431" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C431" s="2"/>
     </row>
-    <row r="432" spans="3:3" ht="14.25">
+    <row r="432" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C432" s="2"/>
     </row>
-    <row r="433" spans="3:3" ht="14.25">
+    <row r="433" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C433" s="2"/>
     </row>
-    <row r="434" spans="3:3" ht="14.25">
+    <row r="434" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C434" s="2"/>
     </row>
-    <row r="435" spans="3:3" ht="14.25">
+    <row r="435" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C435" s="2"/>
     </row>
-    <row r="436" spans="3:3" ht="14.25">
+    <row r="436" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C436" s="2"/>
     </row>
-    <row r="437" spans="3:3" ht="14.25">
+    <row r="437" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C437" s="2"/>
     </row>
-    <row r="438" spans="3:3" ht="14.25">
+    <row r="438" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C438" s="2"/>
     </row>
-    <row r="439" spans="3:3" ht="14.25">
+    <row r="439" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C439" s="2"/>
     </row>
-    <row r="440" spans="3:3" ht="14.25">
+    <row r="440" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C440" s="2"/>
     </row>
-    <row r="441" spans="3:3" ht="14.25">
+    <row r="441" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C441" s="2"/>
     </row>
-    <row r="442" spans="3:3" ht="14.25">
+    <row r="442" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C442" s="2"/>
     </row>
-    <row r="443" spans="3:3" ht="14.25">
+    <row r="443" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C443" s="2"/>
     </row>
-    <row r="444" spans="3:3" ht="14.25">
+    <row r="444" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C444" s="2"/>
     </row>
-    <row r="445" spans="3:3" ht="14.25">
+    <row r="445" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C445" s="2"/>
     </row>
-    <row r="446" spans="3:3" ht="14.25">
+    <row r="446" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C446" s="2"/>
     </row>
-    <row r="447" spans="3:3" ht="14.25">
+    <row r="447" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C447" s="2"/>
     </row>
-    <row r="448" spans="3:3" ht="14.25">
+    <row r="448" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C448" s="2"/>
     </row>
-    <row r="449" spans="3:3" ht="14.25">
+    <row r="449" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C449" s="2"/>
     </row>
-    <row r="450" spans="3:3" ht="14.25">
+    <row r="450" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C450" s="2"/>
     </row>
-    <row r="451" spans="3:3" ht="14.25">
+    <row r="451" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C451" s="2"/>
     </row>
-    <row r="452" spans="3:3" ht="14.25">
+    <row r="452" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C452" s="2"/>
     </row>
-    <row r="453" spans="3:3" ht="14.25">
+    <row r="453" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C453" s="2"/>
     </row>
-    <row r="454" spans="3:3" ht="14.25">
+    <row r="454" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C454" s="2"/>
     </row>
-    <row r="455" spans="3:3" ht="14.25">
+    <row r="455" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C455" s="2"/>
     </row>
-    <row r="456" spans="3:3" ht="14.25">
+    <row r="456" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C456" s="2"/>
     </row>
-    <row r="457" spans="3:3" ht="14.25">
+    <row r="457" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C457" s="2"/>
     </row>
-    <row r="458" spans="3:3" ht="14.25">
+    <row r="458" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C458" s="2"/>
     </row>
-    <row r="459" spans="3:3" ht="14.25">
+    <row r="459" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C459" s="2"/>
     </row>
-    <row r="460" spans="3:3" ht="14.25">
+    <row r="460" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C460" s="2"/>
     </row>
-    <row r="461" spans="3:3" ht="14.25">
+    <row r="461" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C461" s="2"/>
     </row>
-    <row r="462" spans="3:3" ht="14.25">
+    <row r="462" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C462" s="2"/>
     </row>
-    <row r="463" spans="3:3" ht="14.25">
+    <row r="463" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C463" s="2"/>
     </row>
-    <row r="464" spans="3:3" ht="14.25">
+    <row r="464" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C464" s="2"/>
     </row>
-    <row r="465" spans="3:3" ht="14.25">
+    <row r="465" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C465" s="2"/>
     </row>
-    <row r="466" spans="3:3" ht="14.25">
+    <row r="466" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C466" s="2"/>
     </row>
-    <row r="467" spans="3:3" ht="14.25">
+    <row r="467" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C467" s="2"/>
     </row>
-    <row r="468" spans="3:3" ht="14.25">
+    <row r="468" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C468" s="2"/>
     </row>
-    <row r="469" spans="3:3" ht="14.25">
+    <row r="469" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C469" s="2"/>
     </row>
-    <row r="470" spans="3:3" ht="14.25">
+    <row r="470" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C470" s="2"/>
     </row>
-    <row r="471" spans="3:3" ht="14.25">
+    <row r="471" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C471" s="2"/>
     </row>
-    <row r="472" spans="3:3" ht="14.25">
+    <row r="472" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C472" s="2"/>
     </row>
-    <row r="473" spans="3:3" ht="14.25">
+    <row r="473" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C473" s="2"/>
     </row>
-    <row r="474" spans="3:3" ht="14.25">
+    <row r="474" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C474" s="2"/>
     </row>
-    <row r="475" spans="3:3" ht="14.25">
+    <row r="475" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C475" s="2"/>
     </row>
-    <row r="476" spans="3:3" ht="14.25">
+    <row r="476" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C476" s="2"/>
     </row>
-    <row r="477" spans="3:3" ht="14.25">
+    <row r="477" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C477" s="2"/>
     </row>
-    <row r="478" spans="3:3" ht="14.25">
+    <row r="478" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C478" s="2"/>
     </row>
-    <row r="479" spans="3:3" ht="14.25">
+    <row r="479" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C479" s="2"/>
     </row>
-    <row r="480" spans="3:3" ht="14.25">
+    <row r="480" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C480" s="2"/>
     </row>
-    <row r="481" spans="3:3" ht="14.25">
+    <row r="481" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C481" s="2"/>
     </row>
-    <row r="482" spans="3:3" ht="14.25">
+    <row r="482" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C482" s="2"/>
     </row>
-    <row r="483" spans="3:3" ht="14.25">
+    <row r="483" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C483" s="2"/>
     </row>
-    <row r="484" spans="3:3" ht="14.25">
+    <row r="484" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C484" s="2"/>
     </row>
-    <row r="485" spans="3:3" ht="14.25">
+    <row r="485" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C485" s="2"/>
     </row>
-    <row r="486" spans="3:3" ht="14.25">
+    <row r="486" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C486" s="2"/>
     </row>
-    <row r="487" spans="3:3" ht="14.25">
+    <row r="487" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C487" s="2"/>
     </row>
-    <row r="488" spans="3:3" ht="14.25">
+    <row r="488" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C488" s="2"/>
     </row>
-    <row r="489" spans="3:3" ht="14.25">
+    <row r="489" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C489" s="2"/>
     </row>
-    <row r="490" spans="3:3" ht="14.25">
+    <row r="490" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C490" s="2"/>
     </row>
-    <row r="491" spans="3:3" ht="14.25">
+    <row r="491" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C491" s="2"/>
     </row>
-    <row r="492" spans="3:3" ht="14.25">
+    <row r="492" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C492" s="2"/>
     </row>
-    <row r="493" spans="3:3" ht="14.25">
+    <row r="493" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C493" s="2"/>
     </row>
-    <row r="494" spans="3:3" ht="14.25">
+    <row r="494" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C494" s="2"/>
     </row>
-    <row r="495" spans="3:3" ht="14.25">
+    <row r="495" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C495" s="2"/>
     </row>
-    <row r="496" spans="3:3" ht="14.25">
+    <row r="496" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C496" s="2"/>
     </row>
-    <row r="497" spans="3:3" ht="14.25">
+    <row r="497" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C497" s="2"/>
     </row>
-    <row r="498" spans="3:3" ht="14.25">
+    <row r="498" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C498" s="2"/>
     </row>
-    <row r="499" spans="3:3" ht="14.25">
+    <row r="499" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C499" s="2"/>
     </row>
-    <row r="500" spans="3:3" ht="14.25">
+    <row r="500" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C500" s="2"/>
     </row>
-    <row r="501" spans="3:3" ht="14.25">
+    <row r="501" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C501" s="2"/>
     </row>
-    <row r="502" spans="3:3" ht="14.25">
+    <row r="502" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C502" s="2"/>
     </row>
-    <row r="503" spans="3:3" ht="14.25">
+    <row r="503" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C503" s="2"/>
     </row>
-    <row r="504" spans="3:3" ht="14.25">
+    <row r="504" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C504" s="2"/>
     </row>
-    <row r="505" spans="3:3" ht="14.25">
+    <row r="505" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C505" s="2"/>
     </row>
-    <row r="506" spans="3:3" ht="14.25">
+    <row r="506" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C506" s="2"/>
     </row>
-    <row r="507" spans="3:3" ht="14.25">
+    <row r="507" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C507" s="2"/>
     </row>
-    <row r="508" spans="3:3" ht="14.25">
+    <row r="508" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C508" s="2"/>
     </row>
-    <row r="509" spans="3:3" ht="14.25">
+    <row r="509" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C509" s="2"/>
     </row>
-    <row r="510" spans="3:3" ht="14.25">
+    <row r="510" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C510" s="2"/>
     </row>
-    <row r="511" spans="3:3" ht="14.25">
+    <row r="511" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C511" s="2"/>
     </row>
-    <row r="512" spans="3:3" ht="14.25">
+    <row r="512" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C512" s="2"/>
     </row>
-    <row r="513" spans="3:3" ht="14.25">
+    <row r="513" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C513" s="2"/>
     </row>
-    <row r="514" spans="3:3" ht="14.25">
+    <row r="514" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C514" s="2"/>
     </row>
-    <row r="515" spans="3:3" ht="14.25">
+    <row r="515" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C515" s="2"/>
     </row>
-    <row r="516" spans="3:3" ht="14.25">
+    <row r="516" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C516" s="2"/>
     </row>
-    <row r="517" spans="3:3" ht="14.25">
+    <row r="517" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C517" s="2"/>
     </row>
-    <row r="518" spans="3:3" ht="14.25">
+    <row r="518" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C518" s="2"/>
     </row>
-    <row r="519" spans="3:3" ht="14.25">
+    <row r="519" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C519" s="2"/>
     </row>
-    <row r="520" spans="3:3" ht="14.25">
+    <row r="520" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C520" s="2"/>
     </row>
-    <row r="521" spans="3:3" ht="14.25">
+    <row r="521" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C521" s="2"/>
     </row>
-    <row r="522" spans="3:3" ht="14.25">
+    <row r="522" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C522" s="2"/>
     </row>
-    <row r="523" spans="3:3" ht="14.25">
+    <row r="523" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C523" s="2"/>
     </row>
-    <row r="524" spans="3:3" ht="14.25">
+    <row r="524" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C524" s="2"/>
     </row>
-    <row r="525" spans="3:3" ht="14.25">
+    <row r="525" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C525" s="2"/>
     </row>
-    <row r="526" spans="3:3" ht="14.25">
+    <row r="526" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C526" s="2"/>
     </row>
-    <row r="527" spans="3:3" ht="14.25">
+    <row r="527" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C527" s="2"/>
     </row>
-    <row r="528" spans="3:3" ht="14.25">
+    <row r="528" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C528" s="2"/>
     </row>
-    <row r="529" spans="3:3" ht="14.25">
+    <row r="529" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C529" s="2"/>
     </row>
-    <row r="530" spans="3:3" ht="14.25">
+    <row r="530" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C530" s="2"/>
     </row>
-    <row r="531" spans="3:3" ht="14.25">
+    <row r="531" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C531" s="2"/>
     </row>
-    <row r="532" spans="3:3" ht="14.25">
+    <row r="532" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C532" s="2"/>
     </row>
-    <row r="533" spans="3:3" ht="14.25">
+    <row r="533" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C533" s="2"/>
     </row>
-    <row r="534" spans="3:3" ht="14.25">
+    <row r="534" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C534" s="2"/>
     </row>
-    <row r="535" spans="3:3" ht="14.25">
+    <row r="535" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C535" s="2"/>
     </row>
-    <row r="536" spans="3:3" ht="14.25">
+    <row r="536" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C536" s="2"/>
     </row>
-    <row r="537" spans="3:3" ht="14.25">
+    <row r="537" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C537" s="2"/>
     </row>
-    <row r="538" spans="3:3" ht="14.25">
+    <row r="538" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C538" s="2"/>
     </row>
-    <row r="539" spans="3:3" ht="14.25">
+    <row r="539" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C539" s="2"/>
     </row>
-    <row r="540" spans="3:3" ht="14.25">
+    <row r="540" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C540" s="2"/>
     </row>
-    <row r="541" spans="3:3" ht="14.25">
+    <row r="541" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C541" s="2"/>
     </row>
-    <row r="542" spans="3:3" ht="14.25">
+    <row r="542" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C542" s="2"/>
     </row>
-    <row r="543" spans="3:3" ht="14.25">
+    <row r="543" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C543" s="2"/>
     </row>
-    <row r="544" spans="3:3" ht="14.25">
+    <row r="544" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C544" s="2"/>
     </row>
-    <row r="545" spans="3:3" ht="14.25">
+    <row r="545" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C545" s="2"/>
     </row>
-    <row r="546" spans="3:3" ht="14.25">
+    <row r="546" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C546" s="2"/>
     </row>
-    <row r="547" spans="3:3" ht="14.25">
+    <row r="547" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C547" s="2"/>
     </row>
-    <row r="548" spans="3:3" ht="14.25">
+    <row r="548" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C548" s="2"/>
     </row>
-    <row r="549" spans="3:3" ht="14.25">
+    <row r="549" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C549" s="2"/>
     </row>
-    <row r="550" spans="3:3" ht="14.25">
+    <row r="550" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C550" s="2"/>
     </row>
-    <row r="551" spans="3:3" ht="14.25">
+    <row r="551" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C551" s="2"/>
     </row>
-    <row r="552" spans="3:3" ht="14.25">
+    <row r="552" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C552" s="2"/>
     </row>
-    <row r="553" spans="3:3" ht="14.25">
+    <row r="553" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C553" s="2"/>
     </row>
-    <row r="554" spans="3:3" ht="14.25">
+    <row r="554" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C554" s="2"/>
     </row>
-    <row r="555" spans="3:3" ht="14.25">
+    <row r="555" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C555" s="2"/>
     </row>
-    <row r="556" spans="3:3" ht="14.25">
+    <row r="556" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C556" s="2"/>
     </row>
-    <row r="557" spans="3:3" ht="14.25">
+    <row r="557" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C557" s="2"/>
     </row>
-    <row r="558" spans="3:3" ht="14.25">
+    <row r="558" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C558" s="2"/>
     </row>
-    <row r="559" spans="3:3" ht="14.25">
+    <row r="559" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C559" s="2"/>
     </row>
-    <row r="560" spans="3:3" ht="14.25">
+    <row r="560" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C560" s="2"/>
     </row>
-    <row r="561" spans="3:3" ht="14.25">
+    <row r="561" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C561" s="2"/>
     </row>
-    <row r="562" spans="3:3" ht="14.25">
+    <row r="562" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C562" s="2"/>
     </row>
-    <row r="563" spans="3:3" ht="14.25">
+    <row r="563" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C563" s="2"/>
     </row>
-    <row r="564" spans="3:3" ht="14.25">
+    <row r="564" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C564" s="2"/>
     </row>
-    <row r="565" spans="3:3" ht="14.25">
+    <row r="565" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C565" s="2"/>
     </row>
-    <row r="566" spans="3:3" ht="14.25">
+    <row r="566" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C566" s="2"/>
     </row>
-    <row r="567" spans="3:3" ht="14.25">
+    <row r="567" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C567" s="2"/>
     </row>
-    <row r="568" spans="3:3" ht="14.25">
+    <row r="568" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C568" s="2"/>
     </row>
-    <row r="569" spans="3:3" ht="14.25">
+    <row r="569" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C569" s="2"/>
     </row>
-    <row r="570" spans="3:3" ht="14.25">
+    <row r="570" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C570" s="2"/>
     </row>
-    <row r="571" spans="3:3" ht="14.25">
+    <row r="571" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C571" s="2"/>
     </row>
-    <row r="572" spans="3:3" ht="14.25">
+    <row r="572" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C572" s="2"/>
     </row>
-    <row r="573" spans="3:3" ht="14.25">
+    <row r="573" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C573" s="2"/>
     </row>
-    <row r="574" spans="3:3" ht="14.25">
+    <row r="574" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C574" s="2"/>
     </row>
-    <row r="575" spans="3:3" ht="14.25">
+    <row r="575" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C575" s="2"/>
     </row>
-    <row r="576" spans="3:3" ht="14.25">
+    <row r="576" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C576" s="2"/>
     </row>
-    <row r="577" spans="3:3" ht="14.25">
+    <row r="577" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C577" s="2"/>
     </row>
-    <row r="578" spans="3:3" ht="14.25">
+    <row r="578" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C578" s="2"/>
     </row>
-    <row r="579" spans="3:3" ht="14.25">
+    <row r="579" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C579" s="2"/>
     </row>
-    <row r="580" spans="3:3" ht="14.25">
+    <row r="580" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C580" s="2"/>
     </row>
-    <row r="581" spans="3:3" ht="14.25">
+    <row r="581" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C581" s="2"/>
     </row>
-    <row r="582" spans="3:3" ht="14.25">
+    <row r="582" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C582" s="2"/>
     </row>
-    <row r="583" spans="3:3" ht="14.25">
+    <row r="583" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C583" s="2"/>
     </row>
-    <row r="584" spans="3:3" ht="14.25">
+    <row r="584" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C584" s="2"/>
     </row>
-    <row r="585" spans="3:3" ht="14.25">
+    <row r="585" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C585" s="2"/>
     </row>
-    <row r="586" spans="3:3" ht="14.25">
+    <row r="586" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C586" s="2"/>
     </row>
-    <row r="587" spans="3:3" ht="14.25">
+    <row r="587" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C587" s="2"/>
     </row>
-    <row r="588" spans="3:3" ht="14.25">
+    <row r="588" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C588" s="2"/>
     </row>
-    <row r="589" spans="3:3" ht="14.25">
+    <row r="589" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C589" s="2"/>
     </row>
-    <row r="590" spans="3:3" ht="14.25">
+    <row r="590" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C590" s="2"/>
     </row>
-    <row r="591" spans="3:3" ht="14.25">
+    <row r="591" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C591" s="2"/>
     </row>
-    <row r="592" spans="3:3" ht="14.25">
+    <row r="592" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C592" s="2"/>
     </row>
-    <row r="593" spans="3:3" ht="14.25">
+    <row r="593" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C593" s="2"/>
     </row>
-    <row r="594" spans="3:3" ht="14.25">
+    <row r="594" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C594" s="2"/>
     </row>
-    <row r="595" spans="3:3" ht="14.25">
+    <row r="595" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C595" s="2"/>
     </row>
-    <row r="596" spans="3:3" ht="14.25">
+    <row r="596" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C596" s="2"/>
     </row>
-    <row r="597" spans="3:3" ht="14.25">
+    <row r="597" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C597" s="2"/>
     </row>
-    <row r="598" spans="3:3" ht="14.25">
+    <row r="598" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C598" s="2"/>
     </row>
-    <row r="599" spans="3:3" ht="14.25">
+    <row r="599" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C599" s="2"/>
     </row>
-    <row r="600" spans="3:3" ht="14.25">
+    <row r="600" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C600" s="2"/>
     </row>
-    <row r="601" spans="3:3" ht="14.25">
+    <row r="601" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C601" s="2"/>
     </row>
-    <row r="602" spans="3:3" ht="14.25">
+    <row r="602" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C602" s="2"/>
     </row>
-    <row r="603" spans="3:3" ht="14.25">
+    <row r="603" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C603" s="2"/>
     </row>
-    <row r="604" spans="3:3" ht="14.25">
+    <row r="604" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C604" s="2"/>
     </row>
-    <row r="605" spans="3:3" ht="14.25">
+    <row r="605" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C605" s="2"/>
     </row>
-    <row r="606" spans="3:3" ht="14.25">
+    <row r="606" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C606" s="2"/>
     </row>
-    <row r="607" spans="3:3" ht="14.25">
+    <row r="607" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C607" s="2"/>
     </row>
-    <row r="608" spans="3:3" ht="14.25">
+    <row r="608" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C608" s="2"/>
     </row>
-    <row r="609" spans="3:3" ht="14.25">
+    <row r="609" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C609" s="2"/>
     </row>
-    <row r="610" spans="3:3" ht="14.25">
+    <row r="610" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C610" s="2"/>
     </row>
-    <row r="611" spans="3:3" ht="14.25">
+    <row r="611" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C611" s="2"/>
     </row>
-    <row r="612" spans="3:3" ht="14.25">
+    <row r="612" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C612" s="2"/>
     </row>
-    <row r="613" spans="3:3" ht="14.25">
+    <row r="613" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C613" s="2"/>
     </row>
-    <row r="614" spans="3:3" ht="14.25">
+    <row r="614" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C614" s="2"/>
     </row>
-    <row r="615" spans="3:3" ht="14.25">
+    <row r="615" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C615" s="2"/>
     </row>
-    <row r="616" spans="3:3" ht="14.25">
+    <row r="616" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C616" s="2"/>
     </row>
-    <row r="617" spans="3:3" ht="14.25">
+    <row r="617" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C617" s="2"/>
     </row>
-    <row r="618" spans="3:3" ht="14.25">
+    <row r="618" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C618" s="2"/>
     </row>
-    <row r="619" spans="3:3" ht="14.25">
+    <row r="619" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C619" s="2"/>
     </row>
-    <row r="620" spans="3:3" ht="14.25">
+    <row r="620" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C620" s="2"/>
     </row>
-    <row r="621" spans="3:3" ht="14.25">
+    <row r="621" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C621" s="2"/>
     </row>
-    <row r="622" spans="3:3" ht="14.25">
+    <row r="622" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C622" s="2"/>
     </row>
-    <row r="623" spans="3:3" ht="14.25">
+    <row r="623" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C623" s="2"/>
     </row>
-    <row r="624" spans="3:3" ht="14.25">
+    <row r="624" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C624" s="2"/>
     </row>
-    <row r="625" spans="3:3" ht="14.25">
+    <row r="625" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C625" s="2"/>
     </row>
-    <row r="626" spans="3:3" ht="14.25">
+    <row r="626" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C626" s="2"/>
     </row>
-    <row r="627" spans="3:3" ht="14.25">
+    <row r="627" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C627" s="2"/>
     </row>
-    <row r="628" spans="3:3" ht="14.25">
+    <row r="628" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C628" s="2"/>
     </row>
-    <row r="629" spans="3:3" ht="14.25">
+    <row r="629" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C629" s="2"/>
     </row>
-    <row r="630" spans="3:3" ht="14.25">
+    <row r="630" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C630" s="2"/>
     </row>
-    <row r="631" spans="3:3" ht="14.25">
+    <row r="631" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C631" s="2"/>
     </row>
-    <row r="632" spans="3:3" ht="14.25">
+    <row r="632" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C632" s="2"/>
     </row>
-    <row r="633" spans="3:3" ht="14.25">
+    <row r="633" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C633" s="2"/>
     </row>
-    <row r="634" spans="3:3" ht="14.25">
+    <row r="634" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C634" s="2"/>
     </row>
-    <row r="635" spans="3:3" ht="14.25">
+    <row r="635" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C635" s="2"/>
     </row>
-    <row r="636" spans="3:3" ht="14.25">
+    <row r="636" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C636" s="2"/>
     </row>
-    <row r="637" spans="3:3" ht="14.25">
+    <row r="637" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C637" s="2"/>
     </row>
-    <row r="638" spans="3:3" ht="14.25">
+    <row r="638" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C638" s="2"/>
     </row>
-    <row r="639" spans="3:3" ht="14.25">
+    <row r="639" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C639" s="2"/>
     </row>
-    <row r="640" spans="3:3" ht="14.25">
+    <row r="640" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C640" s="2"/>
     </row>
-    <row r="641" spans="3:3" ht="14.25">
+    <row r="641" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C641" s="2"/>
     </row>
-    <row r="642" spans="3:3" ht="14.25">
+    <row r="642" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C642" s="2"/>
     </row>
-    <row r="643" spans="3:3" ht="14.25">
+    <row r="643" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C643" s="2"/>
     </row>
-    <row r="644" spans="3:3" ht="14.25">
+    <row r="644" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C644" s="2"/>
     </row>
-    <row r="645" spans="3:3" ht="14.25">
+    <row r="645" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C645" s="2"/>
     </row>
-    <row r="646" spans="3:3" ht="14.25">
+    <row r="646" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C646" s="2"/>
     </row>
-    <row r="647" spans="3:3" ht="14.25">
+    <row r="647" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C647" s="2"/>
     </row>
-    <row r="648" spans="3:3" ht="14.25">
+    <row r="648" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C648" s="2"/>
     </row>
-    <row r="649" spans="3:3" ht="14.25">
+    <row r="649" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C649" s="2"/>
     </row>
-    <row r="650" spans="3:3" ht="14.25">
+    <row r="650" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C650" s="2"/>
     </row>
-    <row r="651" spans="3:3" ht="14.25">
+    <row r="651" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C651" s="2"/>
     </row>
-    <row r="652" spans="3:3" ht="14.25">
+    <row r="652" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C652" s="2"/>
     </row>
-    <row r="653" spans="3:3" ht="14.25">
+    <row r="653" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C653" s="2"/>
     </row>
-    <row r="654" spans="3:3" ht="14.25">
+    <row r="654" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C654" s="2"/>
     </row>
-    <row r="655" spans="3:3" ht="14.25">
+    <row r="655" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C655" s="2"/>
     </row>
-    <row r="656" spans="3:3" ht="14.25">
+    <row r="656" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C656" s="2"/>
     </row>
-    <row r="657" spans="3:3" ht="14.25">
+    <row r="657" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C657" s="2"/>
     </row>
-    <row r="658" spans="3:3" ht="14.25">
+    <row r="658" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C658" s="2"/>
     </row>
-    <row r="659" spans="3:3" ht="14.25">
+    <row r="659" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C659" s="2"/>
     </row>
-    <row r="660" spans="3:3" ht="14.25">
+    <row r="660" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C660" s="2"/>
     </row>
-    <row r="661" spans="3:3" ht="14.25">
+    <row r="661" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C661" s="2"/>
     </row>
-    <row r="662" spans="3:3" ht="14.25">
+    <row r="662" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C662" s="2"/>
     </row>
-    <row r="663" spans="3:3" ht="14.25">
+    <row r="663" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C663" s="2"/>
     </row>
-    <row r="664" spans="3:3" ht="14.25">
+    <row r="664" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C664" s="2"/>
     </row>
-    <row r="665" spans="3:3" ht="14.25">
+    <row r="665" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C665" s="2"/>
     </row>
-    <row r="666" spans="3:3" ht="14.25">
+    <row r="666" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C666" s="2"/>
     </row>
-    <row r="667" spans="3:3" ht="14.25">
+    <row r="667" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C667" s="2"/>
     </row>
-    <row r="668" spans="3:3" ht="14.25">
+    <row r="668" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C668" s="2"/>
     </row>
-    <row r="669" spans="3:3" ht="14.25">
+    <row r="669" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C669" s="2"/>
     </row>
-    <row r="670" spans="3:3" ht="14.25">
+    <row r="670" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C670" s="2"/>
     </row>
-    <row r="671" spans="3:3" ht="14.25">
+    <row r="671" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C671" s="2"/>
     </row>
-    <row r="672" spans="3:3" ht="14.25">
+    <row r="672" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C672" s="2"/>
     </row>
-    <row r="673" spans="3:3" ht="14.25">
+    <row r="673" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C673" s="2"/>
     </row>
-    <row r="674" spans="3:3" ht="14.25">
+    <row r="674" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C674" s="2"/>
     </row>
-    <row r="675" spans="3:3" ht="14.25">
+    <row r="675" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C675" s="2"/>
     </row>
-    <row r="676" spans="3:3" ht="14.25">
+    <row r="676" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C676" s="2"/>
     </row>
-    <row r="677" spans="3:3" ht="14.25">
+    <row r="677" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C677" s="2"/>
     </row>
-    <row r="678" spans="3:3" ht="14.25">
+    <row r="678" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C678" s="2"/>
     </row>
-    <row r="679" spans="3:3" ht="14.25">
+    <row r="679" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C679" s="2"/>
     </row>
-    <row r="680" spans="3:3" ht="14.25">
+    <row r="680" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C680" s="2"/>
     </row>
-    <row r="681" spans="3:3" ht="14.25">
+    <row r="681" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C681" s="2"/>
     </row>
-    <row r="682" spans="3:3" ht="14.25">
+    <row r="682" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C682" s="2"/>
     </row>
-    <row r="683" spans="3:3" ht="14.25">
+    <row r="683" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C683" s="2"/>
     </row>
-    <row r="684" spans="3:3" ht="14.25">
+    <row r="684" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C684" s="2"/>
     </row>
-    <row r="685" spans="3:3" ht="14.25">
+    <row r="685" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C685" s="2"/>
     </row>
-    <row r="686" spans="3:3" ht="14.25">
+    <row r="686" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C686" s="2"/>
     </row>
-    <row r="687" spans="3:3" ht="14.25">
+    <row r="687" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C687" s="2"/>
     </row>
-    <row r="688" spans="3:3" ht="14.25">
+    <row r="688" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C688" s="2"/>
     </row>
-    <row r="689" spans="3:3" ht="14.25">
+    <row r="689" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C689" s="2"/>
     </row>
-    <row r="690" spans="3:3" ht="14.25">
+    <row r="690" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C690" s="2"/>
     </row>
-    <row r="691" spans="3:3" ht="14.25">
+    <row r="691" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C691" s="2"/>
     </row>
-    <row r="692" spans="3:3" ht="14.25">
+    <row r="692" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C692" s="2"/>
     </row>
-    <row r="693" spans="3:3" ht="14.25">
+    <row r="693" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C693" s="2"/>
     </row>
-    <row r="694" spans="3:3" ht="14.25">
+    <row r="694" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C694" s="2"/>
     </row>
-    <row r="695" spans="3:3" ht="14.25">
+    <row r="695" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C695" s="2"/>
     </row>
-    <row r="696" spans="3:3" ht="14.25">
+    <row r="696" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C696" s="2"/>
     </row>
-    <row r="697" spans="3:3" ht="14.25">
+    <row r="697" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C697" s="2"/>
     </row>
-    <row r="698" spans="3:3" ht="14.25">
+    <row r="698" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C698" s="2"/>
     </row>
-    <row r="699" spans="3:3" ht="14.25">
+    <row r="699" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C699" s="2"/>
     </row>
-    <row r="700" spans="3:3" ht="14.25">
+    <row r="700" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C700" s="2"/>
     </row>
-    <row r="701" spans="3:3" ht="14.25">
+    <row r="701" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C701" s="2"/>
     </row>
-    <row r="702" spans="3:3" ht="14.25">
+    <row r="702" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C702" s="2"/>
     </row>
-    <row r="703" spans="3:3" ht="14.25">
+    <row r="703" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C703" s="2"/>
     </row>
-    <row r="704" spans="3:3" ht="14.25">
+    <row r="704" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C704" s="2"/>
     </row>
-    <row r="705" spans="3:3" ht="14.25">
+    <row r="705" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C705" s="2"/>
     </row>
-    <row r="706" spans="3:3" ht="14.25">
+    <row r="706" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C706" s="2"/>
     </row>
-    <row r="707" spans="3:3" ht="14.25">
+    <row r="707" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C707" s="2"/>
     </row>
-    <row r="708" spans="3:3" ht="14.25">
+    <row r="708" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C708" s="2"/>
     </row>
-    <row r="709" spans="3:3" ht="14.25">
+    <row r="709" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C709" s="2"/>
     </row>
-    <row r="710" spans="3:3" ht="14.25">
+    <row r="710" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C710" s="2"/>
     </row>
-    <row r="711" spans="3:3" ht="14.25">
+    <row r="711" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C711" s="2"/>
     </row>
-    <row r="712" spans="3:3" ht="14.25">
+    <row r="712" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C712" s="2"/>
     </row>
-    <row r="713" spans="3:3" ht="14.25">
+    <row r="713" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C713" s="2"/>
     </row>
-    <row r="714" spans="3:3" ht="14.25">
+    <row r="714" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C714" s="2"/>
     </row>
-    <row r="715" spans="3:3" ht="14.25">
+    <row r="715" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C715" s="2"/>
     </row>
-    <row r="716" spans="3:3" ht="14.25">
+    <row r="716" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C716" s="2"/>
     </row>
-    <row r="717" spans="3:3" ht="14.25">
+    <row r="717" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C717" s="2"/>
     </row>
-    <row r="718" spans="3:3" ht="14.25">
+    <row r="718" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C718" s="2"/>
     </row>
-    <row r="719" spans="3:3" ht="14.25">
+    <row r="719" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C719" s="2"/>
     </row>
-    <row r="720" spans="3:3" ht="14.25">
+    <row r="720" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C720" s="2"/>
     </row>
-    <row r="721" spans="3:3" ht="14.25">
+    <row r="721" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C721" s="2"/>
     </row>
-    <row r="722" spans="3:3" ht="14.25">
+    <row r="722" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C722" s="2"/>
     </row>
-    <row r="723" spans="3:3" ht="14.25">
+    <row r="723" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C723" s="2"/>
     </row>
-    <row r="724" spans="3:3" ht="14.25">
+    <row r="724" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C724" s="2"/>
     </row>
-    <row r="725" spans="3:3" ht="14.25">
+    <row r="725" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C725" s="2"/>
     </row>
-    <row r="726" spans="3:3" ht="14.25">
+    <row r="726" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C726" s="2"/>
     </row>
-    <row r="727" spans="3:3" ht="14.25">
+    <row r="727" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C727" s="2"/>
     </row>
-    <row r="728" spans="3:3" ht="14.25">
+    <row r="728" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C728" s="2"/>
     </row>
-    <row r="729" spans="3:3" ht="14.25">
+    <row r="729" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C729" s="2"/>
     </row>
-    <row r="730" spans="3:3" ht="14.25">
+    <row r="730" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C730" s="2"/>
     </row>
-    <row r="731" spans="3:3" ht="14.25">
+    <row r="731" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C731" s="2"/>
     </row>
-    <row r="732" spans="3:3" ht="14.25">
+    <row r="732" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C732" s="2"/>
     </row>
-    <row r="733" spans="3:3" ht="14.25">
+    <row r="733" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C733" s="2"/>
     </row>
-    <row r="734" spans="3:3" ht="14.25">
+    <row r="734" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C734" s="2"/>
     </row>
-    <row r="735" spans="3:3" ht="14.25">
+    <row r="735" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C735" s="2"/>
     </row>
-    <row r="736" spans="3:3" ht="14.25">
+    <row r="736" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C736" s="2"/>
     </row>
-    <row r="737" spans="3:3" ht="14.25">
+    <row r="737" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C737" s="2"/>
     </row>
-    <row r="738" spans="3:3" ht="14.25">
+    <row r="738" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C738" s="2"/>
     </row>
-    <row r="739" spans="3:3" ht="14.25">
+    <row r="739" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C739" s="2"/>
     </row>
-    <row r="740" spans="3:3" ht="14.25">
+    <row r="740" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C740" s="2"/>
     </row>
-    <row r="741" spans="3:3" ht="14.25">
+    <row r="741" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C741" s="2"/>
     </row>
-    <row r="742" spans="3:3" ht="14.25">
+    <row r="742" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C742" s="2"/>
     </row>
-    <row r="743" spans="3:3" ht="14.25">
+    <row r="743" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C743" s="2"/>
     </row>
-    <row r="744" spans="3:3" ht="14.25">
+    <row r="744" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C744" s="2"/>
     </row>
-    <row r="745" spans="3:3" ht="14.25">
+    <row r="745" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C745" s="2"/>
     </row>
-    <row r="746" spans="3:3" ht="14.25">
+    <row r="746" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C746" s="2"/>
     </row>
-    <row r="747" spans="3:3" ht="14.25">
+    <row r="747" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C747" s="2"/>
     </row>
-    <row r="748" spans="3:3" ht="14.25">
+    <row r="748" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C748" s="2"/>
     </row>
-    <row r="749" spans="3:3" ht="14.25">
+    <row r="749" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C749" s="2"/>
     </row>
-    <row r="750" spans="3:3" ht="14.25">
+    <row r="750" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C750" s="2"/>
     </row>
-    <row r="751" spans="3:3" ht="14.25">
+    <row r="751" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C751" s="2"/>
     </row>
-    <row r="752" spans="3:3" ht="14.25">
+    <row r="752" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C752" s="2"/>
     </row>
-    <row r="753" spans="3:3" ht="14.25">
+    <row r="753" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C753" s="2"/>
     </row>
-    <row r="754" spans="3:3" ht="14.25">
+    <row r="754" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C754" s="2"/>
     </row>
-    <row r="755" spans="3:3" ht="14.25">
+    <row r="755" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C755" s="2"/>
     </row>
-    <row r="756" spans="3:3" ht="14.25">
+    <row r="756" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C756" s="2"/>
     </row>
-    <row r="757" spans="3:3" ht="14.25">
+    <row r="757" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C757" s="2"/>
     </row>
-    <row r="758" spans="3:3" ht="14.25">
+    <row r="758" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C758" s="2"/>
     </row>
-    <row r="759" spans="3:3" ht="14.25">
+    <row r="759" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C759" s="2"/>
     </row>
-    <row r="760" spans="3:3" ht="14.25">
+    <row r="760" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C760" s="2"/>
     </row>
-    <row r="761" spans="3:3" ht="14.25">
+    <row r="761" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C761" s="2"/>
     </row>
-    <row r="762" spans="3:3" ht="14.25">
+    <row r="762" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C762" s="2"/>
     </row>
-    <row r="763" spans="3:3" ht="14.25">
+    <row r="763" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C763" s="2"/>
     </row>
-    <row r="764" spans="3:3" ht="14.25">
+    <row r="764" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C764" s="2"/>
     </row>
-    <row r="765" spans="3:3" ht="14.25">
+    <row r="765" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C765" s="2"/>
     </row>
-    <row r="766" spans="3:3" ht="14.25">
+    <row r="766" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C766" s="2"/>
     </row>
-    <row r="767" spans="3:3" ht="14.25">
+    <row r="767" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C767" s="2"/>
     </row>
-    <row r="768" spans="3:3" ht="14.25">
+    <row r="768" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C768" s="2"/>
     </row>
-    <row r="769" spans="3:3" ht="14.25">
+    <row r="769" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C769" s="2"/>
     </row>
-    <row r="770" spans="3:3" ht="14.25">
+    <row r="770" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C770" s="2"/>
     </row>
-    <row r="771" spans="3:3" ht="14.25">
+    <row r="771" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C771" s="2"/>
     </row>
-    <row r="772" spans="3:3" ht="14.25">
+    <row r="772" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C772" s="2"/>
     </row>
-    <row r="773" spans="3:3" ht="14.25">
+    <row r="773" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C773" s="2"/>
     </row>
-    <row r="774" spans="3:3" ht="14.25">
+    <row r="774" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C774" s="2"/>
     </row>
-    <row r="775" spans="3:3" ht="14.25">
+    <row r="775" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C775" s="2"/>
     </row>
-    <row r="776" spans="3:3" ht="14.25">
+    <row r="776" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C776" s="2"/>
     </row>
-    <row r="777" spans="3:3" ht="14.25">
+    <row r="777" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C777" s="2"/>
     </row>
-    <row r="778" spans="3:3" ht="14.25">
+    <row r="778" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C778" s="2"/>
     </row>
-    <row r="779" spans="3:3" ht="14.25">
+    <row r="779" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C779" s="2"/>
     </row>
-    <row r="780" spans="3:3" ht="14.25">
+    <row r="780" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C780" s="2"/>
     </row>
-    <row r="781" spans="3:3" ht="14.25">
+    <row r="781" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C781" s="2"/>
     </row>
-    <row r="782" spans="3:3" ht="14.25">
+    <row r="782" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C782" s="2"/>
     </row>
-    <row r="783" spans="3:3" ht="14.25">
+    <row r="783" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C783" s="2"/>
     </row>
-    <row r="784" spans="3:3" ht="14.25">
+    <row r="784" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C784" s="2"/>
     </row>
-    <row r="785" spans="3:3" ht="14.25">
+    <row r="785" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C785" s="2"/>
     </row>
-    <row r="786" spans="3:3" ht="14.25">
+    <row r="786" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C786" s="2"/>
     </row>
-    <row r="787" spans="3:3" ht="14.25">
+    <row r="787" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C787" s="2"/>
     </row>
-    <row r="788" spans="3:3" ht="14.25">
+    <row r="788" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C788" s="2"/>
     </row>
-    <row r="789" spans="3:3" ht="14.25">
+    <row r="789" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C789" s="2"/>
     </row>
-    <row r="790" spans="3:3" ht="14.25">
+    <row r="790" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C790" s="2"/>
     </row>
-    <row r="791" spans="3:3" ht="14.25">
+    <row r="791" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C791" s="2"/>
     </row>
-    <row r="792" spans="3:3" ht="14.25">
+    <row r="792" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C792" s="2"/>
     </row>
-    <row r="793" spans="3:3" ht="14.25">
+    <row r="793" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C793" s="2"/>
     </row>
-    <row r="794" spans="3:3" ht="14.25">
+    <row r="794" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C794" s="2"/>
     </row>
-    <row r="795" spans="3:3" ht="14.25">
+    <row r="795" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C795" s="2"/>
     </row>
-    <row r="796" spans="3:3" ht="14.25">
+    <row r="796" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C796" s="2"/>
     </row>
-    <row r="797" spans="3:3" ht="14.25">
+    <row r="797" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C797" s="2"/>
     </row>
-    <row r="798" spans="3:3" ht="14.25">
+    <row r="798" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C798" s="2"/>
     </row>
-    <row r="799" spans="3:3" ht="14.25">
+    <row r="799" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C799" s="2"/>
     </row>
-    <row r="800" spans="3:3" ht="14.25">
+    <row r="800" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C800" s="2"/>
     </row>
-    <row r="801" spans="3:3" ht="14.25">
+    <row r="801" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C801" s="2"/>
     </row>
-    <row r="802" spans="3:3" ht="14.25">
+    <row r="802" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C802" s="2"/>
     </row>
-    <row r="803" spans="3:3" ht="14.25">
+    <row r="803" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C803" s="2"/>
     </row>
-    <row r="804" spans="3:3" ht="14.25">
+    <row r="804" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C804" s="2"/>
     </row>
-    <row r="805" spans="3:3" ht="14.25">
+    <row r="805" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C805" s="2"/>
     </row>
-    <row r="806" spans="3:3" ht="14.25">
+    <row r="806" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C806" s="2"/>
     </row>
-    <row r="807" spans="3:3" ht="14.25">
+    <row r="807" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C807" s="2"/>
     </row>
-    <row r="808" spans="3:3" ht="14.25">
+    <row r="808" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C808" s="2"/>
     </row>
-    <row r="809" spans="3:3" ht="14.25">
+    <row r="809" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C809" s="2"/>
     </row>
-    <row r="810" spans="3:3" ht="14.25">
+    <row r="810" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C810" s="2"/>
     </row>
-    <row r="811" spans="3:3" ht="14.25">
+    <row r="811" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C811" s="2"/>
     </row>
-    <row r="812" spans="3:3" ht="14.25">
+    <row r="812" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C812" s="2"/>
     </row>
-    <row r="813" spans="3:3" ht="14.25">
+    <row r="813" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C813" s="2"/>
     </row>
-    <row r="814" spans="3:3" ht="14.25">
+    <row r="814" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C814" s="2"/>
     </row>
-    <row r="815" spans="3:3" ht="14.25">
+    <row r="815" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C815" s="2"/>
     </row>
-    <row r="816" spans="3:3" ht="14.25">
+    <row r="816" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C816" s="2"/>
     </row>
-    <row r="817" spans="3:3" ht="14.25">
+    <row r="817" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C817" s="2"/>
     </row>
-    <row r="818" spans="3:3" ht="14.25">
+    <row r="818" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C818" s="2"/>
     </row>
-    <row r="819" spans="3:3" ht="14.25">
+    <row r="819" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C819" s="2"/>
     </row>
-    <row r="820" spans="3:3" ht="14.25">
+    <row r="820" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C820" s="2"/>
     </row>
-    <row r="821" spans="3:3" ht="14.25">
+    <row r="821" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C821" s="2"/>
     </row>
-    <row r="822" spans="3:3" ht="14.25">
+    <row r="822" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C822" s="2"/>
     </row>
-    <row r="823" spans="3:3" ht="14.25">
+    <row r="823" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C823" s="2"/>
     </row>
-    <row r="824" spans="3:3" ht="14.25">
+    <row r="824" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C824" s="2"/>
     </row>
-    <row r="825" spans="3:3" ht="14.25">
+    <row r="825" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C825" s="2"/>
     </row>
-    <row r="826" spans="3:3" ht="14.25">
+    <row r="826" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C826" s="2"/>
     </row>
-    <row r="827" spans="3:3" ht="14.25">
+    <row r="827" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C827" s="2"/>
     </row>
-    <row r="828" spans="3:3" ht="14.25">
+    <row r="828" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C828" s="2"/>
     </row>
-    <row r="829" spans="3:3" ht="14.25">
+    <row r="829" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C829" s="2"/>
     </row>
-    <row r="830" spans="3:3" ht="14.25">
+    <row r="830" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C830" s="2"/>
     </row>
-    <row r="831" spans="3:3" ht="14.25">
+    <row r="831" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C831" s="2"/>
     </row>
-    <row r="832" spans="3:3" ht="14.25">
+    <row r="832" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C832" s="2"/>
     </row>
-    <row r="833" spans="3:3" ht="14.25">
+    <row r="833" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C833" s="2"/>
     </row>
-    <row r="834" spans="3:3" ht="14.25">
+    <row r="834" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C834" s="2"/>
     </row>
-    <row r="835" spans="3:3" ht="14.25">
+    <row r="835" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C835" s="2"/>
     </row>
-    <row r="836" spans="3:3" ht="14.25">
+    <row r="836" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C836" s="2"/>
     </row>
-    <row r="837" spans="3:3" ht="14.25">
+    <row r="837" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C837" s="2"/>
     </row>
-    <row r="838" spans="3:3" ht="14.25">
+    <row r="838" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C838" s="2"/>
     </row>
-    <row r="839" spans="3:3" ht="14.25">
+    <row r="839" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C839" s="2"/>
     </row>
-    <row r="840" spans="3:3" ht="14.25">
+    <row r="840" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C840" s="2"/>
     </row>
-    <row r="841" spans="3:3" ht="14.25">
+    <row r="841" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C841" s="2"/>
     </row>
-    <row r="842" spans="3:3" ht="14.25">
+    <row r="842" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C842" s="2"/>
     </row>
-    <row r="843" spans="3:3" ht="14.25">
+    <row r="843" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C843" s="2"/>
     </row>
-    <row r="844" spans="3:3" ht="14.25">
+    <row r="844" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C844" s="2"/>
     </row>
-    <row r="845" spans="3:3" ht="14.25">
+    <row r="845" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C845" s="2"/>
     </row>
-    <row r="846" spans="3:3" ht="14.25">
+    <row r="846" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C846" s="2"/>
     </row>
-    <row r="847" spans="3:3" ht="14.25">
+    <row r="847" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C847" s="2"/>
     </row>
-    <row r="848" spans="3:3" ht="14.25">
+    <row r="848" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C848" s="2"/>
     </row>
-    <row r="849" spans="3:3" ht="14.25">
+    <row r="849" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C849" s="2"/>
     </row>
-    <row r="850" spans="3:3" ht="14.25">
+    <row r="850" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C850" s="2"/>
     </row>
-    <row r="851" spans="3:3" ht="14.25">
+    <row r="851" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C851" s="2"/>
     </row>
-    <row r="852" spans="3:3" ht="14.25">
+    <row r="852" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C852" s="2"/>
     </row>
-    <row r="853" spans="3:3" ht="14.25">
+    <row r="853" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C853" s="2"/>
     </row>
-    <row r="854" spans="3:3" ht="14.25">
+    <row r="854" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C854" s="2"/>
     </row>
-    <row r="855" spans="3:3" ht="14.25">
+    <row r="855" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C855" s="2"/>
     </row>
-    <row r="856" spans="3:3" ht="14.25">
+    <row r="856" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C856" s="2"/>
     </row>
-    <row r="857" spans="3:3" ht="14.25">
+    <row r="857" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C857" s="2"/>
     </row>
-    <row r="858" spans="3:3" ht="14.25">
+    <row r="858" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C858" s="2"/>
     </row>
-    <row r="859" spans="3:3" ht="14.25">
+    <row r="859" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C859" s="2"/>
     </row>
-    <row r="860" spans="3:3" ht="14.25">
+    <row r="860" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C860" s="2"/>
     </row>
-    <row r="861" spans="3:3" ht="14.25">
+    <row r="861" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C861" s="2"/>
     </row>
-    <row r="862" spans="3:3" ht="14.25">
+    <row r="862" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C862" s="2"/>
     </row>
-    <row r="863" spans="3:3" ht="14.25">
+    <row r="863" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C863" s="2"/>
     </row>
-    <row r="864" spans="3:3" ht="14.25">
+    <row r="864" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C864" s="2"/>
     </row>
-    <row r="865" spans="3:3" ht="14.25">
+    <row r="865" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C865" s="2"/>
     </row>
-    <row r="866" spans="3:3" ht="14.25">
+    <row r="866" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C866" s="2"/>
     </row>
-    <row r="867" spans="3:3" ht="14.25">
+    <row r="867" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C867" s="2"/>
     </row>
-    <row r="868" spans="3:3" ht="14.25">
+    <row r="868" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C868" s="2"/>
     </row>
-    <row r="869" spans="3:3" ht="14.25">
+    <row r="869" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C869" s="2"/>
     </row>
-    <row r="870" spans="3:3" ht="14.25">
+    <row r="870" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C870" s="2"/>
     </row>
-    <row r="871" spans="3:3" ht="14.25">
+    <row r="871" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C871" s="2"/>
     </row>
-    <row r="872" spans="3:3" ht="14.25">
+    <row r="872" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C872" s="2"/>
     </row>
-    <row r="873" spans="3:3" ht="14.25">
+    <row r="873" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C873" s="2"/>
     </row>
-    <row r="874" spans="3:3" ht="14.25">
+    <row r="874" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C874" s="2"/>
     </row>
-    <row r="875" spans="3:3" ht="14.25">
+    <row r="875" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C875" s="2"/>
     </row>
-    <row r="876" spans="3:3" ht="14.25">
+    <row r="876" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C876" s="2"/>
     </row>
-    <row r="877" spans="3:3" ht="14.25">
+    <row r="877" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C877" s="2"/>
     </row>
-    <row r="878" spans="3:3" ht="14.25">
+    <row r="878" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C878" s="2"/>
     </row>
-    <row r="879" spans="3:3" ht="14.25">
+    <row r="879" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C879" s="2"/>
     </row>
-    <row r="880" spans="3:3" ht="14.25">
+    <row r="880" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C880" s="2"/>
     </row>
-    <row r="881" spans="3:3" ht="14.25">
+    <row r="881" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C881" s="2"/>
     </row>
-    <row r="882" spans="3:3" ht="14.25">
+    <row r="882" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C882" s="2"/>
     </row>
-    <row r="883" spans="3:3" ht="14.25">
+    <row r="883" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C883" s="2"/>
     </row>
-    <row r="884" spans="3:3" ht="14.25">
+    <row r="884" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C884" s="2"/>
     </row>
-    <row r="885" spans="3:3" ht="14.25">
+    <row r="885" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C885" s="2"/>
     </row>
-    <row r="886" spans="3:3" ht="14.25">
+    <row r="886" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C886" s="2"/>
     </row>
-    <row r="887" spans="3:3" ht="14.25">
+    <row r="887" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C887" s="2"/>
     </row>
-    <row r="888" spans="3:3" ht="14.25">
+    <row r="888" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C888" s="2"/>
     </row>
-    <row r="889" spans="3:3" ht="14.25">
+    <row r="889" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C889" s="2"/>
     </row>
-    <row r="890" spans="3:3" ht="14.25">
+    <row r="890" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C890" s="2"/>
     </row>
-    <row r="891" spans="3:3" ht="14.25">
+    <row r="891" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C891" s="2"/>
     </row>
-    <row r="892" spans="3:3" ht="14.25">
+    <row r="892" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C892" s="2"/>
     </row>
-    <row r="893" spans="3:3" ht="14.25">
+    <row r="893" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C893" s="2"/>
     </row>
-    <row r="894" spans="3:3" ht="14.25">
+    <row r="894" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C894" s="2"/>
     </row>
-    <row r="895" spans="3:3" ht="14.25">
+    <row r="895" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C895" s="2"/>
     </row>
-    <row r="896" spans="3:3" ht="14.25">
+    <row r="896" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C896" s="2"/>
     </row>
-    <row r="897" spans="3:3" ht="14.25">
+    <row r="897" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C897" s="2"/>
     </row>
-    <row r="898" spans="3:3" ht="14.25">
+    <row r="898" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C898" s="2"/>
     </row>
-    <row r="899" spans="3:3" ht="14.25">
+    <row r="899" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C899" s="2"/>
     </row>
-    <row r="900" spans="3:3" ht="14.25">
+    <row r="900" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C900" s="2"/>
     </row>
-    <row r="901" spans="3:3" ht="14.25">
+    <row r="901" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C901" s="2"/>
     </row>
-    <row r="902" spans="3:3" ht="14.25">
+    <row r="902" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C902" s="2"/>
     </row>
-    <row r="903" spans="3:3" ht="14.25">
+    <row r="903" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C903" s="2"/>
     </row>
-    <row r="904" spans="3:3" ht="14.25">
+    <row r="904" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C904" s="2"/>
     </row>
-    <row r="905" spans="3:3" ht="14.25">
+    <row r="905" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C905" s="2"/>
     </row>
-    <row r="906" spans="3:3" ht="14.25">
+    <row r="906" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C906" s="2"/>
     </row>
-    <row r="907" spans="3:3" ht="14.25">
+    <row r="907" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C907" s="2"/>
     </row>
-    <row r="908" spans="3:3" ht="14.25">
+    <row r="908" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C908" s="2"/>
     </row>
-    <row r="909" spans="3:3" ht="14.25">
+    <row r="909" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C909" s="2"/>
     </row>
-    <row r="910" spans="3:3" ht="14.25">
+    <row r="910" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C910" s="2"/>
     </row>
-    <row r="911" spans="3:3" ht="14.25">
+    <row r="911" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C911" s="2"/>
     </row>
-    <row r="912" spans="3:3" ht="14.25">
+    <row r="912" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C912" s="2"/>
     </row>
-    <row r="913" spans="3:3" ht="14.25">
+    <row r="913" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C913" s="2"/>
     </row>
-    <row r="914" spans="3:3" ht="14.25">
+    <row r="914" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C914" s="2"/>
     </row>
-    <row r="915" spans="3:3" ht="14.25">
+    <row r="915" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C915" s="2"/>
     </row>
-    <row r="916" spans="3:3" ht="14.25">
+    <row r="916" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C916" s="2"/>
     </row>
-    <row r="917" spans="3:3" ht="14.25">
+    <row r="917" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C917" s="2"/>
     </row>
-    <row r="918" spans="3:3" ht="14.25">
+    <row r="918" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C918" s="2"/>
     </row>
-    <row r="919" spans="3:3" ht="14.25">
+    <row r="919" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C919" s="2"/>
     </row>
-    <row r="920" spans="3:3" ht="14.25">
+    <row r="920" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C920" s="2"/>
     </row>
-    <row r="921" spans="3:3" ht="14.25">
+    <row r="921" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C921" s="2"/>
     </row>
-    <row r="922" spans="3:3" ht="14.25">
+    <row r="922" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C922" s="2"/>
     </row>
-    <row r="923" spans="3:3" ht="14.25">
+    <row r="923" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C923" s="2"/>
     </row>
-    <row r="924" spans="3:3" ht="14.25">
+    <row r="924" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C924" s="2"/>
     </row>
-    <row r="925" spans="3:3" ht="14.25">
+    <row r="925" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C925" s="2"/>
     </row>
-    <row r="926" spans="3:3" ht="14.25">
+    <row r="926" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C926" s="2"/>
     </row>
-    <row r="927" spans="3:3" ht="14.25">
+    <row r="927" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C927" s="2"/>
     </row>
-    <row r="928" spans="3:3" ht="14.25">
+    <row r="928" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C928" s="2"/>
     </row>
-    <row r="929" spans="3:3" ht="14.25">
+    <row r="929" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C929" s="2"/>
     </row>
-    <row r="930" spans="3:3" ht="14.25">
+    <row r="930" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C930" s="2"/>
     </row>
-    <row r="931" spans="3:3" ht="14.25">
+    <row r="931" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C931" s="2"/>
     </row>
-    <row r="932" spans="3:3" ht="14.25">
+    <row r="932" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C932" s="2"/>
     </row>
-    <row r="933" spans="3:3" ht="14.25">
+    <row r="933" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C933" s="2"/>
     </row>
-    <row r="934" spans="3:3" ht="14.25">
+    <row r="934" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C934" s="2"/>
     </row>
-    <row r="935" spans="3:3" ht="14.25">
+    <row r="935" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C935" s="2"/>
     </row>
-    <row r="936" spans="3:3" ht="14.25">
+    <row r="936" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C936" s="2"/>
     </row>
-    <row r="937" spans="3:3" ht="14.25">
+    <row r="937" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C937" s="2"/>
     </row>
-    <row r="938" spans="3:3" ht="14.25">
+    <row r="938" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C938" s="2"/>
     </row>
-    <row r="939" spans="3:3" ht="14.25">
+    <row r="939" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C939" s="2"/>
     </row>
-    <row r="940" spans="3:3" ht="14.25">
+    <row r="940" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C940" s="2"/>
     </row>
-    <row r="941" spans="3:3" ht="14.25">
+    <row r="941" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C941" s="2"/>
     </row>
-    <row r="942" spans="3:3" ht="14.25">
+    <row r="942" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C942" s="2"/>
     </row>
-    <row r="943" spans="3:3" ht="14.25">
+    <row r="943" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C943" s="2"/>
     </row>
-    <row r="944" spans="3:3" ht="14.25">
+    <row r="944" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C944" s="2"/>
     </row>
-    <row r="945" spans="3:3" ht="14.25">
+    <row r="945" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C945" s="2"/>
     </row>
-    <row r="946" spans="3:3" ht="14.25">
+    <row r="946" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C946" s="2"/>
     </row>
-    <row r="947" spans="3:3" ht="14.25">
+    <row r="947" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C947" s="2"/>
     </row>
-    <row r="948" spans="3:3" ht="14.25">
+    <row r="948" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C948" s="2"/>
     </row>
-    <row r="949" spans="3:3" ht="14.25">
+    <row r="949" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C949" s="2"/>
     </row>
-    <row r="950" spans="3:3" ht="14.25">
+    <row r="950" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C950" s="2"/>
     </row>
-    <row r="951" spans="3:3" ht="14.25">
+    <row r="951" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C951" s="2"/>
     </row>
-    <row r="952" spans="3:3" ht="14.25">
+    <row r="952" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C952" s="2"/>
     </row>
-    <row r="953" spans="3:3" ht="14.25">
+    <row r="953" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C953" s="2"/>
     </row>
-    <row r="954" spans="3:3" ht="14.25">
+    <row r="954" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C954" s="2"/>
     </row>
-    <row r="955" spans="3:3" ht="14.25">
+    <row r="955" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C955" s="2"/>
     </row>
-    <row r="956" spans="3:3" ht="14.25">
+    <row r="956" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C956" s="2"/>
     </row>
-    <row r="957" spans="3:3" ht="14.25">
+    <row r="957" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C957" s="2"/>
     </row>
-    <row r="958" spans="3:3" ht="14.25">
+    <row r="958" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C958" s="2"/>
     </row>
-    <row r="959" spans="3:3" ht="14.25">
+    <row r="959" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C959" s="2"/>
     </row>
-    <row r="960" spans="3:3" ht="14.25">
+    <row r="960" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C960" s="2"/>
     </row>
-    <row r="961" spans="3:3" ht="14.25">
+    <row r="961" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C961" s="2"/>
     </row>
-    <row r="962" spans="3:3" ht="14.25">
+    <row r="962" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C962" s="2"/>
     </row>
-    <row r="963" spans="3:3" ht="14.25">
+    <row r="963" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C963" s="2"/>
     </row>
-    <row r="964" spans="3:3" ht="14.25">
+    <row r="964" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C964" s="2"/>
     </row>
-    <row r="965" spans="3:3" ht="14.25">
+    <row r="965" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C965" s="2"/>
     </row>
-    <row r="966" spans="3:3" ht="14.25">
+    <row r="966" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C966" s="2"/>
     </row>
-    <row r="967" spans="3:3" ht="14.25">
+    <row r="967" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C967" s="2"/>
     </row>
-    <row r="968" spans="3:3" ht="14.25">
+    <row r="968" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C968" s="2"/>
     </row>
-    <row r="969" spans="3:3" ht="14.25">
+    <row r="969" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C969" s="2"/>
     </row>
-    <row r="970" spans="3:3" ht="14.25">
+    <row r="970" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C970" s="2"/>
     </row>
-    <row r="971" spans="3:3" ht="14.25">
+    <row r="971" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C971" s="2"/>
     </row>
-    <row r="972" spans="3:3" ht="14.25">
+    <row r="972" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C972" s="2"/>
     </row>
-    <row r="973" spans="3:3" ht="14.25">
+    <row r="973" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C973" s="2"/>
     </row>
-    <row r="974" spans="3:3" ht="14.25">
+    <row r="974" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C974" s="2"/>
     </row>
-    <row r="975" spans="3:3" ht="14.25">
+    <row r="975" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C975" s="2"/>
     </row>
-    <row r="976" spans="3:3" ht="14.25">
+    <row r="976" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C976" s="2"/>
     </row>
-    <row r="977" spans="3:3" ht="14.25">
+    <row r="977" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C977" s="2"/>
     </row>
-    <row r="978" spans="3:3" ht="14.25">
+    <row r="978" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C978" s="2"/>
     </row>
-    <row r="979" spans="3:3" ht="14.25">
+    <row r="979" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C979" s="2"/>
     </row>
-    <row r="980" spans="3:3" ht="14.25">
+    <row r="980" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C980" s="2"/>
     </row>
-    <row r="981" spans="3:3" ht="14.25">
+    <row r="981" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C981" s="2"/>
     </row>
-    <row r="982" spans="3:3" ht="14.25">
+    <row r="982" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C982" s="2"/>
     </row>
-    <row r="983" spans="3:3" ht="14.25">
+    <row r="983" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C983" s="2"/>
     </row>
-    <row r="984" spans="3:3" ht="14.25">
+    <row r="984" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C984" s="2"/>
     </row>
-    <row r="985" spans="3:3" ht="14.25">
+    <row r="985" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C985" s="2"/>
     </row>
-    <row r="986" spans="3:3" ht="14.25">
+    <row r="986" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C986" s="2"/>
     </row>
-    <row r="987" spans="3:3" ht="14.25">
+    <row r="987" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C987" s="2"/>
     </row>
-    <row r="988" spans="3:3" ht="14.25">
+    <row r="988" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C988" s="2"/>
     </row>
-    <row r="989" spans="3:3" ht="14.25">
+    <row r="989" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C989" s="2"/>
     </row>
-    <row r="990" spans="3:3" ht="14.25">
+    <row r="990" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C990" s="2"/>
     </row>
-    <row r="991" spans="3:3" ht="14.25">
+    <row r="991" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C991" s="2"/>
     </row>
-    <row r="992" spans="3:3" ht="14.25">
+    <row r="992" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C992" s="2"/>
     </row>
-    <row r="993" spans="3:3" ht="14.25">
+    <row r="993" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C993" s="2"/>
     </row>
-    <row r="994" spans="3:3" ht="14.25">
+    <row r="994" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C994" s="2"/>
     </row>
-    <row r="995" spans="3:3" ht="14.25">
+    <row r="995" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C995" s="2"/>
     </row>
-    <row r="996" spans="3:3" ht="14.25">
+    <row r="996" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C996" s="2"/>
     </row>
-    <row r="997" spans="3:3" ht="14.25">
+    <row r="997" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C997" s="2"/>
     </row>
-    <row r="998" spans="3:3" ht="14.25">
+    <row r="998" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C998" s="2"/>
     </row>
-    <row r="999" spans="3:3" ht="14.25">
+    <row r="999" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C999" s="2"/>
     </row>
-    <row r="1000" spans="3:3" ht="14.25">
+    <row r="1000" spans="3:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C1000" s="2"/>
     </row>
   </sheetData>
